--- a/Aamir Khan Filmography.xlsx
+++ b/Aamir Khan Filmography.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Films" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Romances" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Collaborators" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ensemble Cast" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Awards" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Films" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Romances" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaborators" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ensemble Cast" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Awards" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Films'!$A$1:$AT$58</definedName>
@@ -245,14 +245,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -272,7 +272,7 @@
             <v>Lover-boy score</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -281,7 +281,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -313,8 +313,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -342,8 +342,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -366,14 +366,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -397,7 +397,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -448,14 +448,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -475,7 +475,7 @@
             <v>External opposition</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -484,7 +484,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -516,8 +516,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -545,8 +545,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,14 +569,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -600,7 +600,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -653,7 +653,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -668,9 +668,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -690,9 +690,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -712,9 +712,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -734,9 +734,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1061,7 +1061,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13 from the research files. Research cutoff: 2026-09-12. Released feature-film acting appearances through 12 September 2026, including child roles, cameos, song appearances and a voice role. Excluded: the silent short Paranoia (1983); the documentaries Madness in the Desert (2004) and Big in Bollywood (2011); producer-only credits; television; and Lahore 1947 (released 14 August 2026, Wikipedia page now titled Batwara 1947), where he is credited only as producer. Pre-2000 box-office figures come from Wikipedia citations of trade sources and are graded down accordingly. Collaborators covers directors, producers or banners, composers and key writers with at least two of his films, plus directors of historically significant single collaborations. Awards covers documented Filmfare and National Film Award wins for his non-cameo films, all of Aamir Khan's own Filmfare nominations, his wins at other ceremonies, civilian honours, and major international awards and nominations.</t>
+          <t>Generated 2026-10-08 from the research files. Research cutoff: 2026-09-12. Released feature-film acting appearances through 12 September 2026, including child roles, cameos, song appearances and a voice role. Excluded: the silent short Paranoia (1983); the documentaries Madness in the Desert (2004) and Big in Bollywood (2011); producer-only credits; television; and Lahore 1947 (released 14 August 2026, Wikipedia page now titled Batwara 1947), where he is credited only as producer. Pre-2000 box-office figures come from Wikipedia citations of trade sources and are graded down accordingly. Collaborators covers directors, producers or banners, composers and key writers with at least two of his films, plus directors of historically significant single collaborations. Awards covers documented Filmfare and National Film Award wins for his non-cameo films, all of Aamir Khan's own Filmfare nominations, his wins at other ceremonies, civilian honours, and major international awards and nominations.</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Aamir Khan Productions (10 films)</t>
+          <t>Aamir Khan Productions (11 films)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Karim Morani; Bunty Soorma; Aly Morani</t>
+          <t>Karim Morani; Bunty Soorma; Ali Morani</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Cineyug</t>
+          <t>Cineyug Films</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Praful Parikh, Rajiv Kaul (story, screenplay); Tanveer Khan (dialogue)</t>
+          <t>Praful Parekh, Rajeev Kaul (story, screenplay); Tanveer Khan (dialogue)</t>
         </is>
       </c>
       <c r="N28" s="5" t="n"/>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>Venus Records &amp; Tapes</t>
+          <t>Venus Movies</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="79" customHeight="1">
+    <row r="46" ht="94" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
         <is>
           <t>FILM-045</t>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>Flying Unicorn Entertainment; Dharma Productions; Dibakar Banerjee Productions; Excel Entertainment; AKFPL; Sikhya Entertainment</t>
+          <t>Flying Unicorn Entertainment; Dharma Productions; Dibakar Banerjee Productions; Excel Entertainment; Aamir Khan Productions; Sikhya Entertainment</t>
         </is>
       </c>
       <c r="M46" s="5" t="n"/>
@@ -21055,7 +21055,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="184" customHeight="1">
+    <row r="2" ht="169" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>PERSON-001</t>
@@ -21063,23 +21063,19 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Nasir Hussain</t>
+          <t>Aamir Khan Productions</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Director; producer; screenwriter (Nasir Hussain Films)</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>1926</v>
-      </c>
-      <c r="E2" s="17" t="n">
-        <v>2002</v>
-      </c>
+          <t>Production banner</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1948–1996</t>
+          <t>Founded 1999</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -21089,65 +21085,61 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Born in Bhopal State to a schoolteacher from a Pashtun zamindar family; joined Filmistan as a writer in 1948.</t>
+          <t>Founded by Aamir Khan; Kiran Rao, who met him as an assistant director on Lagaan, became a key producer.</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Writer on Anarkali (1953), Munimji (1955) and Paying Guest (1957); directorial debut Tumsa Nahin Dekha (1957), which made Shammi Kapoor a star.</t>
+          <t>Lagaan (2001).</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Tumsa Nahin Dekha (1957); Dil Deke Dekho (1959); Jab Pyar Kisi Se Hota Hai (1961); Teesri Manzil (1966); Caravan (1971); Yaadon Ki Baaraat (1973); Hum Kisise Kum Naheen (1977); Qayamat Se Qayamat Tak (1988); Jo Jeeta Wohi Sikandar (1992)</t>
+          <t>Lagaan (2001); Taare Zameen Par (2007); Jaane Tu... Ya Jaane Na (2008); Peepli Live (2010); Dhobi Ghat (2011); Delhi Belly (2011); Talaash (2012); Dangal (2016); Secret Superstar (2017); Laal Singh Chaddha (2022); Laapataa Ladies (2024); Sitaare Zameen Par (2025); Happy Patel: Khatarnak Jasoos (2026); Lahore 1947 / Batwara 1947 (2026)</t>
         </is>
       </c>
       <c r="K2" s="19" t="inlineStr">
         <is>
-          <t>Musical romances; youthful love against family obstacles; separated-family masala plots</t>
-        </is>
-      </c>
-      <c r="L2" s="19" t="inlineStr">
-        <is>
-          <t>Song-driven popular entertainment; Yaadon Ki Baaraat is identified as the first masala film, and Qayamat Se Qayamat Tak set the template for 1990s musical romance.</t>
-        </is>
-      </c>
+          <t>Socially engaged mainstream films, new directors and occasional art-house releases</t>
+        </is>
+      </c>
+      <c r="L2" s="19" t="n"/>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Best Film and Best Screenplay (Qayamat Se Qayamat Tak); Filmfare Best Film (Jo Jeeta Wohi Sikandar); Filmfare Special Award (1996)</t>
+          <t>Academy Award nomination (Lagaan); Filmfare Best Film (Lagaan; Taare Zameen Par; Dangal); National Film Awards including Best Popular Film (Lagaan) and Best Film on Family Welfare (Taare Zameen Par)</t>
         </is>
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>Described as a major trendsetter in Hindi cinema; Javed Akhtar rated him the most underrated producer-director of his generation.</t>
+          <t>Credited with opening Chinese markets to Indian films through the success of Dangal and Secret Superstar.</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
         <is>
-          <t>Uncle. Cast him as a child in Yaadon Ki Baaraat and produced and wrote the films that made him a star.</t>
+          <t>His own company, which produced or co-produced ten of his acting films, including his directorial debut.</t>
         </is>
       </c>
       <c r="P2" s="17" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>FILM-001; FILM-004; FILM-015; FILM-025</t>
+          <t>FILM-033; FILM-038; FILM-042; FILM-043; FILM-044; FILM-045; FILM-049; FILM-050; FILM-053; FILM-055; FILM-057</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>Qayamat Se Qayamat Tak (1988)</t>
+          <t>Lagaan (2001)</t>
         </is>
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Nasir Hussain was born in 1926 in Bhopal State and joined Filmistan as a writer in 1948, writing hits such as Anarkali, Munimji and Paying Guest. His directorial debut, Tumsa Nahin Dekha (1957), made Shammi Kapoor a star, and a run of musical romances followed, including Dil Deke Dekho and Jab Pyar Kisi Se Hota Hai. Under his own banner he made Caravan (1971) and Yaadon Ki Baaraat (1973), a lost-and-found family saga identified as the first quintessential masala film, and Hum Kisise Kum Naheen (1977). His later films as director failed, and his son Mansoor Khan took over the company. Together they reinvented the romantic musical with Qayamat Se Qayamat Tak (1988), which Nasir Hussain wrote and produced; it won the Filmfare awards for Best Film and Best Screenplay and set the template for Hindi romance in the 1990s. Jo Jeeta Wohi Sikandar (1992) brought another Filmfare Best Film award. For Aamir Khan, his nephew, Nasir Hussain was a formative figure: the eight-year-old appeared as young Ratan in the title song of Yaadon Ki Baaraat, and fifteen years later he launched Aamir as a romantic lead. He also wrote dialogue for Akele Hum Akele Tum (1995). He died in Mumbai on 13 March 2002.</t>
+          <t>Aamir Khan Productions was founded by Aamir Khan in 1999 and launched with Lagaan (2001), a then-unprecedentedly expensive cricket epic nominated for the Academy Award for Best Foreign Language Film. The company became the vehicle for Aamir's selective, message-led career. He directed Taare Zameen Par (2007) for it, and it backed first-time or early-career directors including Abbas Tyrewala (Jaane Tu... Ya Jaane Na), Kiran Rao (Dhobi Ghat, Laapataa Ladies), Abhinay Deo (Delhi Belly) and Advait Chandan (Secret Superstar, Laal Singh Chaddha). Many productions were made with partners, among them PVR, UTV, Excel Entertainment, Disney, Zee Studios, Paramount and Viacom18, and Jio Studios. Dangal (2016), co-produced with Disney, became the highest-grossing Indian film and, with Secret Superstar (2017), is credited with opening China to Indian cinema. The banner's recent run is mixed: the costly Laal Singh Chaddha (2022) was a box-office disaster, while Sitaare Zameen Par (2025) was a hit and Lahore 1947, released in 2026 as Batwara 1947, was not. Of its films, ten feature Aamir Khan on screen, from lead roles to a cameo in Happy Patel: Khatarnak Jasoos.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-075; SOURCE-004; SOURCE-007; SOURCE-021; SOURCE-031</t>
+          <t>SOURCE-099; SOURCE-039; SOURCE-044; SOURCE-055; SOURCE-056; SOURCE-059; SOURCE-061; SOURCE-064</t>
         </is>
       </c>
       <c r="U2" s="5" t="inlineStr">
@@ -21156,7 +21148,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="169" customHeight="1">
+    <row r="3" ht="199" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
           <t>PERSON-002</t>
@@ -21164,91 +21156,89 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>R. D. Burman</t>
+          <t>A. R. Rahman</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Music director</t>
+          <t>Music director (songs and background score)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1939</v>
-      </c>
-      <c r="E3" s="17" t="n">
-        <v>1994</v>
-      </c>
+        <v>1967</v>
+      </c>
+      <c r="E3" s="18" t="n"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1961–1994</t>
+          <t>1992–present</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil; Hindi; international</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Son of composer S. D. Burman and Meera Dev Burman; married Asha Bhosle in 1980.</t>
+          <t>Born Arunachalam Shekhar Dileep Kumar, son of Malayalam film composer R. K. Shekhar; composed advertising jingles from 1987.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Chhote Nawab (1961); breakthrough with Teesri Manzil (1966).</t>
+          <t>Roja (1992); Hindi breakthrough with Rangeela (1995).</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Teesri Manzil (1966); Hare Rama Hare Krishna (1971); Yaadon Ki Baaraat (1973); Sholay (1975); Hum Kisise Kum Naheen (1977); 1942: A Love Story (1994)</t>
+          <t>Roja (1992); Bombay (1995); Rangeela (1995); Dil Se.. (1998); Taal (1999); Lagaan (2001); Swades (2004); Rang De Basanti (2006); Jodhaa Akbar (2008); Slumdog Millionaire (2008); Rockstar (2011)</t>
         </is>
       </c>
       <c r="K3" s="19" t="inlineStr">
         <is>
-          <t>Youthful, dance-driven film music; experimental soundscapes</t>
+          <t>Epic, patriotic and romantic scores</t>
         </is>
       </c>
       <c r="L3" s="19" t="inlineStr">
         <is>
-          <t>Combined Western, Latin, Oriental and Arabic influences with Indian and Bengali folk elements; pioneered electronic rock and disco-rock fusion and experimental production techniques.</t>
+          <t>Synthesises Carnatic, Hindustani, Western classical and qawwali traditions with electronic production; introduced 7.1 surround sound to South Indian films.</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Three Filmfare Best Music Director awards (1983, 1984, 1995 posthumously)</t>
+          <t>Two Academy Awards and two Grammy Awards (Slumdog Millionaire); seven National Film Awards; Padma Shri (2000); Padma Bhushan (2010)</t>
         </is>
       </c>
       <c r="N3" s="19" t="inlineStr">
         <is>
-          <t>One of the most innovative Hindi film composers, closely associated with Kishore Kumar, Lata Mangeshkar, Asha Bhosle and Mohammed Rafi.</t>
+          <t>The most internationally celebrated Indian film composer, who transformed the sound of Hindi and Tamil film music from the 1990s.</t>
         </is>
       </c>
       <c r="O3" s="19" t="inlineStr">
         <is>
-          <t>Composed both films in which Aamir Khan appeared as a child.</t>
+          <t>Scored six Aamir Khan films, including three of his most acclaimed.</t>
         </is>
       </c>
       <c r="P3" s="17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>FILM-001; FILM-002</t>
+          <t>FILM-024; FILM-031; FILM-033; FILM-035; FILM-036; FILM-039</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>Yaadon Ki Baaraat (1973)</t>
+          <t>Lagaan (2001)</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Rahul Dev Burman, born in 1939, was the son of the composer S. D. Burman. He debuted as a music director with Chhote Nawab (1961) and broke through with Nasir Hussain's Teesri Manzil (1966), a major hit. Over the next two decades he became the defining sound of youthful Hindi cinema, writing scores for Hare Rama Hare Krishna, Yaadon Ki Baaraat, Sholay and Hum Kisise Kum Naheen, often with lyricists Majrooh Sultanpuri, Anand Bakshi and Gulzar and singers Kishore Kumar, Asha Bhosle, Lata Mangeshkar and Mohammed Rafi. His style drew on Western, Latin, Oriental and Arabic music, and he experimented with electronic rock, disco-rock fusion and unconventional recording methods. He married Asha Bhosle in 1980. He won three Filmfare Best Music Director awards, the last posthumously for 1942: A Love Story, released in the year of his death in 1994. His connection to Aamir Khan is limited to the child roles: he composed Yaadon Ki Baaraat, whose title song features eight-year-old Aamir as young Ratan, and Madhosh (1974), where Aamir played the younger Raj. Both films used Majrooh Sultanpuri's lyrics.</t>
+          <t>A. R. Rahman was born Arunachalam Shekhar Dileep Kumar in 1967, the son of Malayalam film composer R. K. Shekhar, and made his name composing advertising jingles before Mani Ratnam's Roja (1992) launched his film career. Bombay (1995) sold 15 million soundtrack copies, and Ram Gopal Varma's Rangeela (1995) was his Hindi breakthrough and his first film with Aamir Khan; it won him the Filmfare Best Music Director award. His music blends Carnatic, Hindustani, Western classical and qawwali influences with state-of-the-art production. The partnership with Aamir continued through Deepa Mehta's Earth, then Lagaan (2001), whose songs won the Filmfare and National Film Awards for music and whose lyricist Javed Akhtar also won both. Rahman scored Mangal Pandey: The Rising (2005) and Rang De Basanti (2006), winning another Filmfare award for the latter, and Ghajini (2008), the first Hindi film to cross ₹100 crore nett in India, whose soundtrack was the year's best-selling Bollywood album. His international career peaked with Slumdog Millionaire, which brought two Academy Awards and two Grammys. He has seven National Film Awards and received the Padma Shri in 2000 and the Padma Bhushan in 2010. Across six films he supplied the sound of Aamir Khan's move from romantic hero to epic and political roles.</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-076; SOURCE-004; SOURCE-005</t>
+          <t>SOURCE-094; SOURCE-030; SOURCE-035; SOURCE-039; SOURCE-041; SOURCE-042; SOURCE-045; SOURCE-071</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
@@ -21265,23 +21255,19 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Tahir Hussain</t>
+          <t>Anand–Milind</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Producer; director; screenwriter (Tahir Hussain Enterprises)</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="n">
-        <v>1938</v>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>2010</v>
-      </c>
+          <t>Music directors (song composers)</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1971–1993</t>
+          <t>1983–present</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -21291,66 +21277,70 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Born in Shahabad to a schoolteacher from a Pashtun zamindar family; younger brother and protégé of Nasir Hussain, who directed his first production.</t>
+          <t>Brothers Anand and Milind Srivastava, sons of the composer Chitragupt.</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Producer of Caravan (1971); directorial debut Tum Mere Ho (1990).</t>
+          <t>Ab Ayega Mazaa (1984); breakthrough with Qayamat Se Qayamat Tak (1988).</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Caravan (1971); Anamika; Madhosh (1974); Zakhmee (1975); Tum Mere Ho (1990); Hum Hain Rahi Pyar Ke (1993)</t>
+          <t>Ab Ayega Mazaa (1984); Jalwa (1987); Qayamat Se Qayamat Tak (1988); Baaghi: A Rebel for Love (1990); Dil (1990); Tum Mere Ho (1990); Deewana Mujh Sa Nahin (1990); Jawani Zindabad (1990); Daulat Ki Jung (1992)</t>
         </is>
       </c>
       <c r="K4" s="19" t="inlineStr">
         <is>
-          <t>Mainstream romance and family entertainment</t>
-        </is>
-      </c>
-      <c r="L4" s="19" t="n"/>
+          <t>Youthful romantic soundtracks for the late-1980s and early-1990s romance boom</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>Melodic, song-led romantic scores, frequently with lyricists Majrooh Sultanpuri and Sameer.</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Best Film and a National Film Award Special Mention (as producer) for Hum Hain Rahi Pyar Ke</t>
+          <t>Filmfare Best Music Director (Qayamat Se Qayamat Tak, 1989); Lata Mangeshkar Award, Government of Madhya Pradesh (2020)</t>
         </is>
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>A mainstream producer of the 1970s–1990s best known as father of Aamir Khan and Faisal Khan.</t>
+          <t>Composed for more than 200 Hindi films; their Qayamat Se Qayamat Tak songs defined the sound of the romantic revival.</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
         <is>
-          <t>Father. Produced Madhosh, directed Tum Mere Ho and produced Hum Hain Rahi Pyar Ke, which Aamir co-wrote.</t>
+          <t>The most frequent composers of Aamir Khan's early career, scoring six of his films between 1988 and 1992.</t>
         </is>
       </c>
       <c r="P4" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>FILM-002; FILM-008; FILM-019</t>
+          <t>FILM-004; FILM-008; FILM-009; FILM-010; FILM-011; FILM-014</t>
         </is>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Hum Hain Rahi Pyar Ke (1993)</t>
+          <t>Qayamat Se Qayamat Tak (1988)</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Mohammad Tahir Hussain Khan was born in 1938 in Shahabad. His elder brother, the filmmaker Nasir Hussain, brought him into the industry by directing his first production, Caravan (1971), which became a big hit. As a producer he went on to make Anamika, Madhosh and Zakhmee, the last of which gave the composer Bappi Lahiri early recognition. He was the father of Nikhat Khan, Farhat Khan, Aamir Khan and Faisal Khan, and his productions intersect with Aamir Khan's career at three points. Madhosh (1974) features the child Aamir as the younger version of its lead. Tahir Hussain made his directorial debut with Tum Mere Ho (1990), a snake-charmer fantasy starring Aamir and Juhi Chawla that failed at the box office but later gained a so-bad-it's-good following. His biggest success with his son was Hum Hain Rahi Pyar Ke (1993), directed by Mahesh Bhatt and co-written by Aamir; it won the Filmfare Best Film award and a National Film Award Special Mention shared by producer and director. He died in 2010. Much of this profile comes from a search-result summary rather than a fetched page, so dates and titles carry lower confidence.</t>
+          <t>Anand and Milind Srivastava are brothers and the sons of the veteran composer Chitragupt. Working as Anand–Milind from 1983, they debuted with Ab Ayega Mazaa (1984) and scored Jalwa (1987) before their breakthrough with Qayamat Se Qayamat Tak (1988). Its songs, including 'Papa Kehte Hain' and 'Ae Mere Humsafar', won them the Filmfare Best Music Director award and helped make the film a phenomenon. The success tied them closely to the romantic cycle it started and to Aamir Khan's early stardom. Within two years they had scored Tum Mere Ho, Indra Kumar's Dil (a Filmfare nomination and the year's highest-grossing film), Deewana Mujh Sa Nahin and Jawani Zindabad, followed by Daulat Ki Jung (1992). Their collaborations with Majrooh Sultanpuri (QSQT, Tum Mere Ho, Daulat Ki Jung) and Sameer (Dil, Deewana Mujh Sa Nahin) supplied the courtship songs central to these films' appeal. Their long career includes more than 200 Hindi films, and in 2020 the Madhya Pradesh government gave them the Lata Mangeshkar Award. The fetched biography gives no birth years or detailed account of their style, so the stylistic description here draws on the film records.</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-077; SOURCE-005; SOURCE-012; SOURCE-025; SOURCE-068; SOURCE-082</t>
+          <t>SOURCE-080; SOURCE-007; SOURCE-012; SOURCE-014; SOURCE-015; SOURCE-016; SOURCE-020</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -21362,89 +21352,91 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Ketan Mehta</t>
+          <t>Bappi Lahiri</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Music director (song composer)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
         <v>1952</v>
       </c>
-      <c r="E5" s="18" t="n"/>
+      <c r="E5" s="17" t="n">
+        <v>2022</v>
+      </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1975–present</t>
+          <t>1972–2022</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Hindi; Gujarati</t>
+          <t>Hindi; Bengali; Telugu; other Indian languages</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Born in Navsari, Gujarat; trained at the Film and Television Institute of India, then made documentaries for ISRO in Gujarat.</t>
+          <t>Born Alokesh Aparesh Lahiri in Siliguri to classical musicians; maternal uncle was Kishore Kumar.</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Bhavni Bhavai (1980), a Gujarati film that won the National Film Award for Best Feature Film on National Integration.</t>
+          <t>Bengali film Daadu (1972); recognition in Hindi with Tahir Hussain's Zakhmee (1975) and Chalte Chalte (1976).</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Bhavni Bhavai (1980); Holi (1984); Mirch Masala (1985); Maya Memsaab (1993); Sardar (1993); Mangal Pandey: The Rising (2005); Rang Rasiya (2014); Manjhi: The Mountain Man (2015)</t>
+          <t>Zakhmee (1975); Chalte Chalte (1976); Disco Dancer (1982); Namak Halaal (1982); Himmatwala (1983); Sharaabi (1984); Love Love Love (1989); Awwal Number (1990); Afsana Pyar Ka (1991)</t>
         </is>
       </c>
       <c r="K5" s="19" t="inlineStr">
         <is>
-          <t>Comedy, satire, romance, violence and rebellion; social and political history</t>
+          <t>Dance-floor pop and disco for mass entertainers</t>
         </is>
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>Rooted in parallel cinema, moving later to larger historical and biographical productions.</t>
+          <t>Pioneered synthesised disco in Indian film music, fusing Indian melody with international pop rhythms.</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Two National Film Awards; Ordre des Arts et des Lettres (2010)</t>
+          <t>Filmfare Best Music Director (Sharaabi, 1985); Filmfare Lifetime Achievement Award (2018); Guinness World Record (1986) for recording more than 180 songs in one year</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>A leading figure of Indian parallel cinema of the 1980s whose films addressed caste, gender and rebellion.</t>
+          <t>Transformed Hindi film music in the 1980s with electronic disco and a distinctive public image.</t>
         </is>
       </c>
       <c r="O5" s="19" t="inlineStr">
         <is>
-          <t>Gave Aamir Khan his first adult screen role in Holi and directed his comeback film Mangal Pandey: The Rising two decades later.</t>
+          <t>Scored five Aamir Khan films between 1989 and 1995, mostly lower-profile releases.</t>
         </is>
       </c>
       <c r="P5" s="17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>FILM-003; FILM-035</t>
+          <t>FILM-006; FILM-007; FILM-012; FILM-016; FILM-023</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>Holi (1984)</t>
+          <t>Afsana Pyar Ka (1991)</t>
         </is>
       </c>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>Ketan Mehta was born in 1952 in Navsari, Gujarat, and studied at the Film and Television Institute of India before making documentaries in Gujarat as a television producer for the Indian Space Research Organisation. His first feature, the Gujarati Bhavni Bhavai (1980), won the National Film Award for Best Feature Film on National Integration and established him in the parallel-cinema movement. Holi (1984), a largely improvised drama about a student revolt in a college hostel, followed; it gave Aamir Khan, credited as Aamir Hussain, his first adult role alongside Naseeruddin Shah, Om Puri and the future director Ashutosh Gowariker. Mirch Masala (1985) was nominated for the Golden Prize at the Moscow festival, and he went on to make Maya Memsaab and the biopic Sardar, which won a National Film Award. His interest in comedy, satire, romance, violence and rebellion carried into Mangal Pandey: The Rising (2005), a large historical production with Aamir Khan as the sepoy who helped spark the 1857 rebellion. The film marked Aamir's return after four years away, earned him a Filmfare nomination and drew political protests over its depiction of Pandey. Later films include Rang Rasiya and Manjhi: The Mountain Man. He is married to actress Deepa Sahi, a producer of Mangal Pandey.</t>
+          <t>Bappi Lahiri was born Alokesh Aparesh Lahiri in Siliguri in 1952 to parents who were classical musicians; the singer Kishore Kumar was his maternal uncle. He scored his first film, the Bengali Daadu, in 1972 and gained recognition in Hindi cinema with Zakhmee (1975), produced by Tahir Hussain, before national success with Chalte Chalte (1976). In the 1980s he became the dominant sound of mass entertainers, introducing synthesised disco with Disco Dancer, Namak Halaal, Himmatwala and Sharaabi, which won him the Filmfare Best Music Director award. He set a Guinness record in 1986 for recording more than 180 songs in a year and composed across Hindi, Bengali, Telugu, Kannada, Tamil and Marathi cinema. His work was also the subject of an international copyright case after portions of 'Thoda Resham Lagta Hai' appeared in a 2002 song by the American singer Truth Hurts. By the time he worked with Aamir Khan, the disco wave had peaked: he scored Love Love Love (1989), Dev Anand's Awwal Number (1990), Afsana Pyar Ka (1991), whose 'Tip Tip Tip Tip Baarish Shuru Ho Gayi' was a popular song, Isi Ka Naam Zindagi (1992) and Aatank Hi Aatank (1995). None became a major Aamir Khan hit. He received the Filmfare Lifetime Achievement Award in 2018 and died in Mumbai in 2022.</t>
         </is>
       </c>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-078; SOURCE-006; SOURCE-041</t>
+          <t>SOURCE-082; SOURCE-009; SOURCE-010; SOURCE-017; SOURCE-022; SOURCE-029</t>
         </is>
       </c>
       <c r="U5" s="5" t="inlineStr">
@@ -21453,7 +21445,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="184" customHeight="1">
+    <row r="6" ht="124" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
           <t>PERSON-005</t>
@@ -21461,89 +21453,83 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Mansoor Khan</t>
+          <t>Excel Entertainment</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Director; producer</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>1958</v>
-      </c>
+          <t>Production banner</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n"/>
       <c r="E6" s="18" t="n"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1988–2008</t>
+          <t>Founded 9 August 1999</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Hindi; streaming series</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Son of Nasir Hussain; educated at IIT Bombay, Cornell University and MIT.</t>
+          <t>Founded by Farhan Akhtar and Ritesh Sidhwani.</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Qayamat Se Qayamat Tak (1988), which won the National Film Award for Best Popular Film and the Filmfare Best Director award.</t>
+          <t>Dil Chahta Hai (2001).</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Qayamat Se Qayamat Tak (1988); Jo Jeeta Wohi Sikandar (1992); Akele Hum Akele Tum (1995); Josh (2000); Jaane Tu... Ya Jaane Na (2008, co-producer)</t>
+          <t>Dil Chahta Hai (2001); Lakshya (2004); Don (2006); Rock On!! (2008); Luck by Chance (2009); Zindagi Na Milegi Dobara (2011); Talaash (2012); Bombay Talkies (2013); Dil Dhadakne Do (2015); Gully Boy (2019); Mirzapur; Made in Heaven</t>
         </is>
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>Youthful romance, coming of age, marriage and ambition</t>
-        </is>
-      </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>Musical romances and Indian reworkings of Western films such as Breaking Away, Kramer vs. Kramer and West Side Story.</t>
-        </is>
-      </c>
+          <t>Contemporary urban stories and unusual characters</t>
+        </is>
+      </c>
+      <c r="L6" s="19" t="n"/>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Best Popular Film and Filmfare Best Director (Qayamat Se Qayamat Tak)</t>
+          <t>National Film Awards for Dil Chahta Hai and Rock On!!; Gully Boy selected as India's Academy Award entry</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>His debut is credited with bringing back the musical romantic genre in Hindi cinema.</t>
+          <t>Pioneered contemporary Hindi cinema and moved early into original streaming series.</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
         <is>
-          <t>Cousin. Directed Aamir Khan's breakthrough and two further films, and co-produced Jaane Tu... Ya Jaane Na with him.</t>
+          <t>Produced two films starring Aamir Khan, and three in which he appears as himself or as a voice.</t>
         </is>
       </c>
       <c r="P6" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>FILM-004; FILM-015; FILM-025</t>
+          <t>FILM-034; FILM-040; FILM-044; FILM-045; FILM-048</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Qayamat Se Qayamat Tak (1988)</t>
+          <t>Dil Chahta Hai (2001)</t>
         </is>
       </c>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>Mansoor Khan, born in 1958, is the son of filmmaker Nasir Hussain and a cousin of Aamir Khan. He studied at IIT Bombay, Cornell University and MIT before entering the family business. His directorial debut, Qayamat Se Qayamat Tak (1988), a tragic Romeo and Juliet-style romance produced and written by his father, launched Aamir Khan and Juhi Chawla. It is credited with reviving the musical romantic genre and won the National Film Award for Best Popular Film and the Filmfare Best Director award. He reunited with Aamir on Jo Jeeta Wohi Sikandar (1992), a campus cycling drama whose resemblance to Breaking Away was pointed out after release, and on Akele Hum Akele Tum (1995), a musical marriage drama loosely based on Kramer vs. Kramer. His last film as director, Josh (2000), drew on West Side Story; in 2008 he co-produced Jaane Tu... Ya Jaane Na with Aamir Khan. Across three films with Aamir, Mansoor Khan's work traces the actor's early persona from doomed teenage lover to underdog student to proud young husband. He later left the industry and settled in Coonoor, Tamil Nadu, to farm, and has published The Third Curve (2013), on the world economy, and One: The Story of the Ultimate Myth (2023).</t>
+          <t>Excel Entertainment was founded on 9 August 1999 by Farhan Akhtar and producer Ritesh Sidhwani. Its first film, Dil Chahta Hai (2001), starring Aamir Khan, Saif Ali Khan and Akshaye Khanna, won the National Film Award for Best Feature Film in Hindi, and the company became associated with contemporary urban storytelling through Lakshya, Don, Rock On!!, Zindagi Na Milegi Dobara and Gully Boy, India's Academy Award entry. It later moved into streaming series with Inside Edge, Mirzapur and Made in Heaven. Aamir Khan's work with the banner covers leading roles in Dil Chahta Hai and in Talaash (2012), co-produced with Aamir Khan Productions; appearances as himself in Luck by Chance (2009) and, among many stars, in a song of the anthology Bombay Talkies (2013); and the narrating voice of the dog Pluto in Dil Dhadakne Do (2015).</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-079; SOURCE-007; SOURCE-021; SOURCE-031</t>
+          <t>SOURCE-101; SOURCE-040; SOURCE-046; SOURCE-050; SOURCE-051; SOURCE-054; SOURCE-071</t>
         </is>
       </c>
       <c r="U6" s="5" t="inlineStr">
@@ -21560,19 +21546,21 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Anand–Milind</t>
+          <t>Kiran Rao</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Music directors (song composers)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="n"/>
+          <t>Director; writer; producer</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>1973</v>
+      </c>
       <c r="E7" s="18" t="n"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1983–present</t>
+          <t>2001–present</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -21582,65 +21570,65 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Brothers Anand and Milind Srivastava, sons of the composer Chitragupt.</t>
+          <t>Born in Bangalore and raised in Calcutta; studied economics at Sophia College and mass communication at Jamia Millia Islamia; assistant director on Lagaan, Monsoon Wedding and Swades.</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Ab Ayega Mazaa (1984); breakthrough with Qayamat Se Qayamat Tak (1988).</t>
+          <t>Directorial debut Dhobi Ghat (2011); earlier associate producer of Jaane Tu... Ya Jaane Na (2008).</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Ab Ayega Mazaa (1984); Jalwa (1987); Qayamat Se Qayamat Tak (1988); Baaghi: A Rebel for Love (1990); Dil (1990); Tum Mere Ho (1990); Deewana Mujh Sa Nahin (1990); Jawani Zindabad (1990); Daulat Ki Jung (1992)</t>
+          <t>Jaane Tu... Ya Jaane Na (2008, associate producer); Peepli Live (2010); Dhobi Ghat (2011); Delhi Belly (2011); Talaash (2012); Dangal (2016); Secret Superstar (2017); Laal Singh Chaddha (2022); Laapataa Ladies (2024)</t>
         </is>
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>Youthful romantic soundtracks for the late-1980s and early-1990s romance boom</t>
+          <t>Loneliness and class in the city; women's lives and small-town India</t>
         </is>
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
-          <t>Melodic, song-led romantic scores, frequently with lyricists Majrooh Sultanpuri and Sameer.</t>
+          <t>Intimate, observational filmmaking as director; producer of mainstream and independent films at Aamir Khan Productions.</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Best Music Director (Qayamat Se Qayamat Tak, 1989); Lata Mangeshkar Award, Government of Madhya Pradesh (2020)</t>
+          <t>Laapataa Ladies selected as India's entry for the 97th Academy Awards; Dhobi Ghat longlisted for a BAFTA</t>
         </is>
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Composed for more than 200 Hindi films; their Qayamat Se Qayamat Tak songs defined the sound of the romantic revival.</t>
+          <t>Chairperson of the Mumbai Film Festival (MAMI) from 2015 and co-founder of the Paani Foundation.</t>
         </is>
       </c>
       <c r="O7" s="19" t="inlineStr">
         <is>
-          <t>The most frequent composers of Aamir Khan's early career, scoring six of his films between 1988 and 1992.</t>
+          <t>Former wife (married December 2005, divorced July 2021); directed him in Dhobi Ghat and co-produced five more of his films.</t>
         </is>
       </c>
       <c r="P7" s="17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>FILM-004; FILM-008; FILM-009; FILM-010; FILM-011; FILM-014</t>
+          <t>FILM-042; FILM-043; FILM-049; FILM-050; FILM-053</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Qayamat Se Qayamat Tak (1988)</t>
+          <t>Dhobi Ghat (2011)</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
         <is>
-          <t>Anand and Milind Srivastava are brothers and the sons of the veteran composer Chitragupt. Working as Anand–Milind from 1983, they debuted with Ab Ayega Mazaa (1984) and scored Jalwa (1987) before their breakthrough with Qayamat Se Qayamat Tak (1988). Its songs, including 'Papa Kehte Hain' and 'Ae Mere Humsafar', won them the Filmfare Best Music Director award and helped make the film a phenomenon. The success tied them closely to the romantic cycle it started and to Aamir Khan's early stardom. Within two years they had scored Tum Mere Ho, Indra Kumar's Dil (a Filmfare nomination and the year's highest-grossing film), Deewana Mujh Sa Nahin and Jawani Zindabad, followed by Daulat Ki Jung (1992). Their collaborations with Majrooh Sultanpuri (QSQT, Tum Mere Ho, Daulat Ki Jung) and Sameer (Dil, Deewana Mujh Sa Nahin) supplied the courtship songs central to these films' appeal. Their long career includes more than 200 Hindi films, and in 2020 the Madhya Pradesh government gave them the Lata Mangeshkar Award. The fetched biography gives no birth years or detailed account of their style, so the stylistic description here draws on the film records.</t>
+          <t>Kiran Rao was born in Bangalore in 1973 and grew up in Calcutta. She studied economics at Sophia College and mass communication at Jamia Millia Islamia's AJK Mass Communication Research Centre before working as an assistant director on Lagaan, where she met Aamir Khan, and on Mira Nair's Monsoon Wedding and Ashutosh Gowariker's Swades. She also appears briefly in Dil Chahta Hai. She married Aamir Khan in December 2005; their son Azad was born in 2011, and they divorced in July 2021 while continuing to work together. At Aamir Khan Productions she was associate producer on Jaane Tu... Ya Jaane Na and producer of Peepli Live, Delhi Belly, Talaash, Dangal, Secret Superstar and Laal Singh Chaddha. Her directorial debut, Dhobi Ghat (2011), which she wrote, follows four Mumbai lives, with Aamir as Arun, a reclusive painter haunted by a former tenant's video diaries. It premiered at the Toronto festival, drew strong reviews and was longlisted for a BAFTA. Her second feature, Laapataa Ladies (2024), was India's entry for the 97th Academy Awards. She has chaired the Mumbai Film Festival since 2015 and co-founded the non-profit Paani Foundation in 2016.</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-080; SOURCE-007; SOURCE-012; SOURCE-014; SOURCE-015; SOURCE-016; SOURCE-020</t>
+          <t>SOURCE-113; SOURCE-048; SOURCE-049; SOURCE-050; SOURCE-055; SOURCE-056; SOURCE-059</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
@@ -21657,21 +21645,19 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Aditya Bhattacharya</t>
+          <t>Shankar–Ehsaan–Loy</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Director; writer; producer</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>1965</v>
-      </c>
+          <t>Music directors (songs and background score)</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n"/>
       <c r="E8" s="18" t="n"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1983–present</t>
+          <t>1997–present</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -21681,65 +21667,65 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Son of filmmaker Basu Bhattacharya and Rinki Bhattacharya, and grandson of Bimal Roy; began as an actor.</t>
+          <t>Shankar Mahadevan (vocalist trained in Indian classical music), Ehsaan Noorani (guitarist, Musicians Institute, Los Angeles) and Loy Mendonsa (keyboardist) came together through advertising jingles and Mumbai's non-film music scene.</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Raakh (1989), which won three National Film Awards and the BFJA Best Directorial Debut award but underperformed commercially.</t>
+          <t>First film Dus (begun 1997, left incomplete); mainstream entry with Mission Kashmir (2000); breakthrough with Dil Chahta Hai (2001).</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Raakh (1989); Dubai Return (2005); Bombay's Most Wanted (2012)</t>
+          <t>Mission Kashmir (2000); Dil Chahta Hai (2001); Kal Ho Naa Ho (2003); Bunty Aur Babli (2005); Don (2006); Taare Zameen Par (2007); Rock On!! (2008); Luck by Chance (2009); Zindagi Na Milegi Dobara (2011); Bhaag Milkha Bhaag (2013); Dil Dhadakne Do (2015); Sitaare Zameen Par (2025)</t>
         </is>
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
-          <t>Urban crime, violence and moral corrosion</t>
+          <t>Contemporary urban soundtracks; emotionally direct songs for coming-of-age and family stories</t>
         </is>
       </c>
       <c r="L8" s="19" t="inlineStr">
         <is>
-          <t>Stylised, low-budget urban noir; Raakh gave cinematographer Santosh Sivan and editor A. Sreekar Prasad their Bollywood debuts.</t>
+          <t>Fusion of Carnatic and Hindustani vocals with Western rock, jazz and electronic arrangement; Gulzar called it 'a sensible synthesis of popularity and class'.</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Three National Film Awards for Raakh (to its cast and crew); Bengal Film Journalists' Association Best Directorial Debut</t>
+          <t>National Film Award for Best Music Direction (Kal Ho Naa Ho); three Filmfare Best Music Director awards; Padma Shri to Shankar Mahadevan (2019)</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Raakh has a cult following as an early, dark counterpoint to the romantic films that made Aamir Khan a star.</t>
+          <t>Defined the sound of the post-2000 urban Hindi film.</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in the anti-hero role he filmed before Qayamat Se Qayamat Tak.</t>
+          <t>Scored five films featuring Aamir Khan, from Dil Chahta Hai to Sitaare Zameen Par.</t>
         </is>
       </c>
       <c r="P8" s="17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>FILM-005</t>
+          <t>FILM-034; FILM-038; FILM-040; FILM-048; FILM-055</t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>Raakh (1989)</t>
+          <t>Dil Chahta Hai (2001)</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>Aditya Bhattacharya, born in 1965, comes from one of Hindi cinema's best-known film families: he is the son of director Basu Bhattacharya and writer Rinki Bhattacharya, and the grandson of Bimal Roy. He started out as an actor before turning to direction. His debut, Raakh (1989), co-written with Nuzhat Khan, is a stylish crime drama in which Aamir Khan plays a young man who turns vigilante after his girlfriend is raped by a crime boss, guided by a disillusioned policeman played by Pankaj Kapur. Shot before Qayamat Se Qayamat Tak but released after it, the film underperformed commercially but won three National Film Awards: Best Supporting Actor for Pankaj Kapur, Best Editing for A. Sreekar Prasad, and a Special Mention for Aamir Khan covering both his 1988–89 performances. Bhattacharya won the Bengal Film Journalists' Association award for Best Directorial Debut, and the film's photography marked Santosh Sivan's Bollywood debut. Raakh has since built a cult following. Bhattacharya's later films include Dubai Return (2005), with Irrfan Khan and Divya Dutta, which premiered at IFFI Goa, and Bombay's Most Wanted (2012). He divides his time between Barcelona and Mumbai.</t>
+          <t>Shankar Mahadevan, Ehsaan Noorani and Loy Mendonsa came from Mumbai's rock, blues, jazz and pop scene. Ehsaan and Loy began working together around 1989 composing advertising jingles, and Shankar joined them through composer Ranjit Barot. Their first film, Mukul Anand's Dus, was left incomplete after the director's death; Mission Kashmir (2000) brought them into the mainstream. Their breakthrough was Farhan Akhtar's Dil Chahta Hai (2001), with Aamir Khan, whose songs won them Filmfare's R. D. Burman Award for New Music Talent and became part of the film's cult status. The trio fuse Shankar's Carnatic and Hindustani vocals with Ehsaan's rock guitar and Loy's electronic arrangement, a mix Gulzar called 'a sensible synthesis of popularity and class'. They won the National Film Award for Kal Ho Naa Ho and Filmfare awards for Bunty Aur Babli and 2 States. With Aamir Khan they also scored Taare Zameen Par (2007), whose song 'Maa', sung by Shankar Mahadevan, won National Film Awards for playback and lyrics, as well as Luck by Chance, Dil Dhadakne Do and, nearly two decades after TZP, the songs of Sitaare Zameen Par (2025). Shankar Mahadevan received the Padma Shri in 2019.</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-081; SOURCE-008; SOURCE-067</t>
+          <t>SOURCE-102; SOURCE-040; SOURCE-044; SOURCE-046; SOURCE-054; SOURCE-061; SOURCE-070; SOURCE-072</t>
         </is>
       </c>
       <c r="U8" s="5" t="inlineStr">
@@ -21748,15 +21734,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="184" customHeight="1">
+    <row r="9" ht="154" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PERSON-008</t>
+          <t>PERSON-009</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bappi Lahiri</t>
+          <t>Anu Malik</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -21765,82 +21751,80 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1952</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>2022</v>
-      </c>
+        <v>1960</v>
+      </c>
+      <c r="E9" s="18" t="n"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1972–2022</t>
+          <t>1974–present</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Hindi; Bengali; Telugu; other Indian languages</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Born Alokesh Aparesh Lahiri in Siliguri to classical musicians; maternal uncle was Kishore Kumar.</t>
+          <t>Son of composer Sardar Malik; brother of composer Daboo Malik and uncle of Amaal Mallik and Armaan Malik.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Bengali film Daadu (1972); recognition in Hindi with Tahir Hussain's Zakhmee (1975) and Chalte Chalte (1976).</t>
+          <t>A song for Hunterwali 77 (1975); first full soundtrack Poonam (1981); breakthrough with Mard (1985) and especially Baazigar (1993).</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Zakhmee (1975); Chalte Chalte (1976); Disco Dancer (1982); Namak Halaal (1982); Himmatwala (1983); Sharaabi (1984); Love Love Love (1989); Awwal Number (1990); Afsana Pyar Ka (1991)</t>
+          <t>Mard (1985); Baazigar (1993); Main Khiladi Tu Anari (1994); Baazi (1995); Akele Hum Akele Tum (1995); Ishq (1997); Border (1997); Mela (2000); Refugee (2000); Main Hoon Na (2004); Umrao Jaan (2006)</t>
         </is>
       </c>
       <c r="K9" s="19" t="inlineStr">
         <is>
-          <t>Dance-floor pop and disco for mass entertainers</t>
+          <t>Popular romantic and dance songs for mainstream entertainers</t>
         </is>
       </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
-          <t>Pioneered synthesised disco in Indian film music, fusing Indian melody with international pop rhythms.</t>
+          <t>Melodious, classically based compositions with prominent tabla; repeatedly accused of borrowing melodies.</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Best Music Director (Sharaabi, 1985); Filmfare Lifetime Achievement Award (2018); Guinness World Record (1986) for recording more than 180 songs in one year</t>
+          <t>National Film Award for Best Music Direction (Refugee, 2000); Filmfare Best Music Director (Baazigar; Main Hoon Na); 14 Filmfare nominations</t>
         </is>
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Transformed Hindi film music in the 1980s with electronic disco and a distinctive public image.</t>
+          <t>One of the most commercially successful Hindi composers of the 1990s and 2000s and a long-running Indian Idol judge.</t>
         </is>
       </c>
       <c r="O9" s="19" t="inlineStr">
         <is>
-          <t>Scored five Aamir Khan films between 1989 and 1995, mostly lower-profile releases.</t>
+          <t>Scored four Aamir Khan films between 1995 and 2000.</t>
         </is>
       </c>
       <c r="P9" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>FILM-006; FILM-007; FILM-012; FILM-016; FILM-023</t>
+          <t>FILM-022; FILM-025; FILM-027; FILM-032</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Afsana Pyar Ka (1991)</t>
+          <t>Akele Hum Akele Tum (1995)</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>Bappi Lahiri was born Alokesh Aparesh Lahiri in Siliguri in 1952 to parents who were classical musicians; the singer Kishore Kumar was his maternal uncle. He scored his first film, the Bengali Daadu, in 1972 and gained recognition in Hindi cinema with Zakhmee (1975), produced by Tahir Hussain, before national success with Chalte Chalte (1976). In the 1980s he became the dominant sound of mass entertainers, introducing synthesised disco with Disco Dancer, Namak Halaal, Himmatwala and Sharaabi, which won him the Filmfare Best Music Director award. He set a Guinness record in 1986 for recording more than 180 songs in a year and composed across Hindi, Bengali, Telugu, Kannada, Tamil and Marathi cinema. His work was also the subject of an international copyright case after portions of 'Thoda Resham Lagta Hai' appeared in a 2002 song by the American singer Truth Hurts. By the time he worked with Aamir Khan, the disco wave had peaked: he scored Love Love Love (1989), Dev Anand's Awwal Number (1990), Afsana Pyar Ka (1991), whose 'Tip Tip Tip Tip Baarish Shuru Ho Gayi' was a popular song, Isi Ka Naam Zindagi (1992) and Aatank Hi Aatank (1995). None became a major Aamir Khan hit. He received the Filmfare Lifetime Achievement Award in 2018 and died in Mumbai in 2022.</t>
+          <t>Anu Malik, born in 1960, is the son of composer Sardar Malik. He composed his first film song as a teenager for Hunterwali 77 (1975), scored his first full soundtrack with Poonam (1981) and broke through with Mard (1985). Baazigar (1993) established him among the top music directors and won him a Filmfare award. His output combined melodious, classically inflected tunes with dance numbers, alongside repeated accusations of plagiarism. His four films with Aamir Khan came at the height of his popularity. He composed the songs for Ashutosh Gowariker's Baazi (1995) and Mansoor Khan's musical Akele Hum Akele Tum (1995), in which Aamir played an aspiring playback singer; the soundtrack sold about 2.5 million units and 'Raja Ko Rani Se' earned several Filmfare nominations. His songs for Indra Kumar's Ishq (1997) sold about 3 million units, and he was one of three composers on Dharmesh Darshan's Mela (2000). Malik later won the National Film Award for Refugee (2000) and a second Filmfare award for Main Hoon Na (2004), and judged Indian Idol from 2004 to 2018.</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-082; SOURCE-009; SOURCE-010; SOURCE-017; SOURCE-022; SOURCE-029</t>
+          <t>SOURCE-092; SOURCE-028; SOURCE-031; SOURCE-033; SOURCE-038</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
@@ -21852,24 +21836,26 @@
     <row r="10" ht="184" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>PERSON-009</t>
+          <t>PERSON-010</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Indra Kumar</t>
+          <t>Farhan Akhtar</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Director; producer (Maruti International)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n"/>
+          <t>Director; writer; producer; actor</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>1974</v>
+      </c>
       <c r="E10" s="18" t="n"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1985–present (producer); 1990–present (director)</t>
+          <t>2001–present</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -21879,65 +21865,65 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Worked as a producer before directing, with Mohabbat (1985) and Kasam (1988).</t>
+          <t>Son of screenwriters Javed Akhtar and Honey Irani; apprenticed on Lamhe (1991) at 17, assisted on Himalay Putra (1997) and worked in advertising.</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Dil (1990), a major commercial success and the year's highest-grossing Hindi film.</t>
+          <t>Dil Chahta Hai (2001), his directorial debut and Excel Entertainment's first film.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Dil (1990); Beta (1992); Raja (1995); Ishq (1997); Mann (1999); Masti (2004); Dhamaal series (2007–2019); Total Dhamaal (2019)</t>
+          <t>Dil Chahta Hai (2001); Lakshya (2004); Don (2006); Rock On!! (2008); Luck by Chance (2009); Don 2 (2011); Zindagi Na Milegi Dobara (2011); Talaash (2012); Bhaag Milkha Bhaag (2013); Dil Dhadakne Do (2015)</t>
         </is>
       </c>
       <c r="K10" s="19" t="inlineStr">
         <is>
-          <t>Family melodrama and romance in the 1990s; broad ensemble comedy later</t>
+          <t>Urban friendships, self-discovery and contemporary relationships</t>
         </is>
       </c>
       <c r="L10" s="19" t="inlineStr">
         <is>
-          <t>Crowd-pleasing melodrama built around hit soundtracks, later shifting to comedy franchises.</t>
+          <t>Realistic, conversational urban storytelling credited with starting a new wave in Hindi cinema.</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Five Filmfare nominations, including Best Director for Beta and Raja</t>
+          <t>National Film Awards for Best Hindi Film (Dil Chahta Hai; Rock On!!); Filmfare Best Actor (Bhaag Milkha Bhaag); Filmfare Best Screenplay (Dil Chahta Hai)</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Delivered major romantic hits in the early 1990s and later popularised long-running Hindi comedy franchises.</t>
+          <t>Co-founder of Excel Entertainment and a key figure in the modernisation of Hindi cinema after 2000.</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
         <is>
-          <t>Directed three Aamir Khan films, beginning with Dil, the actor's biggest early hit after QSQT.</t>
+          <t>Directed Dil Chahta Hai and co-produced three further films featuring Aamir Khan, writing the dialogue for Talaash and Dil Dhadakne Do.</t>
         </is>
       </c>
       <c r="P10" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>FILM-009; FILM-027; FILM-030</t>
+          <t>FILM-034; FILM-040; FILM-044; FILM-048</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Dil (1990)</t>
+          <t>Dil Chahta Hai (2001)</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>Indra Kumar began as a producer with Mohabbat (1985) and Kasam (1988) before directing his first film, Dil (1990), under his banner Maruti International with Ashok Thakeria. Starring Aamir Khan and Madhuri Dixit as rival students who marry against their fathers' wishes, Dil became the highest-grossing Hindi film of the year, won Madhuri Dixit her first Filmfare Best Actress award and brought Aamir a Best Actor nomination. Indra Kumar consolidated his reputation with Beta (1992) and Raja (1995), both of which earned him Filmfare Best Director nominations. He reunited with Aamir on Ishq (1997), a broad romantic comedy pairing Aamir with Juhi Chawla and Ajay Devgn with Kajol against two scheming fathers; it was the third-highest-grossing Hindi film of 1997. Their third film, Mann (1999), a remake of An Affair to Remember with Manisha Koirala, is recorded inconsistently: the film's own Wikipedia article calls it profitable, while his biography calls it a commercial failure. After 2000 he moved decisively to ensemble comedy with Masti (2004) and the Dhamaal franchise, whose Total Dhamaal (2019) became his highest-grossing release. His three films with Aamir Khan span the class-conflict romance, the masala romantic comedy and the tearjerker.</t>
+          <t>Farhan Akhtar, born in 1974, is the son of Javed Akhtar and Honey Irani and the brother of director Zoya Akhtar. He apprenticed on Yash Chopra's Lamhe at 17, assisted on Himalay Putra and spent about three years in advertising before founding Excel Entertainment with Ritesh Sidhwani in 1999. His directorial debut, Dil Chahta Hai (2001), which he also wrote, followed three affluent Mumbai friends; Aamir Khan played Akash, the flippant joker who falls for an engaged woman. It was acclaimed for its realistic depiction of urban youth, won the National Film Award for Best Hindi Film and seven Filmfare awards, including Best Screenplay for Akhtar, and is credited with launching a new wave of urban Hindi cinema. Akhtar went on to direct Lakshya and the Don films, and to act, beginning with Rock On!! (2008) and winning the Filmfare Best Actor award for Bhaag Milkha Bhaag. As producer he backed three more projects with Aamir: Zoya Akhtar's Luck by Chance (2009), in which Aamir appears as himself; Reema Kagti's Talaash (2012), co-produced with Aamir Khan Productions and with dialogue by Akhtar; and Dil Dhadakne Do (2015), where Aamir voices the narrating dog and Akhtar wrote the dialogue and appears on screen.</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-083; SOURCE-014; SOURCE-033; SOURCE-037</t>
+          <t>SOURCE-100; SOURCE-040; SOURCE-046; SOURCE-050; SOURCE-054; SOURCE-070</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr">
@@ -21949,26 +21935,24 @@
     <row r="11" ht="184" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PERSON-010</t>
+          <t>PERSON-011</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Mahesh Bhatt</t>
+          <t>Jatin–Lalit</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Director; producer; screenwriter</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>1948</v>
-      </c>
+          <t>Music directors (song composers)</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n"/>
       <c r="E11" s="18" t="n"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>1974–present (director until 1999)</t>
+          <t>1991–2006 (as a duo)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -21978,65 +21962,65 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Son of director Nanabhai Bhatt and Shirin Mohammad Ali; assistant director to Raj Khosla.</t>
+          <t>Brothers Jatin and Lalit Pandit; nephews of classical vocalist Pandit Jasraj; their sisters include actresses Sulakshana and Vijayta Pandit.</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Manzilein Aur Bhi Hain (1974); breakthrough with Arth (1982); Saaransh (1984) was India's Academy Award submission.</t>
+          <t>Yaara Dildara (1991); breakthrough with 'Pehla Nasha' from Jo Jeeta Wohi Sikandar (1992).</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Arth (1982); Saaransh (1984); Aashiqui (1990); Dil Hai Ke Manta Nahin (1991); Sadak (1991); Sir (1993); Hum Hain Rahi Pyar Ke (1993); Tamanna (1997); Zakhm (1998)</t>
+          <t>Jo Jeeta Wohi Sikandar (1992); Khiladi (1992); Dilwale Dulhania Le Jayenge (1995); Kuch Kuch Hota Hai (1998); Ghulam (1998); Sarfarosh (1999); Kabhi Khushi Kabhie Gham (2001); Fanaa (2006)</t>
         </is>
       </c>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>Autobiographical relationships, illegitimacy and infidelity; later commercial romance</t>
+          <t>Melodious romantic songs for the 1990s–2000s love story</t>
         </is>
       </c>
       <c r="L11" s="19" t="inlineStr">
         <is>
-          <t>Unconventional narratives and bold themes, balanced in the 1990s with music-driven commercial films.</t>
+          <t>Melody-first romantic scores influenced by R. D. Burman's approach.</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Five National Film Awards (including for Hum Hain Rahi Pyar Ke, Tamanna and Zakhm); four Filmfare Awards</t>
+          <t>Twelve Filmfare nominations without a win, a record</t>
         </is>
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>One of the most prominent Hindi filmmakers of the 1980s and 1990s; co-founded Vishesh Films and mentored many actors.</t>
+          <t>Composers of several of the most popular Hindi romantic soundtracks of the 1990s; split in 2006.</t>
         </is>
       </c>
       <c r="O11" s="19" t="inlineStr">
         <is>
-          <t>Directed two of Aamir Khan's most successful romantic comedies; Aamir co-wrote the second.</t>
+          <t>Scored four Aamir Khan films, including 'Aati Kya Khandala', which Aamir sang in Ghulam.</t>
         </is>
       </c>
       <c r="P11" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>FILM-013; FILM-019</t>
+          <t>FILM-015; FILM-028; FILM-029; FILM-037</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Hum Hain Rahi Pyar Ke (1993)</t>
+          <t>Jo Jeeta Wohi Sikandar (1992)</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>Mahesh Bhatt was born in 1948 to director Nanabhai Bhatt and Shirin Mohammad Ali, and entered films as an assistant to Raj Khosla. He directed his first film, Manzilein Aur Bhi Hain, at 26, and made his name with the autobiographical Arth (1982) and Saaransh (1984), India's submission for the Academy Award. With his brother Mukesh he co-founded Vishesh Films in 1986–87, and in the 1990s he moved toward commercial romance with Aashiqui, Sadak and Dil Hai Ke Manta Nahin (1991). That film, a remake of It Happened One Night, cast Aamir Khan as a jobless journalist opposite Mahesh's daughter Pooja Bhatt; its success boosted her career and its soundtrack was widely praised. Two years later Bhatt directed Aamir in Hum Hain Rahi Pyar Ke (1993), a Houseboat-inspired family romance for which Aamir co-wrote the screenplay and dialogue with Robin Bhatt. It won the Filmfare Best Film award and Best Actress for Juhi Chawla, and a National Film Award Special Mention for Bhatt and producer Tahir Hussain. Bhatt stopped directing after Kartoos (1999), continuing as a writer and producer; Vishesh Films produced hits such as Raaz and Murder. He has won five National Film Awards and four Filmfare awards.</t>
+          <t>Jatin and Lalit Pandit, nephews of the classical vocalist Pandit Jasraj and brothers of actresses Sulakshana and Vijayta Pandit, began composing together with Yaara Dildara (1991). Their breakthrough was Mansoor Khan's Jo Jeeta Wohi Sikandar (1992), whose 'Pehla Nasha' brought their first Filmfare nomination and became one of the defining romantic songs of Aamir Khan's early career. In the following decade they scored landmark soundtracks including Dilwale Dulhania Le Jayenge, Kuch Kuch Hota Hai and Kabhi Khushi Kabhie Gham, with melodious compositions influenced by R. D. Burman. Their further collaborations with Aamir cover his changing roles: Ghulam (1998), including the playful 'Aati Kya Khandala', sung by Aamir himself and nominated for Filmfare Best Male Playback; Sarfarosh (1999), with 'Is Deewane Ladke Ko' and 'Jo Haal Dil Ka'; and Fanaa (2006), whose songs and Filmfare Best Music Director nomination came in the duo's final year. Despite their popularity they hold the record for most Filmfare nominations without a win. The brothers split in 2006 for personal reasons and reunited for a concert in February 2020. Their brother-in-law Aadesh Shrivastava composed the background score of Baazi.</t>
         </is>
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-084; SOURCE-018; SOURCE-025; SOURCE-068</t>
+          <t>SOURCE-088; SOURCE-021; SOURCE-034; SOURCE-036; SOURCE-043; SOURCE-028</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
@@ -22045,29 +22029,27 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="139" customHeight="1">
+    <row r="12" ht="184" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>PERSON-011</t>
+          <t>PERSON-012</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Mukesh Bhatt (Vishesh Films)</t>
+          <t>Nadeem–Shravan</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Producer; production banner</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>1952</v>
-      </c>
+          <t>Music directors (song composers)</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n"/>
       <c r="E12" s="18" t="n"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>1990–present</t>
+          <t>1977–2005; 2009; 2016–present</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -22077,61 +22059,65 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Son of director-producer Nanabhai Bhatt; younger brother of Mahesh Bhatt, with whom he co-founded Vishesh Films.</t>
+          <t>Nadeem Akhtar Saifi (born 1954) and Shravan Kumar Rathod (1954–2021) met in 1973; their first film was the Bhojpuri Dangal (1977).</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Vishesh Films' early 1990s productions, including Dil Hai Ke Manta Nahin (1991).</t>
+          <t>First Hindi film Maine Jeena Seekh Liya (1981); breakthrough with Aashiqui (1990).</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Dil Hai Ke Manta Nahin (1991); Ghulam (1998); Raaz (2002); Murder (2004); Jannat (2008); Aashiqui 2 (2013)</t>
+          <t>Aashiqui (1990); Saajan (1991); Dil Hai Ke Manta Nahin (1991); Deewana (1992); Hum Hain Rahi Pyar Ke (1993); Raja Hindustani (1996); Pardes (1997); Dhadkan (2000)</t>
         </is>
       </c>
       <c r="K12" s="19" t="inlineStr">
         <is>
-          <t>Music-led romances, thrillers and horror franchises</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="n"/>
+          <t>Romantic ballads and filmi ghazals for the 1990s love story</t>
+        </is>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>Strong Hindustani classical influence, with bansuri, sitar and shehnai prominent in filmi-ghazal melodies.</t>
+        </is>
+      </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Filmfare nominations (1992, 1999, 2003)</t>
+          <t>Four Filmfare Best Music Director awards (1991, 1992, 1993, 1997); Screen Awards for Raja Hindustani and Pardes</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Built Vishesh Films into a consistently profitable mid-budget studio; took sole control after the brothers split in 2021.</t>
+          <t>Among the best-selling Hindi film composers; Aashiqui sold 20 million units and Raja Hindustani 11 million, helping establish T-Series.</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
         <is>
-          <t>Produced two Aamir Khan films a decade apart.</t>
+          <t>Scored four Aamir Khan films, including his biggest 1990s romantic hit, Raja Hindustani.</t>
         </is>
       </c>
       <c r="P12" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>FILM-013; FILM-028</t>
+          <t>FILM-013; FILM-017; FILM-019; FILM-026</t>
         </is>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Ghulam (1998)</t>
+          <t>Raja Hindustani (1996)</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>Mukesh Bhatt, born in 1952, is the son of Nanabhai Bhatt and the younger brother of Mahesh Bhatt. The brothers founded Vishesh Films (1986 according to Mukesh Bhatt's article, 1987 according to Mahesh Bhatt's), and Mukesh ran the business side of a banner that went on to produce more than twenty hits. With T-Series founder Gulshan Kumar he produced Dil Hai Ke Manta Nahin (1991), Mahesh Bhatt's romantic comedy with Aamir Khan and Pooja Bhatt, which was nominated for Filmfare Best Film. He produced Ghulam (1998), directed by Vikram Bhatt and adapted from On the Waterfront, in which Aamir played a Mumbai boxer who stands up to a local gangster; it was a hit and its train-race sequence won Filmfare's Best Scene award. In the 2000s the banner became known for Raaz, Murder, Jannat and Aashiqui 2. After a professional split announced in May 2021, Mukesh Bhatt took sole control of Vishesh Films.</t>
+          <t>Nadeem Akhtar Saifi and Shravan Kumar Rathod met in 1973 and began composing together with the Bhojpuri film Dangal (1977) and the Hindi Maine Jeena Seekh Liya (1981). Their breakthrough came with Aashiqui (1990), given to them by T-Series founder Gulshan Kumar; its soundtrack sold 20 million units, reported as the best-selling Bollywood album of all time. Through the 1990s they dominated romantic film music with Saajan, Deewana, Pardes and Dhadkan, blending Hindustani classical colours such as bansuri, sitar and shehnai with filmi-ghazal melody, and won four Filmfare Best Music Director awards. Their collaborations with Aamir Khan began with Dil Hai Ke Manta Nahin (1991), whose title song won Anuradha Paudwal a Filmfare award, and continued with Damini (1993), in which Aamir makes a cameo, and Hum Hain Rahi Pyar Ke (1993). Their peak with him was Raja Hindustani (1996): its songs, including 'Pardesi Pardesi', won the Filmfare and Screen music awards, and the album sold 11 million copies. After Gulshan Kumar's murder in 1997, police accused Nadeem of involvement; he was exonerated by four courts, including the House of Lords, and lived abroad, which disrupted the partnership. Shravan Rathod died in 2021.</t>
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-085; SOURCE-084; SOURCE-018; SOURCE-034</t>
+          <t>SOURCE-086; SOURCE-018; SOURCE-023; SOURCE-025; SOURCE-032</t>
         </is>
       </c>
       <c r="U12" s="5" t="inlineStr">
@@ -22143,24 +22129,28 @@
     <row r="13" ht="184" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PERSON-012</t>
+          <t>PERSON-013</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Nadeem–Shravan</t>
+          <t>Nasir Hussain</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Music directors (song composers)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
+          <t>Director; producer; screenwriter (Nasir Hussain Films)</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>1926</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>2002</v>
+      </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>1977–2005; 2009; 2016–present</t>
+          <t>1948–1996</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -22170,42 +22160,42 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Nadeem Akhtar Saifi (born 1954) and Shravan Kumar Rathod (1954–2021) met in 1973; their first film was the Bhojpuri Dangal (1977).</t>
+          <t>Born in Bhopal State to a schoolteacher from a Pashtun zamindar family; joined Filmistan as a writer in 1948.</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>First Hindi film Maine Jeena Seekh Liya (1981); breakthrough with Aashiqui (1990).</t>
+          <t>Writer on Anarkali (1953), Munimji (1955) and Paying Guest (1957); directorial debut Tumsa Nahin Dekha (1957), which made Shammi Kapoor a star.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Aashiqui (1990); Saajan (1991); Dil Hai Ke Manta Nahin (1991); Deewana (1992); Hum Hain Rahi Pyar Ke (1993); Raja Hindustani (1996); Pardes (1997); Dhadkan (2000)</t>
+          <t>Tumsa Nahin Dekha (1957); Dil Deke Dekho (1959); Jab Pyar Kisi Se Hota Hai (1961); Teesri Manzil (1966); Caravan (1971); Yaadon Ki Baaraat (1973); Hum Kisise Kum Naheen (1977); Qayamat Se Qayamat Tak (1988); Jo Jeeta Wohi Sikandar (1992)</t>
         </is>
       </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
-          <t>Romantic ballads and filmi ghazals for the 1990s love story</t>
+          <t>Musical romances; youthful love against family obstacles; separated-family masala plots</t>
         </is>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
-          <t>Strong Hindustani classical influence, with bansuri, sitar and shehnai prominent in filmi-ghazal melodies.</t>
+          <t>Song-driven popular entertainment; Yaadon Ki Baaraat is identified as the first masala film, and Qayamat Se Qayamat Tak set the template for 1990s musical romance.</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Four Filmfare Best Music Director awards (1991, 1992, 1993, 1997); Screen Awards for Raja Hindustani and Pardes</t>
+          <t>Filmfare Best Film and Best Screenplay (Qayamat Se Qayamat Tak); Filmfare Best Film (Jo Jeeta Wohi Sikandar); Filmfare Special Award (1996)</t>
         </is>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Among the best-selling Hindi film composers; Aashiqui sold 20 million units and Raja Hindustani 11 million, helping establish T-Series.</t>
+          <t>Described as a major trendsetter in Hindi cinema; Javed Akhtar rated him the most underrated producer-director of his generation.</t>
         </is>
       </c>
       <c r="O13" s="19" t="inlineStr">
         <is>
-          <t>Scored four Aamir Khan films, including his biggest 1990s romantic hit, Raja Hindustani.</t>
+          <t>Uncle. Cast him as a child in Yaadon Ki Baaraat and produced and wrote the films that made him a star.</t>
         </is>
       </c>
       <c r="P13" s="17" t="n">
@@ -22213,22 +22203,22 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>FILM-013; FILM-017; FILM-019; FILM-026</t>
+          <t>FILM-001; FILM-004; FILM-015; FILM-025</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Raja Hindustani (1996)</t>
+          <t>Qayamat Se Qayamat Tak (1988)</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>Nadeem Akhtar Saifi and Shravan Kumar Rathod met in 1973 and began composing together with the Bhojpuri film Dangal (1977) and the Hindi Maine Jeena Seekh Liya (1981). Their breakthrough came with Aashiqui (1990), given to them by T-Series founder Gulshan Kumar; its soundtrack sold 20 million units, reported as the best-selling Bollywood album of all time. Through the 1990s they dominated romantic film music with Saajan, Deewana, Pardes and Dhadkan, blending Hindustani classical colours such as bansuri, sitar and shehnai with filmi-ghazal melody, and won four Filmfare Best Music Director awards. Their collaborations with Aamir Khan began with Dil Hai Ke Manta Nahin (1991), whose title song won Anuradha Paudwal a Filmfare award, and continued with Damini (1993), in which Aamir makes a cameo, and Hum Hain Rahi Pyar Ke (1993). Their peak with him was Raja Hindustani (1996): its songs, including 'Pardesi Pardesi', won the Filmfare and Screen music awards, and the album sold 11 million copies. After Gulshan Kumar's murder in 1997, police accused Nadeem of involvement; he was exonerated by four courts, including the House of Lords, and lived abroad, which disrupted the partnership. Shravan Rathod died in 2021.</t>
+          <t>Nasir Hussain was born in 1926 in Bhopal State and joined Filmistan as a writer in 1948, writing hits such as Anarkali, Munimji and Paying Guest. His directorial debut, Tumsa Nahin Dekha (1957), made Shammi Kapoor a star, and a run of musical romances followed, including Dil Deke Dekho and Jab Pyar Kisi Se Hota Hai. Under his own banner he made Caravan (1971) and Yaadon Ki Baaraat (1973), a lost-and-found family saga identified as the first quintessential masala film, and Hum Kisise Kum Naheen (1977). His later films as director failed, and his son Mansoor Khan took over the company. Together they reinvented the romantic musical with Qayamat Se Qayamat Tak (1988), which Nasir Hussain wrote and produced; it won the Filmfare awards for Best Film and Best Screenplay and set the template for Hindi romance in the 1990s. Jo Jeeta Wohi Sikandar (1992) brought another Filmfare Best Film award. For Aamir Khan, his nephew, Nasir Hussain was a formative figure: the eight-year-old appeared as young Ratan in the title song of Yaadon Ki Baaraat, and fifteen years later he launched Aamir as a romantic lead. He also wrote dialogue for Akele Hum Akele Tum (1995). He died in Mumbai on 13 March 2002.</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-086; SOURCE-018; SOURCE-023; SOURCE-025; SOURCE-032</t>
+          <t>SOURCE-075; SOURCE-004; SOURCE-007; SOURCE-021; SOURCE-031</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr">
@@ -22240,7 +22230,7 @@
     <row r="14" ht="109" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>PERSON-013</t>
+          <t>PERSON-016</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -22335,69 +22325,71 @@
     <row r="15" ht="184" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PERSON-014</t>
+          <t>PERSON-017</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Jatin–Lalit</t>
+          <t>Zoya Akhtar</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Music directors (song composers)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n"/>
+          <t>Director; writer</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>1972</v>
+      </c>
       <c r="E15" s="18" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>1991–2006 (as a duo)</t>
+          <t>2009–present</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Hindi; streaming series</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Brothers Jatin and Lalit Pandit; nephews of classical vocalist Pandit Jasraj; their sisters include actresses Sulakshana and Vijayta Pandit.</t>
+          <t>Daughter of Javed Akhtar and Honey Irani; trained at NYU's Tisch School of the Arts and assisted Mira Nair, Tony Gerber and Dev Benegal.</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Yaara Dildara (1991); breakthrough with 'Pehla Nasha' from Jo Jeeta Wohi Sikandar (1992).</t>
+          <t>Luck by Chance (2009), which won the Filmfare Best Debut Director award.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Jo Jeeta Wohi Sikandar (1992); Khiladi (1992); Dilwale Dulhania Le Jayenge (1995); Kuch Kuch Hota Hai (1998); Ghulam (1998); Sarfarosh (1999); Kabhi Khushi Kabhie Gham (2001); Fanaa (2006)</t>
+          <t>Luck by Chance (2009); Zindagi Na Milegi Dobara (2011); Talaash (2012, co-writer); Bombay Talkies (2013, segment); Dil Dhadakne Do (2015); Gully Boy (2019); Made in Heaven (2019–2023); The Archies (2023)</t>
         </is>
       </c>
       <c r="K15" s="19" t="inlineStr">
         <is>
-          <t>Melodious romantic songs for the 1990s–2000s love story</t>
+          <t>Privileged families and friendships under strain; the film industry; class and aspiration</t>
         </is>
       </c>
       <c r="L15" s="19" t="inlineStr">
         <is>
-          <t>Melody-first romantic scores influenced by R. D. Burman's approach.</t>
+          <t>Observational ensemble drama with wry humour, often co-written with Reema Kagti.</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Twelve Filmfare nominations without a win, a record</t>
+          <t>Four Filmfare Awards including Best Debut Director (Luck by Chance) and Best Director (Zindagi Na Milegi Dobara; Gully Boy); member of the Academy of Motion Picture Arts and Sciences</t>
         </is>
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Composers of several of the most popular Hindi romantic soundtracks of the 1990s; split in 2006.</t>
+          <t>One of the most influential contemporary Hindi filmmakers; Gully Boy was India's Academy Award entry.</t>
         </is>
       </c>
       <c r="O15" s="19" t="inlineStr">
         <is>
-          <t>Scored four Aamir Khan films, including 'Aati Kya Khandala', which Aamir sang in Ghulam.</t>
+          <t>Four credits with Aamir Khan: his cameo in her debut, their co-written Talaash, the anthology whose song features him, and his narration in Dil Dhadakne Do.</t>
         </is>
       </c>
       <c r="P15" s="17" t="n">
@@ -22405,22 +22397,22 @@
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>FILM-015; FILM-028; FILM-029; FILM-037</t>
+          <t>FILM-040; FILM-044; FILM-045; FILM-048</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Jo Jeeta Wohi Sikandar (1992)</t>
+          <t>Talaash (2012)</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>Jatin and Lalit Pandit, nephews of the classical vocalist Pandit Jasraj and brothers of actresses Sulakshana and Vijayta Pandit, began composing together with Yaara Dildara (1991). Their breakthrough was Mansoor Khan's Jo Jeeta Wohi Sikandar (1992), whose 'Pehla Nasha' brought their first Filmfare nomination and became one of the defining romantic songs of Aamir Khan's early career. In the following decade they scored landmark soundtracks including Dilwale Dulhania Le Jayenge, Kuch Kuch Hota Hai and Kabhi Khushi Kabhie Gham, with melodious compositions influenced by R. D. Burman. Their further collaborations with Aamir cover his changing roles: Ghulam (1998), including the playful 'Aati Kya Khandala', sung by Aamir himself and nominated for Filmfare Best Male Playback; Sarfarosh (1999), with 'Is Deewane Ladke Ko' and 'Jo Haal Dil Ka'; and Fanaa (2006), whose songs and Filmfare Best Music Director nomination came in the duo's final year. Despite their popularity they hold the record for most Filmfare nominations without a win. The brothers split in 2006 for personal reasons and reunited for a concert in February 2020. Their brother-in-law Aadesh Shrivastava composed the background score of Baazi.</t>
+          <t>Zoya Akhtar was born in Mumbai in 1972 to Javed Akhtar and Honey Irani and is the sister of Farhan Akhtar. After a filmmaking diploma from NYU's Tisch School of the Arts she assisted Mira Nair, Tony Gerber and Dev Benegal. Her debut, Luck by Chance (2009), a critically acclaimed look at newcomers in Bollywood, features Aamir Khan among the industry figures playing themselves and won her the Filmfare Best Debut Director award. Zindagi Na Milegi Dobara (2011) brought her the Filmfare Best Director award. With her regular writing partner Reema Kagti she co-wrote the story and screenplay of Talaash (2012), a neo-noir ghost story with Aamir Khan as a grieving police inspector. She directed the 'Sheila Ki Jawaani' segment of the centenary anthology Bombay Talkies (2013), whose song 'Apna Bombay Talkies' features Aamir among many stars, and directed Dil Dhadakne Do (2015), in which Aamir voices Pluto, the dog who narrates the Mehra family's cruise. Gully Boy (2019) won her a second Filmfare Best Director award and was India's Academy Award entry. With Kagti she founded Tiger Baby Films in 2015 and created the series Made in Heaven, and she later directed The Archies. She is a member of the Academy.</t>
         </is>
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-088; SOURCE-021; SOURCE-034; SOURCE-036; SOURCE-043; SOURCE-028</t>
+          <t>SOURCE-108; SOURCE-046; SOURCE-050; SOURCE-051; SOURCE-054</t>
         </is>
       </c>
       <c r="U15" s="5" t="inlineStr">
@@ -22432,26 +22424,26 @@
     <row r="16" ht="184" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>PERSON-015</t>
+          <t>PERSON-018</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Santoshi</t>
+          <t>Ashutosh Gowariker</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Director; screenwriter</t>
+          <t>Director; writer; actor</t>
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>1956</v>
+        <v>1964</v>
       </c>
       <c r="E16" s="18" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1982–present</t>
+          <t>1984–present</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -22461,65 +22453,65 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Son of filmmaker P. L. Santoshi; assistant director to Govind Nihalani on Vijeta (1982) and Ardh Satya (1983).</t>
+          <t>Born in Kolhapur; began as an actor in Holi (1984), where he met Aamir Khan, and worked in television and films such as Naam, Goonj and Kabhi Haan Kabhi Naa.</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Ghayal (1990), a blockbuster and critical success.</t>
+          <t>Directorial debut Pehla Nasha (1993); Baazi (1995) followed; both failed commercially. Breakthrough with Lagaan (2001).</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Ghayal (1990); Damini (1993); Andaz Apna Apna (1994); Barsaat (1995); Ghatak (1996); Pukar (2000); The Legend of Bhagat Singh (2002); Khakee (2004); Ajab Prem Ki Ghazab Kahani (2009)</t>
+          <t>Pehla Nasha (1993); Baazi (1995); Lagaan (2001); Swades (2004); Jodhaa Akbar (2008); Panipat (2019)</t>
         </is>
       </c>
       <c r="K16" s="19" t="inlineStr">
         <is>
-          <t>Women's rights (Damini, Lajja), national integration (Pukar), activism (Halla Bol); also broad comedy</t>
+          <t>Epic period and historical drama; rural India and national identity</t>
         </is>
       </c>
       <c r="L16" s="19" t="inlineStr">
         <is>
-          <t>Socially conscious action and courtroom drama, with a single foray into absurdist comedy that became a cult classic.</t>
+          <t>Long-form epics with large ensembles and music by A. R. Rahman.</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Three National Film Awards; six Filmfare Awards for direction, screenplay, dialogue and story</t>
+          <t>Academy Award nomination (Lagaan, as the film's director); Filmfare Best Film and Best Director (Lagaan; Jodhaa Akbar); National Film Awards; Academy voting member</t>
         </is>
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Credited with early mainstream feminist films addressing rape as a social issue.</t>
+          <t>Lagaan is India's third and, as of 2025, most recent nominee for the Academy Award for Best Foreign Language Film.</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in the cult comedy Andaz Apna Apna, gave him a cameo in Damini, and directed Aamir Khan Productions' Lahore 1947, in which Aamir did not act.</t>
+          <t>Friends since acting together in Holi; Gowariker directed Aamir in three films, and Aamir produced Lagaan.</t>
         </is>
       </c>
       <c r="P16" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>FILM-017; FILM-021</t>
+          <t>FILM-020; FILM-022; FILM-033</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Andaz Apna Apna (1994)</t>
+          <t>Lagaan (2001)</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Santoshi, born in 1956, is the son of filmmaker P. L. Santoshi and trained as an assistant to Govind Nihalani on Vijeta and Ardh Satya. His debut, Ghayal (1990), was a blockbuster and critical success, and Damini (1993), a legal drama regarded as a cult feminist film, is widely considered his best. Aamir Khan appears as himself in a song in Damini, promoting their next project. That project, Andaz Apna Apna (1994), paired Aamir with Salman Khan as rival fortune-hunters in an absurdist comedy of mistaken identities. It flopped on release and was nominated for four Filmfare awards, then became a cult classic, voted the second-best Bollywood comedy in an Indian Express poll and re-released in a 4K restoration in 2025. Santoshi went on to Barsaat, Ghatak, Pukar, The Legend of Bhagat Singh, Khakee and Ajab Prem Ki Ghazab Kahani, and has won three National Film Awards and six Filmfare awards. His films are known for socially conscious narratives about women's rights, national integration and activism. He later directed Lahore 1947, produced by Aamir Khan Productions and starring Sunny Deol; it was released in August 2026 as Batwara 1947, with Aamir credited as producer rather than performer.</t>
+          <t>Ashutosh Gowariker was born in Kolhapur in 1964 and began as an actor, making his debut in Ketan Mehta's Holi (1984), where he met Aamir Khan, the start of a long professional relationship. He continued acting in television and in films such as Naam, Goonj, Chamatkar and Kabhi Haan Kabhi Naa. His first two films as director both involved Aamir: the thriller Pehla Nasha (1993), a Body Double remake in which Aamir, Shah Rukh Khan and Saif Ali Khan appear as themselves, and the action film Baazi (1995), with Aamir as a framed police inspector; both failed commercially, and critics called Baazi a collage of Die Hard and Rambo. The partnership was vindicated by Lagaan (2001), which Aamir produced and starred in. The period cricket epic won the Filmfare Best Film and Best Director awards and eight National Film Awards, and was nominated for the Academy Award for Best Foreign Language Film. Gowariker went on to direct Swades with Shah Rukh Khan, the historical romance Jodhaa Akbar, which won the Filmfare Best Film and Best Director awards and was cited by the British Film Institute among the great Bollywood films of the century, and Panipat. He is a voting member of the Academy.</t>
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-089; SOURCE-023; SOURCE-027; SOURCE-064</t>
+          <t>SOURCE-091; SOURCE-026; SOURCE-028; SOURCE-039; SOURCE-071</t>
         </is>
       </c>
       <c r="U16" s="5" t="inlineStr">
@@ -22528,27 +22520,27 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="109" customHeight="1">
+    <row r="17" ht="184" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PERSON-016</t>
+          <t>PERSON-019</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Karim Morani (Cineyug)</t>
+          <t>Indra Kumar</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Producer; production banner</t>
+          <t>Director; producer (Maruti International)</t>
         </is>
       </c>
       <c r="D17" s="18" t="n"/>
       <c r="E17" s="18" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>1985–2015</t>
+          <t>1985–present (producer); 1990–present (director)</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -22558,61 +22550,65 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Co-owns Cineyug, a film production and event-management company, with his brother Aly Morani.</t>
+          <t>Worked as a producer before directing, with Mohabbat (1985) and Kasam (1988).</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Arjun (1985).</t>
+          <t>Dil (1990), a major commercial success and the year's highest-grossing Hindi film.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Arjun (1985); Vardi (1989); Yodha (1991); Damini (1993); Raja Hindustani (1996); Dum (2003); Ra.One (2011); Chennai Express (2013); Happy New Year (2014); Dilwale (2015)</t>
+          <t>Dil (1990); Beta (1992); Raja (1995); Ishq (1997); Mann (1999); Masti (2004); Dhamaal series (2007–2019); Total Dhamaal (2019)</t>
         </is>
       </c>
       <c r="K17" s="19" t="inlineStr">
         <is>
-          <t>Star-driven mainstream entertainers</t>
-        </is>
-      </c>
-      <c r="L17" s="19" t="n"/>
+          <t>Family melodrama and romance in the 1990s; broad ensemble comedy later</t>
+        </is>
+      </c>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <t>Crowd-pleasing melodrama built around hit soundtracks, later shifting to comedy franchises.</t>
+        </is>
+      </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Best Film (Raja Hindustani, credited to Cineyug)</t>
+          <t>Five Filmfare nominations, including Best Director for Beta and Raja</t>
         </is>
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Producer and co-producer of several major commercial hits over three decades.</t>
+          <t>Delivered major romantic hits in the early 1990s and later popularised long-running Hindi comedy franchises.</t>
         </is>
       </c>
       <c r="O17" s="19" t="inlineStr">
         <is>
-          <t>Cineyug produced Damini, with Aamir Khan's cameo, and Raja Hindustani, his biggest romantic hit of the 1990s.</t>
+          <t>Directed three Aamir Khan films, beginning with Dil, the actor's biggest early hit after QSQT.</t>
         </is>
       </c>
       <c r="P17" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>FILM-017; FILM-026</t>
+          <t>FILM-009; FILM-027; FILM-030</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>Raja Hindustani (1996)</t>
+          <t>Dil (1990)</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>Karim Morani and his brother Aly Morani run Cineyug, which combines film production with event management. Its productions span Arjun (1985), Vardi, Yodha and Rajkumar Santoshi's Damini (1993), in which Aamir Khan makes a cameo, through to later hits such as Ra.One, Chennai Express, Happy New Year and Dilwale. Cineyug's most significant film with Aamir Khan was Raja Hindustani (1996), produced by Ali Morani, Karim Morani and Bunty Soorma and directed by Dharmesh Darshan. Declared an all-time blockbuster and the highest-grossing film of 1996, it won the Filmfare Best Film award, credited to Cineyug, and Aamir's first Filmfare Best Actor award.</t>
+          <t>Indra Kumar began as a producer with Mohabbat (1985) and Kasam (1988) before directing his first film, Dil (1990), under his banner Maruti International with Ashok Thakeria. Starring Aamir Khan and Madhuri Dixit as rival students who marry against their fathers' wishes, Dil became the highest-grossing Hindi film of the year, won Madhuri Dixit her first Filmfare Best Actress award and brought Aamir a Best Actor nomination. Indra Kumar consolidated his reputation with Beta (1992) and Raja (1995), both of which earned him Filmfare Best Director nominations. He reunited with Aamir on Ishq (1997), a broad romantic comedy pairing Aamir with Juhi Chawla and Ajay Devgn with Kajol against two scheming fathers; it was the third-highest-grossing Hindi film of 1997. Their third film, Mann (1999), a remake of An Affair to Remember with Manisha Koirala, is recorded inconsistently: the film's own Wikipedia article calls it profitable, while his biography calls it a commercial failure. After 2000 he moved decisively to ensemble comedy with Masti (2004) and the Dhamaal franchise, whose Total Dhamaal (2019) became his highest-grossing release. His three films with Aamir Khan span the class-conflict romance, the masala romantic comedy and the tearjerker.</t>
         </is>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-090; SOURCE-023; SOURCE-032</t>
+          <t>SOURCE-083; SOURCE-014; SOURCE-033; SOURCE-037</t>
         </is>
       </c>
       <c r="U17" s="5" t="inlineStr">
@@ -22624,26 +22620,26 @@
     <row r="18" ht="184" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>PERSON-017</t>
+          <t>PERSON-020</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Ashutosh Gowariker</t>
+          <t>Mansoor Khan</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Director; writer; actor</t>
+          <t>Director; producer</t>
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>1964</v>
+        <v>1958</v>
       </c>
       <c r="E18" s="18" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>1984–present</t>
+          <t>1988–2008</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -22653,42 +22649,42 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Born in Kolhapur; began as an actor in Holi (1984), where he met Aamir Khan, and worked in television and films such as Naam, Goonj and Kabhi Haan Kabhi Naa.</t>
+          <t>Son of Nasir Hussain; educated at IIT Bombay, Cornell University and MIT.</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Directorial debut Pehla Nasha (1993); Baazi (1995) followed; both failed commercially. Breakthrough with Lagaan (2001).</t>
+          <t>Qayamat Se Qayamat Tak (1988), which won the National Film Award for Best Popular Film and the Filmfare Best Director award.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Pehla Nasha (1993); Baazi (1995); Lagaan (2001); Swades (2004); Jodhaa Akbar (2008); Panipat (2019)</t>
+          <t>Qayamat Se Qayamat Tak (1988); Jo Jeeta Wohi Sikandar (1992); Akele Hum Akele Tum (1995); Josh (2000); Jaane Tu... Ya Jaane Na (2008, co-producer)</t>
         </is>
       </c>
       <c r="K18" s="19" t="inlineStr">
         <is>
-          <t>Epic period and historical drama; rural India and national identity</t>
+          <t>Youthful romance, coming of age, marriage and ambition</t>
         </is>
       </c>
       <c r="L18" s="19" t="inlineStr">
         <is>
-          <t>Long-form epics with large ensembles and music by A. R. Rahman.</t>
+          <t>Musical romances and Indian reworkings of Western films such as Breaking Away, Kramer vs. Kramer and West Side Story.</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Academy Award nomination (Lagaan, as the film's director); Filmfare Best Film and Best Director (Lagaan; Jodhaa Akbar); National Film Awards; Academy voting member</t>
+          <t>National Film Award for Best Popular Film and Filmfare Best Director (Qayamat Se Qayamat Tak)</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Lagaan is India's third and, as of 2025, most recent nominee for the Academy Award for Best Foreign Language Film.</t>
+          <t>His debut is credited with bringing back the musical romantic genre in Hindi cinema.</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
         <is>
-          <t>Friends since acting together in Holi; Gowariker directed Aamir in three films, and Aamir produced Lagaan.</t>
+          <t>Cousin. Directed Aamir Khan's breakthrough and two further films, and co-produced Jaane Tu... Ya Jaane Na with him.</t>
         </is>
       </c>
       <c r="P18" s="17" t="n">
@@ -22696,22 +22692,22 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>FILM-020; FILM-022; FILM-033</t>
+          <t>FILM-004; FILM-015; FILM-025</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>Lagaan (2001)</t>
+          <t>Qayamat Se Qayamat Tak (1988)</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Ashutosh Gowariker was born in Kolhapur in 1964 and began as an actor, making his debut in Ketan Mehta's Holi (1984), where he met Aamir Khan, the start of a long professional relationship. He continued acting in television and in films such as Naam, Goonj, Chamatkar and Kabhi Haan Kabhi Naa. His first two films as director both involved Aamir: the thriller Pehla Nasha (1993), a Body Double remake in which Aamir, Shah Rukh Khan and Saif Ali Khan appear as themselves, and the action film Baazi (1995), with Aamir as a framed police inspector; both failed commercially, and critics called Baazi a collage of Die Hard and Rambo. The partnership was vindicated by Lagaan (2001), which Aamir produced and starred in. The period cricket epic won the Filmfare Best Film and Best Director awards and eight National Film Awards, and was nominated for the Academy Award for Best Foreign Language Film. Gowariker went on to direct Swades with Shah Rukh Khan, the historical romance Jodhaa Akbar, which won the Filmfare Best Film and Best Director awards and was cited by the British Film Institute among the great Bollywood films of the century, and Panipat. He is a voting member of the Academy.</t>
+          <t>Mansoor Khan, born in 1958, is the son of filmmaker Nasir Hussain and a cousin of Aamir Khan. He studied at IIT Bombay, Cornell University and MIT before entering the family business. His directorial debut, Qayamat Se Qayamat Tak (1988), a tragic Romeo and Juliet-style romance produced and written by his father, launched Aamir Khan and Juhi Chawla. It is credited with reviving the musical romantic genre and won the National Film Award for Best Popular Film and the Filmfare Best Director award. He reunited with Aamir on Jo Jeeta Wohi Sikandar (1992), a campus cycling drama whose resemblance to Breaking Away was pointed out after release, and on Akele Hum Akele Tum (1995), a musical marriage drama loosely based on Kramer vs. Kramer. His last film as director, Josh (2000), drew on West Side Story; in 2008 he co-produced Jaane Tu... Ya Jaane Na with Aamir Khan. Across three films with Aamir, Mansoor Khan's work traces the actor's early persona from doomed teenage lover to underdog student to proud young husband. He later left the industry and settled in Coonoor, Tamil Nadu, to farm, and has published The Third Curve (2013), on the world economy, and One: The Story of the Ultimate Myth (2023).</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-091; SOURCE-026; SOURCE-028; SOURCE-039; SOURCE-071</t>
+          <t>SOURCE-079; SOURCE-007; SOURCE-021; SOURCE-031</t>
         </is>
       </c>
       <c r="U18" s="5" t="inlineStr">
@@ -22720,15 +22716,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="154" customHeight="1">
+    <row r="19" ht="169" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PERSON-018</t>
+          <t>PERSON-022</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Anu Malik</t>
+          <t>Pritam</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -22737,12 +22733,12 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>1960</v>
+        <v>1971</v>
       </c>
       <c r="E19" s="18" t="n"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1974–present</t>
+          <t>2001–present</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -22752,65 +22748,65 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Son of composer Sardar Malik; brother of composer Daboo Malik and uncle of Amaal Mallik and Armaan Malik.</t>
+          <t>Pritam Chakraborty studied sound recording at FTII and composed advertising jingles and television title tracks.</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>A song for Hunterwali 77 (1975); first full soundtrack Poonam (1981); breakthrough with Mard (1985) and especially Baazigar (1993).</t>
+          <t>Co-composed Tere Liye (2001) with Jeet Gannguli; solo debut Stumped (2003); breakthrough with Dhoom (2004).</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Mard (1985); Baazigar (1993); Main Khiladi Tu Anari (1994); Baazi (1995); Akele Hum Akele Tum (1995); Ishq (1997); Border (1997); Mela (2000); Refugee (2000); Main Hoon Na (2004); Umrao Jaan (2006)</t>
+          <t>Dhoom (2004); Gangster (2006); Jab We Met (2007); Life in a... Metro (2007); Barfi! (2012); Dhoom 3 (2013); Ae Dil Hai Mushkil (2016); Dangal (2016); Laal Singh Chaddha (2022); Brahmastra: Part One – Shiva (2022); Animal (2023)</t>
         </is>
       </c>
       <c r="K19" s="19" t="inlineStr">
         <is>
-          <t>Popular romantic and dance songs for mainstream entertainers</t>
+          <t>Chart-topping romantic and anthem songs for big-budget films</t>
         </is>
       </c>
       <c r="L19" s="19" t="inlineStr">
         <is>
-          <t>Melodious, classically based compositions with prominent tabla; repeatedly accused of borrowing melodies.</t>
+          <t>Fusion of Indian classical influences with rock, Sufi and contemporary pop; has acknowledged early plagiarism mistakes.</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Best Music Direction (Refugee, 2000); Filmfare Best Music Director (Baazigar; Main Hoon Na); 14 Filmfare nominations</t>
+          <t>National Film Award for Best Music Direction (70th National Film Awards); six Filmfare Best Music Director awards</t>
         </is>
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>One of the most commercially successful Hindi composers of the 1990s and 2000s and a long-running Indian Idol judge.</t>
+          <t>One of contemporary Bollywood's most prolific and commercially successful composers, with more than 125 film scores.</t>
         </is>
       </c>
       <c r="O19" s="19" t="inlineStr">
         <is>
-          <t>Scored four Aamir Khan films between 1995 and 2000.</t>
+          <t>Composed the songs for three of Aamir Khan's biggest productions of the 2010s–2020s.</t>
         </is>
       </c>
       <c r="P19" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>FILM-022; FILM-025; FILM-027; FILM-032</t>
+          <t>FILM-046; FILM-049; FILM-053</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>Akele Hum Akele Tum (1995)</t>
+          <t>Dangal (2016)</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>Anu Malik, born in 1960, is the son of composer Sardar Malik. He composed his first film song as a teenager for Hunterwali 77 (1975), scored his first full soundtrack with Poonam (1981) and broke through with Mard (1985). Baazigar (1993) established him among the top music directors and won him a Filmfare award. His output combined melodious, classically inflected tunes with dance numbers, alongside repeated accusations of plagiarism. His four films with Aamir Khan came at the height of his popularity. He composed the songs for Ashutosh Gowariker's Baazi (1995) and Mansoor Khan's musical Akele Hum Akele Tum (1995), in which Aamir played an aspiring playback singer; the soundtrack sold about 2.5 million units and 'Raja Ko Rani Se' earned several Filmfare nominations. His songs for Indra Kumar's Ishq (1997) sold about 3 million units, and he was one of three composers on Dharmesh Darshan's Mela (2000). Malik later won the National Film Award for Refugee (2000) and a second Filmfare award for Main Hoon Na (2004), and judged Indian Idol from 2004 to 2018.</t>
+          <t>Pritam Chakraborty, born in 1971, studied sound recording at FTII and wrote jingles for brands such as Santro and McDonald's and television title tracks before co-composing Tere Liye (2001) with Jeet Gannguli. His breakthrough was Yash Raj's Dhoom (2004), whose title track became popular internationally, followed by Gangster, Jab We Met and Barfi!. His style fuses Indian classical colours with rock, Sufi and contemporary pop, and he has acknowledged that he made plagiarism mistakes early in his career. With Aamir Khan he composed the songs for Dhoom 3 (2013), extending the franchise's sound, and for Dangal (2016), whose earthy, lyric-driven songs by Amitabh Bhattacharya, such as 'Haanikaarak Bapu' and 'Dhaakad', won Screen and Mirchi awards. He then composed Laal Singh Chaddha (2022); its songs, including 'Tere Hawaale', earned several Filmfare nominations although the film failed. Pritam has won six Filmfare Best Music Director awards and a National Film Award at the 70th National Film Awards. Across three films he became the principal song composer of Aamir Khan's large-scale later productions.</t>
         </is>
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-092; SOURCE-028; SOURCE-031; SOURCE-033; SOURCE-038</t>
+          <t>SOURCE-118; SOURCE-052; SOURCE-055; SOURCE-059</t>
         </is>
       </c>
       <c r="U19" s="5" t="inlineStr">
@@ -22819,97 +22815,97 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="169" customHeight="1">
+    <row r="20" ht="154" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>PERSON-019</t>
+          <t>PERSON-023</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Ram Gopal Varma</t>
+          <t>Ram Sampath</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Director; producer; writer</t>
+          <t>Music director (songs and background score)</t>
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>1962</v>
+        <v>1977</v>
       </c>
       <c r="E20" s="18" t="n"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>1989–present</t>
+          <t>1997–2017; 2023–present</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Telugu; Hindi</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Born in Hyderabad; studied civil engineering and ran a video rental store, then assisted on Telugu films.</t>
+          <t>Composed advertising jingles in Mumbai before moving into pop albums and film music.</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Siva (1989), a Telugu crime thriller that introduced the Steadicam to Indian cinema; Hindi breakthrough with Rangeela (1995).</t>
+          <t>Film work includes Khakee (2004); breakthrough with Delhi Belly (2011).</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Siva (1989); Kshana Kshanam (1991); Rangeela (1995); Satya (1998); Company (2002); Bhoot (2003); Sarkar (2005); Rakta Charitra (2010)</t>
+          <t>Khakee (2004); Delhi Belly (2011); Talaash (2012); Satyamev Jayate (2012, television); Raees (2017); Laapataa Ladies (2024); Sitaare Zameen Par (2025, background score)</t>
         </is>
       </c>
       <c r="K20" s="19" t="inlineStr">
         <is>
-          <t>Gangster noir, horror and political crime; one major musical romance</t>
+          <t>Contemporary rock-inflected soundtracks and socially themed music</t>
         </is>
       </c>
       <c r="L20" s="19" t="inlineStr">
         <is>
-          <t>Pioneer of 'Mumbai noir'; gritty realism and technical innovation.</t>
+          <t>Versatile composer moving between advertising, pop and film with contemporary rock elements.</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Shool (1999, as producer); Nandi Awards for Siva; Filmfare Best Story (Rangeela)</t>
+          <t>Filmfare Best Music Director and Best Background Score (Laapataa Ladies, 2025)</t>
         </is>
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Regarded as a pioneer of new-age Indian cinema; launched directors including Anurag Kashyap and Madhur Bhandarkar.</t>
+          <t>Won a landmark 2008 plagiarism case over Krazzy 4, an important precedent for composers' rights in India.</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>Directed Rangeela, a turning point that recast Aamir Khan as a streetwise Mumbai lover.</t>
+          <t>Aamir Khan Productions' regular composer: Delhi Belly, Talaash, the Satyamev Jayate television show and the Sitaare Zameen Par score.</t>
         </is>
       </c>
       <c r="P20" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>FILM-024</t>
+          <t>FILM-043; FILM-044; FILM-055</t>
         </is>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Rangeela (1995)</t>
+          <t>Talaash (2012)</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>Ram Gopal Varma was born in Hyderabad in 1962, studied civil engineering and briefly worked as a site engineer before running a video rental store, where he studied which films audiences chose. After assisting on Telugu films he directed Siva (1989), a crime thriller that won Nandi Awards and introduced the Steadicam to Indian cinema. His Hindi breakthrough came with Rangeela (1995), a musical romance with Aamir Khan as Munna, a black-market ticket seller in love with his childhood friend Mili, played by Urmila Matondkar, who is being groomed for stardom. With A. R. Rahman's music and Manish Malhotra's costumes, the film was hailed for bringing a modern sensibility to mid-1990s Hindi cinema; it won Filmfare awards including Best Music Director and Best Story for Varma, and marked a turning point for both leads. Varma then redefined Hindi crime cinema with Satya (1998), Company (2002) and Sarkar (2005), pioneering a 'Mumbai noir' style, and scored a horror hit with Bhoot. His production 'factory' launched directors such as Anurag Kashyap and Madhur Bhandarkar. Rangeela remains his only film with Aamir Khan.</t>
+          <t>Ram Sampath, born in 1977, began in Mumbai's advertising industry and moved into pop albums and films, including Khakee (2004). In 2008 he won a plagiarism case against the makers of Krazzy 4, a significant precedent for composers in India. His breakthrough came with Delhi Belly (2011), produced by Aamir Khan Productions, whose 'Bhaag D.K. Bose' became an internet sensation and controversy; Aamir appears in the film's closing-credits song. He scored Talaash (2012), the Aamir Khan Productions and Excel thriller starring Aamir, with lyrics by Javed Akhtar, and composed the music of Aamir's television series Satyamev Jayate, including its title track. After a break he returned with Laapataa Ladies, directed by Kiran Rao, which won him the Filmfare awards for Best Music Director and Best Background Score, and composed the background score for Sitaare Zameen Par (2025), whose songs are by Shankar–Ehsaan–Loy. His career is closely tied to Aamir Khan's production company in the 2010s and 2020s.</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-093; SOURCE-030</t>
+          <t>SOURCE-114; SOURCE-049; SOURCE-050; SOURCE-061</t>
         </is>
       </c>
       <c r="U20" s="5" t="inlineStr">
@@ -22918,128 +22914,124 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="199" customHeight="1">
+    <row r="21" ht="169" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PERSON-020</t>
+          <t>PERSON-025</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>A. R. Rahman</t>
+          <t>Tahir Hussain</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Music director (songs and background score)</t>
+          <t>Producer; director; screenwriter (Tahir Hussain Enterprises)</t>
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>1967</v>
-      </c>
-      <c r="E21" s="18" t="n"/>
+        <v>1938</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>2010</v>
+      </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1992–present</t>
+          <t>1971–1993</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Tamil; Hindi; international</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Born Arunachalam Shekhar Dileep Kumar, son of Malayalam film composer R. K. Shekhar; composed advertising jingles from 1987.</t>
+          <t>Born in Shahabad to a schoolteacher from a Pashtun zamindar family; younger brother and protégé of Nasir Hussain, who directed his first production.</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Roja (1992); Hindi breakthrough with Rangeela (1995).</t>
+          <t>Producer of Caravan (1971); directorial debut Tum Mere Ho (1990).</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Roja (1992); Bombay (1995); Rangeela (1995); Dil Se.. (1998); Taal (1999); Lagaan (2001); Swades (2004); Rang De Basanti (2006); Jodhaa Akbar (2008); Slumdog Millionaire (2008); Rockstar (2011)</t>
+          <t>Caravan (1971); Anamika; Madhosh (1974); Zakhmee (1975); Tum Mere Ho (1990); Hum Hain Rahi Pyar Ke (1993)</t>
         </is>
       </c>
       <c r="K21" s="19" t="inlineStr">
         <is>
-          <t>Epic, patriotic and romantic scores</t>
-        </is>
-      </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>Synthesises Carnatic, Hindustani, Western classical and qawwali traditions with electronic production; introduced 7.1 surround sound to South Indian films.</t>
-        </is>
-      </c>
+          <t>Mainstream romance and family entertainment</t>
+        </is>
+      </c>
+      <c r="L21" s="19" t="n"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Two Academy Awards and two Grammy Awards (Slumdog Millionaire); seven National Film Awards; Padma Shri (2000); Padma Bhushan (2010)</t>
+          <t>Filmfare Best Film and a National Film Award Special Mention (as producer) for Hum Hain Rahi Pyar Ke</t>
         </is>
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>The most internationally celebrated Indian film composer, who transformed the sound of Hindi and Tamil film music from the 1990s.</t>
+          <t>A mainstream producer of the 1970s–1990s best known as father of Aamir Khan and Faisal Khan.</t>
         </is>
       </c>
       <c r="O21" s="19" t="inlineStr">
         <is>
-          <t>Scored six Aamir Khan films, including three of his most acclaimed.</t>
+          <t>Father. Produced Madhosh, directed Tum Mere Ho and produced Hum Hain Rahi Pyar Ke, which Aamir co-wrote.</t>
         </is>
       </c>
       <c r="P21" s="17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>FILM-024; FILM-031; FILM-033; FILM-035; FILM-036; FILM-039</t>
+          <t>FILM-002; FILM-008; FILM-019</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>Lagaan (2001)</t>
+          <t>Hum Hain Rahi Pyar Ke (1993)</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>A. R. Rahman was born Arunachalam Shekhar Dileep Kumar in 1967, the son of Malayalam film composer R. K. Shekhar, and made his name composing advertising jingles before Mani Ratnam's Roja (1992) launched his film career. Bombay (1995) sold 15 million soundtrack copies, and Ram Gopal Varma's Rangeela (1995) was his Hindi breakthrough and his first film with Aamir Khan; it won him the Filmfare Best Music Director award. His music blends Carnatic, Hindustani, Western classical and qawwali influences with state-of-the-art production. The partnership with Aamir continued through Deepa Mehta's Earth, then Lagaan (2001), whose songs won the Filmfare and National Film Awards for music and whose lyricist Javed Akhtar also won both. Rahman scored Mangal Pandey: The Rising (2005) and Rang De Basanti (2006), winning another Filmfare award for the latter, and Ghajini (2008), the first Hindi film to cross ₹100 crore nett in India, whose soundtrack was the year's best-selling Bollywood album. His international career peaked with Slumdog Millionaire, which brought two Academy Awards and two Grammys. He has seven National Film Awards and received the Padma Shri in 2000 and the Padma Bhushan in 2010. Across six films he supplied the sound of Aamir Khan's move from romantic hero to epic and political roles.</t>
+          <t>Mohammad Tahir Hussain Khan was born in 1938 in Shahabad. His elder brother, the filmmaker Nasir Hussain, brought him into the industry by directing his first production, Caravan (1971), which became a big hit. As a producer he went on to make Anamika, Madhosh and Zakhmee, the last of which gave the composer Bappi Lahiri early recognition. He was the father of Nikhat Khan, Farhat Khan, Aamir Khan and Faisal Khan, and his productions intersect with Aamir Khan's career at three points. Madhosh (1974) features the child Aamir as the younger version of its lead. Tahir Hussain made his directorial debut with Tum Mere Ho (1990), a snake-charmer fantasy starring Aamir and Juhi Chawla that failed at the box office but later gained a so-bad-it's-good following. His biggest success with his son was Hum Hain Rahi Pyar Ke (1993), directed by Mahesh Bhatt and co-written by Aamir; it won the Filmfare Best Film award and a National Film Award Special Mention shared by producer and director. He died in 2010. Much of this profile comes from a search-result summary rather than a fetched page, so dates and titles carry lower confidence.</t>
         </is>
       </c>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-094; SOURCE-030; SOURCE-035; SOURCE-039; SOURCE-041; SOURCE-042; SOURCE-045; SOURCE-071</t>
+          <t>SOURCE-077; SOURCE-005; SOURCE-012; SOURCE-025; SOURCE-068; SOURCE-082</t>
         </is>
       </c>
       <c r="U21" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="154" customHeight="1">
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="139" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>PERSON-021</t>
+          <t>PERSON-026</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Dharmesh Darshan</t>
+          <t>Yash Raj Films</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Director; writer</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>1967</v>
-      </c>
+          <t>Production banner</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="n"/>
       <c r="E22" s="18" t="n"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>1993–2006</t>
+          <t>Founded 1970</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -23049,65 +23041,61 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Brother of producer Suneel Darshan; nephew of Mahesh and Mukesh Bhatt.</t>
+          <t>Founded by director Yash Chopra; led by Aditya Chopra, vice-chairman from 2010 and chairman after Yash Chopra's death in October 2012.</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Lootere (1993), an action romance with Sunny Deol and Juhi Chawla; breakthrough with Raja Hindustani (1996).</t>
+          <t>Founded 1970.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Lootere (1993); Raja Hindustani (1996); Mela (2000); Dhadkan (2000); Haan Maine Bhi Pyaar Kiya (2002); Bewafaa (2005); Aap Ki Khatir (2006)</t>
+          <t>Dilwale Dulhania Le Jayenge (1995); Fanaa (2006); Ek Tha Tiger (2012); Dhoom 3 (2013); Thugs of Hindostan (2018)</t>
         </is>
       </c>
       <c r="K22" s="19" t="inlineStr">
         <is>
-          <t>Romantic melodrama, class and family obstacles</t>
-        </is>
-      </c>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>Mainstream romance, often drawn from earlier Indian or international films.</t>
-        </is>
-      </c>
+          <t>Romance, spectacle and action franchises</t>
+        </is>
+      </c>
+      <c r="L22" s="19" t="n"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Screen Award for Best Director (Raja Hindustani, 1997); two Filmfare nominations</t>
+          <t>Ranked by Filmfare in 2006 as one of India's most powerful production companies</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>One of the youngest successful directors of his generation, alongside Sooraj Barjatya and Karan Johar.</t>
+          <t>One of Hindi cinema's dominant studios, known for landmark romances and, later, the Dhoom and spy franchises; also distributes other producers' films.</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan's biggest 1990s romantic hit and the poorly received Mela.</t>
+          <t>Produced three Aamir Khan films; Yash Chopra had earlier directed him in Parampara (1993), a non-YRF production.</t>
         </is>
       </c>
       <c r="P22" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>FILM-026; FILM-032</t>
+          <t>FILM-037; FILM-046; FILM-051</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Raja Hindustani (1996)</t>
+          <t>Dhoom 3 (2013)</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Dharmesh Darshan, born in 1967, is the brother of producer Suneel Darshan and a nephew of Mahesh and Mukesh Bhatt. He debuted with Lootere (1993) and, at under thirty, had a major blockbuster with Raja Hindustani (1996). Inspired by Jab Jab Phool Khile, it cast Aamir Khan as a proud small-town taxi driver who marries a rich woman, played by Karisma Kapoor, and is separated from her by her scheming stepmother. It grossed ₹76.34 crore worldwide, the highest of 1996, and won five Filmfare awards, including Aamir's first Best Actor award, plus a Screen Award for Best Director for Darshan. He reunited with Aamir on Mela (2000), a masala adventure co-starring Aamir's brother Faisal Khan and Twinkle Khanna, co-written from a story by Suneel Darshan. His biography calls it a major commercial disaster with highly negative reviews, though Rediff called Aamir its saving grace. The same year he had a hit with Dhadkan. Later films included Haan Maine Bhi Pyaar Kiya, Bewafaa, which did well overseas, and Aap Ki Khatir (2006), after which he stopped directing.</t>
+          <t>Yash Raj Films was founded in 1970 by director Yash Chopra and is led by his son Aditya Chopra, vice-chairman from 2010 and chairman after Yash Chopra's death in October 2012. The studio is known for landmark romances such as Dilwale Dulhania Le Jayenge and for action franchises including Dhoom and the spy universe begun with Ek Tha Tiger. Aamir Khan's association began before he worked for the banner: Yash Chopra directed him in Parampara (1993), produced by Firoz Nadiadwala. For YRF itself, Aditya and Yash Chopra produced Fanaa (2006), the first film shot at YRF Studios and a major success. Aditya Chopra then cast Aamir as the twin circus-performer thieves of Dhoom 3 (2013), which became the first Indian film to gross ₹500 crore worldwide, and as the con man Firangi in the period epic Thugs of Hindostan (2018), which set a record opening before collapsing commercially.</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-095; SOURCE-032; SOURCE-038</t>
+          <t>SOURCE-106; SOURCE-024; SOURCE-043; SOURCE-052; SOURCE-057</t>
         </is>
       </c>
       <c r="U22" s="5" t="inlineStr">
@@ -23116,27 +23104,29 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="154" customHeight="1">
+    <row r="23" ht="124" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PERSON-022</t>
+          <t>PERSON-027</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Vikram Bhatt</t>
+          <t>Abhijat Joshi</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="n"/>
+          <t>Screenwriter</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>1969</v>
+      </c>
       <c r="E23" s="18" t="n"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>1982–present</t>
+          <t>1998–2023</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -23146,65 +23136,61 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Grandson of pioneer filmmaker Vijay Bhatt and son of cinematographer Pravin Bhatt; began at 14 assisting Mukul Anand on Kanoon Kya Karega (1982).</t>
+          <t>Playwright and professor of English at Otterbein University, Ohio, since 2003.</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Breakthrough with Ghulam (1998).</t>
+          <t>Kareeb (1998) and Mission Kashmir (2000) for Vidhu Vinod Chopra.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Ghulam (1998); Kasoor (2001); Raaz (2002); 1920 (2008); Shaapit (2010); Haunted – 3D (2011); Raaz 3D (2012)</t>
+          <t>Mission Kashmir (2000); Lage Raho Munna Bhai (2006); 3 Idiots (2009); PK (2014); Sanju (2018); Shikara (2020); Dunki (2023)</t>
         </is>
       </c>
       <c r="K23" s="19" t="inlineStr">
         <is>
-          <t>Horror and thriller; the Raaz franchise</t>
-        </is>
-      </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>Genre filmmaking; introduced stereoscopic 3D horror to Indian cinema with Haunted – 3D.</t>
-        </is>
-      </c>
+          <t>Moral questions dramatised through comedy and emotion</t>
+        </is>
+      </c>
+      <c r="L23" s="19" t="n"/>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Best Director nominations for Ghulam (1999) and Raaz (2003)</t>
+          <t>National Film Award for Best Screenplay (Lage Raho Munna Bhai); Filmfare story, screenplay and dialogue awards (2007, 2010, 2015)</t>
         </is>
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>A leading figure in Hindi horror cinema; founded Loneranger Productions.</t>
+          <t>Rajkumar Hirani's principal co-writer; their partnership holds records for IIFA Best Dialogue.</t>
         </is>
       </c>
       <c r="O23" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in Ghulam, his most successful film.</t>
+          <t>Co-wrote both Hirani films starring Aamir Khan, winning Filmfare writing awards for each.</t>
         </is>
       </c>
       <c r="P23" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>FILM-028</t>
+          <t>FILM-041; FILM-047</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>Ghulam (1998)</t>
+          <t>3 Idiots (2009)</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>Vikram Bhatt is the grandson of Vijay Bhatt, a pioneer of Indian cinema, and the son of cinematographer Pravin Bhatt. He entered films at 14, working with Mukul Anand on Kanoon Kya Karega (1982). His breakthrough came with Ghulam (1998), produced by Mukesh Bhatt and written by Anjum Rajabali from On the Waterfront. Aamir Khan plays Siddhu, an aimless Mumbai boxer drawn into a gangster's orbit through his brother, who finds the courage to testify and fight back. The film was a hit and earned Bhatt a Filmfare Best Director nomination. Its train-race dare won Filmfare's Best Scene award, and Aamir's own recording of 'Aati Kya Khandala' earned him a playback nomination. Bhatt then moved toward thrillers and horror with Kasoor and Raaz (2002), which earned a second Best Director nomination and began a franchise. Later films include 1920, Shaapit and Haunted – 3D (2011), which introduced stereoscopic 3D horror to India and became the highest-grossing Hindi horror film at the time. Ghulam remains his only film with Aamir Khan.</t>
+          <t>Abhijat Joshi, born in 1969, is a playwright and has taught English at Otterbein University in Ohio since 2003, writing Hindi films alongside his academic career. His screen credits began with Kareeb (1998) and Mission Kashmir (2000) for Vidhu Vinod Chopra, and include Eklavya: The Royal Guard, Broken Horses, Wazir and Shikara. He is best known as Rajkumar Hirani's co-writer: Lage Raho Munna Bhai won him the National Film Award for Best Screenplay, and their dialogue collaborations hold records at the IIFA Awards. With Hirani he co-wrote 3 Idiots (2009), sharing the Filmfare awards for Best Story, Screenplay and Dialogue, and PK (2014), sharing the Best Screenplay award; he is also credited on Nanban (2012), the Tamil remake of 3 Idiots. The partnership continued with Sanju (2018) and Dunki (2023).</t>
         </is>
       </c>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-096; SOURCE-034</t>
+          <t>SOURCE-112; SOURCE-047; SOURCE-053; SOURCE-073; SOURCE-109</t>
         </is>
       </c>
       <c r="U23" s="5" t="inlineStr">
@@ -23213,27 +23199,27 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="184" customHeight="1">
+    <row r="24" ht="169" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>PERSON-023</t>
+          <t>PERSON-028</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>John Matthew Matthan</t>
+          <t>Advait Chandan</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Director; producer; writer (Cinematt Pictures)</t>
+          <t>Director; writer</t>
         </is>
       </c>
       <c r="D24" s="18" t="n"/>
       <c r="E24" s="18" t="n"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>1999–2013</t>
+          <t>2017–present</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -23243,65 +23229,61 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Assistant director on Richard Attenborough's Gandhi (1982) and to Govind Nihalani; later an advertising director who set up Cinematt Pictures in the early 1990s.</t>
+          <t>Began in 2007 as third assistant director and assistant production manager on Taare Zameen Par; assistant, casting director and post-production supervisor on Dhobi Ghat.</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Sarfarosh (1999), developed from 1992 over seven years of research and production.</t>
+          <t>Secret Superstar (2017), which he wrote and directed.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Sarfarosh (1999); Shikhar (2005); A New Love Ishtory (2013)</t>
+          <t>Secret Superstar (2017); Laal Singh Chaddha (2022); Loveyapa (2025)</t>
         </is>
       </c>
       <c r="K24" s="19" t="inlineStr">
         <is>
-          <t>Terrorism, policing and national security; social themes such as brain drain</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="inlineStr">
-        <is>
-          <t>Meticulously researched realism within a commercial thriller format; praised for characterisation.</t>
-        </is>
-      </c>
+          <t>Ordinary people achieving the extraordinary; family and devotion</t>
+        </is>
+      </c>
+      <c r="L24" s="19" t="n"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Best Popular Film; Filmfare Best Film (Critics) and Best Screenplay; Screen Most Promising Debut Director (all for Sarfarosh); jury chair at IFFI 2021</t>
+          <t>Zee Cine Most Promising Director (Secret Superstar); Filmfare Best Director and Best Screenplay nominations</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Sarfarosh is regarded as a landmark 1990s thriller that married serious themes to commercial filmmaking.</t>
+          <t>His debut became one of the most profitable Indian films, driven by its success in China.</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
         <is>
-          <t>Directed Sarfarosh, one of Aamir Khan's most acclaimed performances of the 1990s.</t>
+          <t>Trained on Aamir Khan's productions and directed him in two films, one a major success and one a major failure.</t>
         </is>
       </c>
       <c r="P24" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>FILM-029</t>
+          <t>FILM-050; FILM-053</t>
         </is>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>Sarfarosh (1999)</t>
+          <t>Secret Superstar (2017)</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>John Matthew Matthan began his career as an assistant director on Richard Attenborough's Gandhi (1982) and with Govind Nihalani before becoming an advertising director and founding Cinematt Pictures in Mumbai in the early 1990s. He started developing Sarfarosh in 1992 and spent seven years on research, pre-production and production. Released in 1999, the thriller cast Aamir Khan as ACP Ajay Singh Rathod, a policeman whose family was shattered by terrorism, investigating an arms network run by his admired friend, Gulfam Hassan, played by Naseeruddin Shah. Filmfare's reviewer credited Matthan with drawing perfectly crafted performances from the whole cast, and Rediff praised the film for marrying serious and commercial cinema. Sarfarosh won the National Film Award for Best Popular Film, Filmfare's Critics' Award for Best Film and Best Screenplay for Matthan, and the Screen Award for Most Promising Debut Director. It also brought Aamir a Zee Cine Best Actor award. Matthan's later projects were slower: Shikhar (2005) was reworked after 9/11 made its brain-drain theme less relevant, and A New Love Ishtory, completed in 2009, was delayed until 2013. He chaired the feature-film jury at IFFI in 2021.</t>
+          <t>Advait Chandan came up inside Aamir Khan's production world. In 2007 he was third assistant director and assistant production manager on Taare Zameen Par, and on Kiran Rao's Dhobi Ghat he worked as an assistant, casting director and post-production supervisor. His biography's career section is flagged as needing more citations. Aamir Khan Productions and Zee Studios backed his writing-directing debut, Secret Superstar (2017), about a teenage girl who sings anonymously on YouTube to escape an abusive father; Aamir played Shakti Kumar, a vain music director who becomes her mentor, earning a Filmfare supporting nomination. The film became the highest-grossing Hindi film of 2017 and one of the most profitable Indian films, largely through its release in China. It won Chandan the Zee Cine Most Promising Director award and Filmfare nominations for direction and screenplay. He then directed Laal Singh Chaddha (2022), Atul Kulkarni's Indian adaptation of Forrest Gump with Aamir in the title role. Hit by a boycott campaign and mixed reviews, it lost heavily at the box office. Chandan's next film was Loveyapa (2025).</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-097; SOURCE-036; SOURCE-069</t>
+          <t>SOURCE-120; SOURCE-044; SOURCE-048; SOURCE-056; SOURCE-059</t>
         </is>
       </c>
       <c r="U24" s="5" t="inlineStr">
@@ -23310,97 +23292,97 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="184" customHeight="1">
+    <row r="25" ht="169" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PERSON-024</t>
+          <t>PERSON-031</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Deepa Mehta</t>
+          <t>Amit Trivedi</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Director; writer; producer</t>
+          <t>Music director (song composer)</t>
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1950</v>
+        <v>1979</v>
       </c>
       <c r="E25" s="18" t="n"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>1976–present</t>
+          <t>2001–present</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Canadian; Hindi; English</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Born in Amritsar; studied philosophy at Lady Shri Ram College; emigrated to Canada in 1973 and co-founded Sunrise Films.</t>
+          <t>Born in Mumbai; formed Om the Fusion Band in college and composed for theatre, television, Marathi films and advertising.</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Feature debut Sam &amp; Me (1991), followed by Camilla (1994).</t>
+          <t>Aamir (2008); breakthrough with Dev.D (2009).</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Fire (1996); Earth (1998); Bollywood/Hollywood (2002); Water (2005); Heaven on Earth (2008); Midnight's Children (2012); Funny Boy (2020)</t>
+          <t>Dev.D (2009); Wake Up Sid (2009); Udaan (2010); Lootera (2013); Bombay Talkies (2013); Queen (2014); Udta Punjab (2016); Secret Superstar (2017); Andhadhun (2018)</t>
         </is>
       </c>
       <c r="K25" s="19" t="inlineStr">
         <is>
-          <t>Partition, sectarian violence, gender, sexuality and the lives of marginalised women; Indian-Canadian identity</t>
+          <t>Indie-pop soundtracks for new-wave Hindi films</t>
         </is>
       </c>
       <c r="L25" s="19" t="inlineStr">
         <is>
-          <t>Transnational art cinema examining how politics and patriarchy shape ordinary lives.</t>
+          <t>Inventive indie-pop blending electronic and traditional sounds.</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Academy Award nomination (Water); Genie Award for Best Original Screenplay; Governor General's Performing Arts Award (2012); Officer of the Order of Canada (2013); Canadian Screen Award for Best Director (2021)</t>
+          <t>National Film Award for Best Music Direction (Dev.D); Filmfare R. D. Burman Award (2010)</t>
         </is>
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>A pioneering Canadian woman filmmaker whose Elements trilogy provoked protests in India and international acclaim.</t>
+          <t>A defining composer of the independent-minded Hindi cinema of the 2010s.</t>
         </is>
       </c>
       <c r="O25" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in Earth, one of his darkest and most praised roles.</t>
+          <t>Composed Bombay Talkies, including the song in which Aamir Khan appears, and Secret Superstar.</t>
         </is>
       </c>
       <c r="P25" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>FILM-031</t>
+          <t>FILM-045; FILM-050</t>
         </is>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>Earth (1998)</t>
+          <t>Secret Superstar (2017)</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>Deepa Mehta was born in Amritsar in 1950, grew up aware of the scars of Partition, and studied philosophy at Lady Shri Ram College before moving to Canada in 1973. There she co-founded Sunrise Films, directed television, and made her feature debut with Sam &amp; Me (1991). Her Elements trilogy made her internationally known: Fire (1996), about two sisters-in-law in love, drew protests from Hindu fundamentalist groups; Water (2005), about child widows, had to be shot in Sri Lanka and was nominated for the Academy Award. Between them came Earth (1998), adapted from Bapsi Sidhwa's novel Ice Candy Man and seen through a young girl's eyes in 1947 Lahore. Aamir Khan plays Dil Navaz, the ice-candy seller whose rejected love for the nanny Shanta and the horror of Partition massacres turn him into her betrayer. Rediff called it probably the best performance of his life, and the film was India's submission for the Academy Award. Mehta's later work includes Bollywood/Hollywood, Heaven on Earth, Midnight's Children with Salman Rushdie and Funny Boy, which won the Canadian Screen Award for Best Director. She is an Officer of the Order of Canada. Earth is the only film in which Aamir Khan's romantic persona turns fully destructive.</t>
+          <t>Amit Trivedi, born in Mumbai in 1979, formed Om the Fusion Band in college and composed for Hindi and Gujarati theatre, television, Marathi films and advertising jingles for brands such as McDonald's and Airtel before his film debut with Aamir (2008). Dev.D (2009) was his breakthrough, winning the National Film Award for Best Music Direction, and he received Filmfare's R. D. Burman Award for New Music Talent in 2010. He composed and scored Wake Up Sid, wrote all the songs and the background score of Udaan, and became a leading composer of the 2010s Hindi new wave with Lootera, Queen and Andhadhun, for which he wrote nine songs. His indie-pop sound combines electronic textures with traditional elements. He composed the anthology Bombay Talkies (2013), whose song 'Apna Bombay Talkies' brings together many stars including Aamir Khan, and Advait Chandan's Secret Superstar (2017), produced by Aamir Khan Productions. Written for a teenage singer, its songs made Meghna Mishra a Filmfare winner and brought Trivedi the second of three consecutive Filmfare nominations, for Udta Punjab, Secret Superstar and Manmarziyaan.</t>
         </is>
       </c>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-098; SOURCE-035</t>
+          <t>SOURCE-116; SOURCE-051; SOURCE-056</t>
         </is>
       </c>
       <c r="U25" s="5" t="inlineStr">
@@ -23409,27 +23391,29 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="169" customHeight="1">
+    <row r="26" ht="154" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>PERSON-025</t>
+          <t>PERSON-038</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Aamir Khan Productions</t>
+          <t>Dharmesh Darshan</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Production banner</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="n"/>
+          <t>Director; writer</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>1967</v>
+      </c>
       <c r="E26" s="18" t="n"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Founded 1999</t>
+          <t>1993–2006</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -23439,61 +23423,65 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Founded by Aamir Khan; Kiran Rao, who met him as an assistant director on Lagaan, became a key producer.</t>
+          <t>Brother of producer Suneel Darshan; nephew of Mahesh and Mukesh Bhatt.</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Lagaan (2001).</t>
+          <t>Lootere (1993), an action romance with Sunny Deol and Juhi Chawla; breakthrough with Raja Hindustani (1996).</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Lagaan (2001); Taare Zameen Par (2007); Jaane Tu... Ya Jaane Na (2008); Peepli Live (2010); Dhobi Ghat (2011); Delhi Belly (2011); Talaash (2012); Dangal (2016); Secret Superstar (2017); Laal Singh Chaddha (2022); Laapataa Ladies (2024); Sitaare Zameen Par (2025); Happy Patel: Khatarnak Jasoos (2026); Lahore 1947 / Batwara 1947 (2026)</t>
+          <t>Lootere (1993); Raja Hindustani (1996); Mela (2000); Dhadkan (2000); Haan Maine Bhi Pyaar Kiya (2002); Bewafaa (2005); Aap Ki Khatir (2006)</t>
         </is>
       </c>
       <c r="K26" s="19" t="inlineStr">
         <is>
-          <t>Socially engaged mainstream films, new directors and occasional art-house releases</t>
-        </is>
-      </c>
-      <c r="L26" s="19" t="n"/>
+          <t>Romantic melodrama, class and family obstacles</t>
+        </is>
+      </c>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>Mainstream romance, often drawn from earlier Indian or international films.</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Academy Award nomination (Lagaan); Filmfare Best Film (Lagaan; Taare Zameen Par; Dangal); National Film Awards including Best Popular Film (Lagaan) and Best Film on Family Welfare (Taare Zameen Par)</t>
+          <t>Screen Award for Best Director (Raja Hindustani, 1997); two Filmfare nominations</t>
         </is>
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Credited with opening Chinese markets to Indian films through the success of Dangal and Secret Superstar.</t>
+          <t>One of the youngest successful directors of his generation, alongside Sooraj Barjatya and Karan Johar.</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
         <is>
-          <t>His own company, which produced or co-produced ten of his acting films, including his directorial debut.</t>
+          <t>Directed Aamir Khan's biggest 1990s romantic hit and the poorly received Mela.</t>
         </is>
       </c>
       <c r="P26" s="17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>FILM-033; FILM-038; FILM-042; FILM-043; FILM-044; FILM-049; FILM-050; FILM-053; FILM-055; FILM-057</t>
+          <t>FILM-026; FILM-032</t>
         </is>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>Lagaan (2001)</t>
+          <t>Raja Hindustani (1996)</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Aamir Khan Productions was founded by Aamir Khan in 1999 and launched with Lagaan (2001), a then-unprecedentedly expensive cricket epic nominated for the Academy Award for Best Foreign Language Film. The company became the vehicle for Aamir's selective, message-led career. He directed Taare Zameen Par (2007) for it, and it backed first-time or early-career directors including Abbas Tyrewala (Jaane Tu... Ya Jaane Na), Kiran Rao (Dhobi Ghat, Laapataa Ladies), Abhinay Deo (Delhi Belly) and Advait Chandan (Secret Superstar, Laal Singh Chaddha). Many productions were made with partners, among them PVR, UTV, Excel Entertainment, Disney, Zee Studios, Paramount and Viacom18, and Jio Studios. Dangal (2016), co-produced with Disney, became the highest-grossing Indian film and, with Secret Superstar (2017), is credited with opening China to Indian cinema. The banner's recent run is mixed: the costly Laal Singh Chaddha (2022) was a box-office disaster, while Sitaare Zameen Par (2025) was a hit and Lahore 1947, released in 2026 as Batwara 1947, was not. Of its films, ten feature Aamir Khan on screen, from lead roles to a cameo in Happy Patel: Khatarnak Jasoos.</t>
+          <t>Dharmesh Darshan, born in 1967, is the brother of producer Suneel Darshan and a nephew of Mahesh and Mukesh Bhatt. He debuted with Lootere (1993) and, at under thirty, had a major blockbuster with Raja Hindustani (1996). Inspired by Jab Jab Phool Khile, it cast Aamir Khan as a proud small-town taxi driver who marries a rich woman, played by Karisma Kapoor, and is separated from her by her scheming stepmother. It grossed ₹76.34 crore worldwide, the highest of 1996, and won five Filmfare awards, including Aamir's first Best Actor award, plus a Screen Award for Best Director for Darshan. He reunited with Aamir on Mela (2000), a masala adventure co-starring Aamir's brother Faisal Khan and Twinkle Khanna, co-written from a story by Suneel Darshan. His biography calls it a major commercial disaster with highly negative reviews, though Rediff called Aamir its saving grace. The same year he had a hit with Dhadkan. Later films included Haan Maine Bhi Pyaar Kiya, Bewafaa, which did well overseas, and Aap Ki Khatir (2006), after which he stopped directing.</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-099; SOURCE-039; SOURCE-044; SOURCE-055; SOURCE-056; SOURCE-059; SOURCE-061; SOURCE-064</t>
+          <t>SOURCE-095; SOURCE-032; SOURCE-038</t>
         </is>
       </c>
       <c r="U26" s="5" t="inlineStr">
@@ -23502,29 +23490,27 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="184" customHeight="1">
+    <row r="27" ht="109" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PERSON-026</t>
+          <t>PERSON-042</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Farhan Akhtar</t>
+          <t>Karim Morani</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Director; writer; producer; actor</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="n">
-        <v>1974</v>
-      </c>
+          <t>Producer; production banner</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="n"/>
       <c r="E27" s="18" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2001–present</t>
+          <t>1985–2015</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -23534,65 +23520,61 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Son of screenwriters Javed Akhtar and Honey Irani; apprenticed on Lamhe (1991) at 17, assisted on Himalay Putra (1997) and worked in advertising.</t>
+          <t>Co-owns Cineyug, a film production and event-management company, with his brother Aly Morani.</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Dil Chahta Hai (2001), his directorial debut and Excel Entertainment's first film.</t>
+          <t>Arjun (1985).</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Dil Chahta Hai (2001); Lakshya (2004); Don (2006); Rock On!! (2008); Luck by Chance (2009); Don 2 (2011); Zindagi Na Milegi Dobara (2011); Talaash (2012); Bhaag Milkha Bhaag (2013); Dil Dhadakne Do (2015)</t>
+          <t>Arjun (1985); Vardi (1989); Yodha (1991); Damini (1993); Raja Hindustani (1996); Dum (2003); Ra.One (2011); Chennai Express (2013); Happy New Year (2014); Dilwale (2015)</t>
         </is>
       </c>
       <c r="K27" s="19" t="inlineStr">
         <is>
-          <t>Urban friendships, self-discovery and contemporary relationships</t>
-        </is>
-      </c>
-      <c r="L27" s="19" t="inlineStr">
-        <is>
-          <t>Realistic, conversational urban storytelling credited with starting a new wave in Hindi cinema.</t>
-        </is>
-      </c>
+          <t>Star-driven mainstream entertainers</t>
+        </is>
+      </c>
+      <c r="L27" s="19" t="n"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>National Film Awards for Best Hindi Film (Dil Chahta Hai; Rock On!!); Filmfare Best Actor (Bhaag Milkha Bhaag); Filmfare Best Screenplay (Dil Chahta Hai)</t>
+          <t>Filmfare Best Film (Raja Hindustani, credited to Cineyug)</t>
         </is>
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Co-founder of Excel Entertainment and a key figure in the modernisation of Hindi cinema after 2000.</t>
+          <t>Producer and co-producer of several major commercial hits over three decades.</t>
         </is>
       </c>
       <c r="O27" s="19" t="inlineStr">
         <is>
-          <t>Directed Dil Chahta Hai and co-produced three further films featuring Aamir Khan, writing the dialogue for Talaash and Dil Dhadakne Do.</t>
+          <t>Cineyug produced Damini, with Aamir Khan's cameo, and Raja Hindustani, his biggest romantic hit of the 1990s.</t>
         </is>
       </c>
       <c r="P27" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>FILM-034; FILM-040; FILM-044; FILM-048</t>
+          <t>FILM-017; FILM-026</t>
         </is>
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>Dil Chahta Hai (2001)</t>
+          <t>Raja Hindustani (1996)</t>
         </is>
       </c>
       <c r="S27" s="5" t="inlineStr">
         <is>
-          <t>Farhan Akhtar, born in 1974, is the son of Javed Akhtar and Honey Irani and the brother of director Zoya Akhtar. He apprenticed on Yash Chopra's Lamhe at 17, assisted on Himalay Putra and spent about three years in advertising before founding Excel Entertainment with Ritesh Sidhwani in 1999. His directorial debut, Dil Chahta Hai (2001), which he also wrote, followed three affluent Mumbai friends; Aamir Khan played Akash, the flippant joker who falls for an engaged woman. It was acclaimed for its realistic depiction of urban youth, won the National Film Award for Best Hindi Film and seven Filmfare awards, including Best Screenplay for Akhtar, and is credited with launching a new wave of urban Hindi cinema. Akhtar went on to direct Lakshya and the Don films, and to act, beginning with Rock On!! (2008) and winning the Filmfare Best Actor award for Bhaag Milkha Bhaag. As producer he backed three more projects with Aamir: Zoya Akhtar's Luck by Chance (2009), in which Aamir appears as himself; Reema Kagti's Talaash (2012), co-produced with Aamir Khan Productions and with dialogue by Akhtar; and Dil Dhadakne Do (2015), where Aamir voices the narrating dog and Akhtar wrote the dialogue and appears on screen.</t>
+          <t>Karim Morani and his brother Aly Morani run Cineyug, which combines film production with event management. Its productions span Arjun (1985), Vardi, Yodha and Rajkumar Santoshi's Damini (1993), in which Aamir Khan makes a cameo, through to later hits such as Ra.One, Chennai Express, Happy New Year and Dilwale. Cineyug's most significant film with Aamir Khan was Raja Hindustani (1996), produced by Ali Morani, Karim Morani and Bunty Soorma and directed by Dharmesh Darshan. Declared an all-time blockbuster and the highest-grossing film of 1996, it won the Filmfare Best Film award, credited to Cineyug, and Aamir's first Filmfare Best Actor award.</t>
         </is>
       </c>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-100; SOURCE-040; SOURCE-046; SOURCE-050; SOURCE-054; SOURCE-070</t>
+          <t>SOURCE-090; SOURCE-023; SOURCE-032</t>
         </is>
       </c>
       <c r="U27" s="5" t="inlineStr">
@@ -23601,91 +23583,97 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="124" customHeight="1">
+    <row r="28" ht="184" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>PERSON-027</t>
+          <t>PERSON-043</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Excel Entertainment</t>
+          <t>Ketan Mehta</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Production banner</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="n"/>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>1952</v>
+      </c>
       <c r="E28" s="18" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Founded 9 August 1999</t>
+          <t>1975–present</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Hindi; streaming series</t>
+          <t>Hindi; Gujarati</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Founded by Farhan Akhtar and Ritesh Sidhwani.</t>
+          <t>Born in Navsari, Gujarat; trained at the Film and Television Institute of India, then made documentaries for ISRO in Gujarat.</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Dil Chahta Hai (2001).</t>
+          <t>Bhavni Bhavai (1980), a Gujarati film that won the National Film Award for Best Feature Film on National Integration.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Dil Chahta Hai (2001); Lakshya (2004); Don (2006); Rock On!! (2008); Luck by Chance (2009); Zindagi Na Milegi Dobara (2011); Talaash (2012); Bombay Talkies (2013); Dil Dhadakne Do (2015); Gully Boy (2019); Mirzapur; Made in Heaven</t>
+          <t>Bhavni Bhavai (1980); Holi (1984); Mirch Masala (1985); Maya Memsaab (1993); Sardar (1993); Mangal Pandey: The Rising (2005); Rang Rasiya (2014); Manjhi: The Mountain Man (2015)</t>
         </is>
       </c>
       <c r="K28" s="19" t="inlineStr">
         <is>
-          <t>Contemporary urban stories and unusual characters</t>
-        </is>
-      </c>
-      <c r="L28" s="19" t="n"/>
+          <t>Comedy, satire, romance, violence and rebellion; social and political history</t>
+        </is>
+      </c>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>Rooted in parallel cinema, moving later to larger historical and biographical productions.</t>
+        </is>
+      </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>National Film Awards for Dil Chahta Hai and Rock On!!; Gully Boy selected as India's Academy Award entry</t>
+          <t>Two National Film Awards; Ordre des Arts et des Lettres (2010)</t>
         </is>
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Pioneered contemporary Hindi cinema and moved early into original streaming series.</t>
+          <t>A leading figure of Indian parallel cinema of the 1980s whose films addressed caste, gender and rebellion.</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
         <is>
-          <t>Produced two films starring Aamir Khan, and three in which he appears as himself or as a voice.</t>
+          <t>Gave Aamir Khan his first adult screen role in Holi and directed his comeback film Mangal Pandey: The Rising two decades later.</t>
         </is>
       </c>
       <c r="P28" s="17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>FILM-034; FILM-040; FILM-044; FILM-045; FILM-048</t>
+          <t>FILM-003; FILM-035</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>Dil Chahta Hai (2001)</t>
+          <t>Holi (1984)</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Excel Entertainment was founded on 9 August 1999 by Farhan Akhtar and producer Ritesh Sidhwani. Its first film, Dil Chahta Hai (2001), starring Aamir Khan, Saif Ali Khan and Akshaye Khanna, won the National Film Award for Best Feature Film in Hindi, and the company became associated with contemporary urban storytelling through Lakshya, Don, Rock On!!, Zindagi Na Milegi Dobara and Gully Boy, India's Academy Award entry. It later moved into streaming series with Inside Edge, Mirzapur and Made in Heaven. Aamir Khan's work with the banner covers leading roles in Dil Chahta Hai and in Talaash (2012), co-produced with Aamir Khan Productions; appearances as himself in Luck by Chance (2009) and, among many stars, in a song of the anthology Bombay Talkies (2013); and the narrating voice of the dog Pluto in Dil Dhadakne Do (2015).</t>
+          <t>Ketan Mehta was born in 1952 in Navsari, Gujarat, and studied at the Film and Television Institute of India before making documentaries in Gujarat as a television producer for the Indian Space Research Organisation. His first feature, the Gujarati Bhavni Bhavai (1980), won the National Film Award for Best Feature Film on National Integration and established him in the parallel-cinema movement. Holi (1984), a largely improvised drama about a student revolt in a college hostel, followed; it gave Aamir Khan, credited as Aamir Hussain, his first adult role alongside Naseeruddin Shah, Om Puri and the future director Ashutosh Gowariker. Mirch Masala (1985) was nominated for the Golden Prize at the Moscow festival, and he went on to make Maya Memsaab and the biopic Sardar, which won a National Film Award. His interest in comedy, satire, romance, violence and rebellion carried into Mangal Pandey: The Rising (2005), a large historical production with Aamir Khan as the sepoy who helped spark the 1857 rebellion. The film marked Aamir's return after four years away, earned him a Filmfare nomination and drew political protests over its depiction of Pandey. Later films include Rang Rasiya and Manjhi: The Mountain Man. He is married to actress Deepa Sahi, a producer of Mangal Pandey.</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-101; SOURCE-040; SOURCE-046; SOURCE-050; SOURCE-051; SOURCE-054; SOURCE-071</t>
+          <t>SOURCE-078; SOURCE-006; SOURCE-041</t>
         </is>
       </c>
       <c r="U28" s="5" t="inlineStr">
@@ -23694,27 +23682,29 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="169" customHeight="1">
+    <row r="29" ht="184" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PERSON-028</t>
+          <t>PERSON-044</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Shankar–Ehsaan–Loy</t>
+          <t>Mahesh Bhatt</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Music directors (songs and background score)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="n"/>
+          <t>Director; producer; screenwriter</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>1948</v>
+      </c>
       <c r="E29" s="18" t="n"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>1997–present</t>
+          <t>1974–present (director until 1999)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -23724,65 +23714,65 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Shankar Mahadevan (vocalist trained in Indian classical music), Ehsaan Noorani (guitarist, Musicians Institute, Los Angeles) and Loy Mendonsa (keyboardist) came together through advertising jingles and Mumbai's non-film music scene.</t>
+          <t>Son of director Nanabhai Bhatt and Shirin Mohammad Ali; assistant director to Raj Khosla.</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>First film Dus (begun 1997, left incomplete); mainstream entry with Mission Kashmir (2000); breakthrough with Dil Chahta Hai (2001).</t>
+          <t>Manzilein Aur Bhi Hain (1974); breakthrough with Arth (1982); Saaransh (1984) was India's Academy Award submission.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Mission Kashmir (2000); Dil Chahta Hai (2001); Kal Ho Naa Ho (2003); Bunty Aur Babli (2005); Don (2006); Taare Zameen Par (2007); Rock On!! (2008); Luck by Chance (2009); Zindagi Na Milegi Dobara (2011); Bhaag Milkha Bhaag (2013); Dil Dhadakne Do (2015); Sitaare Zameen Par (2025)</t>
+          <t>Arth (1982); Saaransh (1984); Aashiqui (1990); Dil Hai Ke Manta Nahin (1991); Sadak (1991); Sir (1993); Hum Hain Rahi Pyar Ke (1993); Tamanna (1997); Zakhm (1998)</t>
         </is>
       </c>
       <c r="K29" s="19" t="inlineStr">
         <is>
-          <t>Contemporary urban soundtracks; emotionally direct songs for coming-of-age and family stories</t>
+          <t>Autobiographical relationships, illegitimacy and infidelity; later commercial romance</t>
         </is>
       </c>
       <c r="L29" s="19" t="inlineStr">
         <is>
-          <t>Fusion of Carnatic and Hindustani vocals with Western rock, jazz and electronic arrangement; Gulzar called it 'a sensible synthesis of popularity and class'.</t>
+          <t>Unconventional narratives and bold themes, balanced in the 1990s with music-driven commercial films.</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Best Music Direction (Kal Ho Naa Ho); three Filmfare Best Music Director awards; Padma Shri to Shankar Mahadevan (2019)</t>
+          <t>Five National Film Awards (including for Hum Hain Rahi Pyar Ke, Tamanna and Zakhm); four Filmfare Awards</t>
         </is>
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Defined the sound of the post-2000 urban Hindi film.</t>
+          <t>One of the most prominent Hindi filmmakers of the 1980s and 1990s; co-founded Vishesh Films and mentored many actors.</t>
         </is>
       </c>
       <c r="O29" s="19" t="inlineStr">
         <is>
-          <t>Scored five films featuring Aamir Khan, from Dil Chahta Hai to Sitaare Zameen Par.</t>
+          <t>Directed two of Aamir Khan's most successful romantic comedies; Aamir co-wrote the second.</t>
         </is>
       </c>
       <c r="P29" s="17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>FILM-034; FILM-038; FILM-040; FILM-048; FILM-055</t>
+          <t>FILM-013; FILM-019</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>Dil Chahta Hai (2001)</t>
+          <t>Hum Hain Rahi Pyar Ke (1993)</t>
         </is>
       </c>
       <c r="S29" s="5" t="inlineStr">
         <is>
-          <t>Shankar Mahadevan, Ehsaan Noorani and Loy Mendonsa came from Mumbai's rock, blues, jazz and pop scene. Ehsaan and Loy began working together around 1989 composing advertising jingles, and Shankar joined them through composer Ranjit Barot. Their first film, Mukul Anand's Dus, was left incomplete after the director's death; Mission Kashmir (2000) brought them into the mainstream. Their breakthrough was Farhan Akhtar's Dil Chahta Hai (2001), with Aamir Khan, whose songs won them Filmfare's R. D. Burman Award for New Music Talent and became part of the film's cult status. The trio fuse Shankar's Carnatic and Hindustani vocals with Ehsaan's rock guitar and Loy's electronic arrangement, a mix Gulzar called 'a sensible synthesis of popularity and class'. They won the National Film Award for Kal Ho Naa Ho and Filmfare awards for Bunty Aur Babli and 2 States. With Aamir Khan they also scored Taare Zameen Par (2007), whose song 'Maa', sung by Shankar Mahadevan, won National Film Awards for playback and lyrics, as well as Luck by Chance, Dil Dhadakne Do and, nearly two decades after TZP, the songs of Sitaare Zameen Par (2025). Shankar Mahadevan received the Padma Shri in 2019.</t>
+          <t>Mahesh Bhatt was born in 1948 to director Nanabhai Bhatt and Shirin Mohammad Ali, and entered films as an assistant to Raj Khosla. He directed his first film, Manzilein Aur Bhi Hain, at 26, and made his name with the autobiographical Arth (1982) and Saaransh (1984), India's submission for the Academy Award. With his brother Mukesh he co-founded Vishesh Films in 1986–87, and in the 1990s he moved toward commercial romance with Aashiqui, Sadak and Dil Hai Ke Manta Nahin (1991). That film, a remake of It Happened One Night, cast Aamir Khan as a jobless journalist opposite Mahesh's daughter Pooja Bhatt; its success boosted her career and its soundtrack was widely praised. Two years later Bhatt directed Aamir in Hum Hain Rahi Pyar Ke (1993), a Houseboat-inspired family romance for which Aamir co-wrote the screenplay and dialogue with Robin Bhatt. It won the Filmfare Best Film award and Best Actress for Juhi Chawla, and a National Film Award Special Mention for Bhatt and producer Tahir Hussain. Bhatt stopped directing after Kartoos (1999), continuing as a writer and producer; Vishesh Films produced hits such as Raaz and Murder. He has won five National Film Awards and four Filmfare awards.</t>
         </is>
       </c>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-102; SOURCE-040; SOURCE-044; SOURCE-046; SOURCE-054; SOURCE-061; SOURCE-070; SOURCE-072</t>
+          <t>SOURCE-084; SOURCE-018; SOURCE-025; SOURCE-068</t>
         </is>
       </c>
       <c r="U29" s="5" t="inlineStr">
@@ -23791,29 +23781,29 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="199" customHeight="1">
+    <row r="30" ht="139" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>PERSON-029</t>
+          <t>PERSON-046</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Rakeysh Omprakash Mehra</t>
+          <t>Mukesh Bhatt</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Director; producer; writer</t>
+          <t>Producer; production banner</t>
         </is>
       </c>
       <c r="D30" s="17" t="n">
-        <v>1963</v>
+        <v>1952</v>
       </c>
       <c r="E30" s="18" t="n"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2001–present</t>
+          <t>1990–present</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -23823,65 +23813,61 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Born in Delhi; studied at Shri Ram College of Commerce; sold vacuum cleaners for Eureka Forbes, then founded Flicks Motion Picture Company in 1986 to make commercials.</t>
+          <t>Son of director-producer Nanabhai Bhatt; younger brother of Mahesh Bhatt, with whom he co-founded Vishesh Films.</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Aks (2001), a commercial failure; breakthrough with Rang De Basanti (2006).</t>
+          <t>Vishesh Films' early 1990s productions, including Dil Hai Ke Manta Nahin (1991).</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Aks (2001); Rang De Basanti (2006); Delhi-6 (2009); Bhaag Milkha Bhaag (2013); Mirzya (2016); Mere Pyare Prime Minister (2019); Toofaan (2021)</t>
+          <t>Dil Hai Ke Manta Nahin (1991); Ghulam (1998); Raaz (2002); Murder (2004); Jannat (2008); Aashiqui 2 (2013)</t>
         </is>
       </c>
       <c r="K30" s="19" t="inlineStr">
         <is>
-          <t>Youth activism, national identity, marks-driven education and vote-bank politics</t>
-        </is>
-      </c>
-      <c r="L30" s="19" t="inlineStr">
-        <is>
-          <t>Ensemble socio-political drama with music by A. R. Rahman and editing by P. S. Bharathi, his wife.</t>
-        </is>
-      </c>
+          <t>Music-led romances, thrillers and horror franchises</t>
+        </is>
+      </c>
+      <c r="L30" s="19" t="n"/>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Two Filmfare Best Director awards (Rang De Basanti; Bhaag Milkha Bhaag); two National Film Awards for Best Popular Film; BAFTA nomination; Nargis Dutt Award</t>
+          <t>Filmfare nominations (1992, 1999, 2003)</t>
         </is>
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Rang De Basanti's influence on youth protest was dubbed the 'RDB effect'.</t>
+          <t>Built Vishesh Films into a consistently profitable mid-budget studio; took sole control after the brothers split in 2021.</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in Rang De Basanti, which won him the Filmfare Best Actor (Critics) award.</t>
+          <t>Produced two Aamir Khan films a decade apart.</t>
         </is>
       </c>
       <c r="P30" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>FILM-036</t>
+          <t>FILM-013; FILM-028</t>
         </is>
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>Rang De Basanti (2006)</t>
+          <t>Ghulam (1998)</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>Rakeysh Omprakash Mehra was born in Delhi in 1963 and studied commerce before working in sales for Eureka Forbes. In 1986 he founded Flicks Motion Picture Company and directed commercials for brands such as Coca-Cola and Pepsi. His first feature, the supernatural thriller Aks (2001) with Amitabh Bachchan, failed commercially. His second, Rang De Basanti (2006), was inspired partly by the Mandal Commission protests and follows a group of Delhi students cast in a British filmmaker's documentary about revolutionaries. Aamir Khan plays DJ, their charismatic, cynical leader, who is also cast as Chandrashekhar Azad. The film broke opening records, won the Filmfare awards for Best Film and Best Director, the National Film Award for Best Popular Film and a BAFTA nomination, and was India's Academy Award submission. Aamir won the Filmfare Best Actor (Critics) award. Its candlelight protests were copied in real life after the Jessica Lall verdict, and the media coined the term 'RDB effect' for such activism. Mehra later made Delhi-6, the Milkha Singh biopic Bhaag Milkha Bhaag (his second Filmfare Best Director award), Mirzya and Toofaan. He is married to P. S. Bharathi, who won the National and Filmfare editing awards for Rang De Basanti. In 2025 he chaired the international jury at IFFI.</t>
+          <t>Mukesh Bhatt, born in 1952, is the son of Nanabhai Bhatt and the younger brother of Mahesh Bhatt. The brothers founded Vishesh Films (1986 according to Mukesh Bhatt's article, 1987 according to Mahesh Bhatt's), and Mukesh ran the business side of a banner that went on to produce more than twenty hits. With T-Series founder Gulshan Kumar he produced Dil Hai Ke Manta Nahin (1991), Mahesh Bhatt's romantic comedy with Aamir Khan and Pooja Bhatt, which was nominated for Filmfare Best Film. He produced Ghulam (1998), directed by Vikram Bhatt and adapted from On the Waterfront, in which Aamir played a Mumbai boxer who stands up to a local gangster; it was a hit and its train-race sequence won Filmfare's Best Scene award. In the 2000s the banner became known for Raaz, Murder, Jannat and Aashiqui 2. After a professional split announced in May 2021, Mukesh Bhatt took sole control of Vishesh Films.</t>
         </is>
       </c>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-103; SOURCE-042</t>
+          <t>SOURCE-085; SOURCE-084; SOURCE-018; SOURCE-034</t>
         </is>
       </c>
       <c r="U30" s="5" t="inlineStr">
@@ -23890,70 +23876,76 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="124" customHeight="1">
+    <row r="31" ht="169" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PERSON-030</t>
+          <t>PERSON-049</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>UTV Motion Pictures (Ronnie Screwvala)</t>
+          <t>R. D. Burman</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Producer; production banner</t>
+          <t>Music director</t>
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>1956</v>
-      </c>
-      <c r="E31" s="18" t="n"/>
+        <v>1939</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>1994</v>
+      </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>1981–present</t>
+          <t>1961–1994</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Hindi; media</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Ronnie Screwvala pioneered cable television in India in 1981 and founded UTV Software Communications, whose film arm was UTV Motion Pictures.</t>
+          <t>Son of composer S. D. Burman and Meera Dev Burman; married Asha Bhosle in 1980.</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>UTV Motion Pictures productions from the early 2000s.</t>
+          <t>Chhote Nawab (1961); breakthrough with Teesri Manzil (1966).</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Lakshya (2004); Swades (2004); Rang De Basanti (2006); Jodhaa Akbar (2008); Delhi Belly (2011); Barfi! (2012); later, as RSVP Movies, Kedarnath (2018) and Uri: The Surgical Strike (2019)</t>
+          <t>Teesri Manzil (1966); Hare Rama Hare Krishna (1971); Yaadon Ki Baaraat (1973); Sholay (1975); Hum Kisise Kum Naheen (1977); 1942: A Love Story (1994)</t>
         </is>
       </c>
       <c r="K31" s="19" t="inlineStr">
         <is>
-          <t>Ambitious mainstream and crossover films</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="n"/>
+          <t>Youthful, dance-driven film music; experimental soundscapes</t>
+        </is>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>Combined Western, Latin, Oriental and Arabic influences with Indian and Bengali folk elements; pioneered electronic rock and disco-rock fusion and experimental production techniques.</t>
+        </is>
+      </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Best Popular Film (Rang De Basanti); Filmfare Best Film (Rang De Basanti; Jodhaa Akbar; Barfi!)</t>
+          <t>Three Filmfare Best Music Director awards (1983, 1984, 1995 posthumously)</t>
         </is>
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Built one of India's first corporate studios, sold to Disney in 2012 at an enterprise value of US$1.4 billion.</t>
+          <t>One of the most innovative Hindi film composers, closely associated with Kishore Kumar, Lata Mangeshkar, Asha Bhosle and Mohammed Rafi.</t>
         </is>
       </c>
       <c r="O31" s="19" t="inlineStr">
         <is>
-          <t>Co-produced Rang De Basanti and Delhi Belly; UTV also distributed Dangal.</t>
+          <t>Composed both films in which Aamir Khan appeared as a child.</t>
         </is>
       </c>
       <c r="P31" s="17" t="n">
@@ -23961,22 +23953,22 @@
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>FILM-036; FILM-043</t>
+          <t>FILM-001; FILM-002</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>Rang De Basanti (2006)</t>
+          <t>Yaadon Ki Baaraat (1973)</t>
         </is>
       </c>
       <c r="S31" s="5" t="inlineStr">
         <is>
-          <t>Ronnie Screwvala, born in 1956, pioneered cable television in India in 1981 and built UTV Software Communications into a media group with partners including News Corp, Fox, Disney and Bloomberg. Its film arm, UTV Motion Pictures, produced prestige and commercial hits including Lakshya, Swades, Jodhaa Akbar and Barfi!. With Aamir Khan it co-produced Rang De Basanti (2006) with director Rakeysh Omprakash Mehra; Screwvala shared its Filmfare Best Film award, National Film Award for Best Popular Film and BAFTA nomination. UTV also co-produced Delhi Belly (2011) with Aamir Khan Productions, and UTV Motion Pictures distributed Dangal in 2016. Screwvala sold UTV to Disney in 2012 and later founded RSVP Movies, which made Kedarnath and Uri: The Surgical Strike.</t>
+          <t>Rahul Dev Burman, born in 1939, was the son of the composer S. D. Burman. He debuted as a music director with Chhote Nawab (1961) and broke through with Nasir Hussain's Teesri Manzil (1966), a major hit. Over the next two decades he became the defining sound of youthful Hindi cinema, writing scores for Hare Rama Hare Krishna, Yaadon Ki Baaraat, Sholay and Hum Kisise Kum Naheen, often with lyricists Majrooh Sultanpuri, Anand Bakshi and Gulzar and singers Kishore Kumar, Asha Bhosle, Lata Mangeshkar and Mohammed Rafi. His style drew on Western, Latin, Oriental and Arabic music, and he experimented with electronic rock, disco-rock fusion and unconventional recording methods. He married Asha Bhosle in 1980. He won three Filmfare Best Music Director awards, the last posthumously for 1942: A Love Story, released in the year of his death in 1994. His connection to Aamir Khan is limited to the child roles: he composed Yaadon Ki Baaraat, whose title song features eight-year-old Aamir as young Ratan, and Madhosh (1974), where Aamir played the younger Raj. Both films used Majrooh Sultanpuri's lyrics.</t>
         </is>
       </c>
       <c r="T31" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-104; SOURCE-042; SOURCE-049; SOURCE-055</t>
+          <t>SOURCE-076; SOURCE-004; SOURCE-005</t>
         </is>
       </c>
       <c r="U31" s="5" t="inlineStr">
@@ -23985,29 +23977,29 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="154" customHeight="1">
+    <row r="32" ht="184" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>PERSON-031</t>
+          <t>PERSON-051</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Kunal Kohli</t>
+          <t>Rajkumar Hirani</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Director; dialogue writer</t>
+          <t>Director; writer; editor</t>
         </is>
       </c>
       <c r="D32" s="17" t="n">
-        <v>1969</v>
+        <v>1962</v>
       </c>
       <c r="E32" s="18" t="n"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Late 1990s–present</t>
+          <t>1991–present</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -24017,65 +24009,65 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Film critic in the late 1990s; hosted Chalo Cinema on EL TV and directed about 24 music videos.</t>
+          <t>Studied film editing at FTII on a scholarship; directed and produced advertising films; edited Mission Kashmir (2000) and promos for Vidhu Vinod Chopra.</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Mujhse Dosti Karoge! (2002), a commercial failure; breakthrough with Hum Tum (2004).</t>
+          <t>Munna Bhai M.B.B.S. (2003), which won the National Film Award for Best Popular Film.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Mujhse Dosti Karoge! (2002); Hum Tum (2004); Fanaa (2006); Thoda Pyaar Thoda Magic (2008); Break Ke Baad (2010, producer); Teri Meri Kahaani (2012)</t>
+          <t>Munna Bhai M.B.B.S. (2003); Lage Raho Munna Bhai (2006); 3 Idiots (2009); PK (2014); Sanju (2018); Dunki (2023)</t>
         </is>
       </c>
       <c r="K32" s="19" t="inlineStr">
         <is>
-          <t>Romantic comedy and romantic thriller</t>
+          <t>Social critique through comedy: medicine, Gandhian values, education, religious exploitation, immigration</t>
         </is>
       </c>
       <c r="L32" s="19" t="inlineStr">
         <is>
-          <t>Glossy romantic films with prominent music, made largely with Yash Raj Films.</t>
+          <t>Warm, humane comedy with emotional climaxes; edits his own films; long partnership with writer Abhijat Joshi.</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Best Director (Hum Tum)</t>
+          <t>Four National Film Awards for Best Popular Film; 11 Filmfare Awards including Best Film and Best Director (3 Idiots)</t>
         </is>
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>A leading director of mainstream romantic films in the mid-2000s.</t>
+          <t>One of Hindi cinema's most successful directors; 3 Idiots and PK each became the highest-grossing Indian film on release.</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
         <is>
-          <t>Directed and wrote the dialogue for Fanaa, pairing Aamir Khan with Kajol.</t>
+          <t>Directed Aamir Khan in two record-breaking films; a Lala Amarnath biopic was reported as a possible third collaboration.</t>
         </is>
       </c>
       <c r="P32" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>FILM-037</t>
+          <t>FILM-041; FILM-047</t>
         </is>
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>Fanaa (2006)</t>
+          <t>3 Idiots (2009)</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Kunal Kohli, born in 1969, was a film critic and television host on Chalo Cinema before directing music videos and moving to features. His debut, Mujhse Dosti Karoge! (2002), failed despite an A-list cast, but Hum Tum (2004) was a hit and won him the Filmfare Best Director award. His next film, Fanaa (2006), produced by Aditya and Yash Chopra, was a romantic thriller in which Aamir Khan plays Rehan, a charming Delhi tour guide who is secretly a Kashmiri separatist, and Kajol plays the blind woman he seduces. Kohli also wrote the dialogue. Released during a ban in Gujarat prompted by Aamir's remarks on the Narmada dam, it grossed ₹105.48 crore worldwide and marked Kajol's return after five years. It won Filmfare awards for Kajol, for lyricist Prasoon Joshi and for the singers of 'Chand Sifarish', though some critics found it melodramatic. Kohli's later films, Thoda Pyaar Thoda Magic and Teri Meri Kahaani, did not match its success, and he produced Break Ke Baad and made his acting debut in Phir Se....</t>
+          <t>Rajkumar Hirani, born in 1962, studied film editing at FTII and built a career in advertising before editing Vidhu Vinod Chopra's Mission Kashmir (2000). Chopra produced his directorial debut, Munna Bhai M.B.B.S. (2003), which won the National Film Award for Best Popular Film, and its sequel Lage Raho Munna Bhai (2006). Hirani edits all his own films and writes with Abhijat Joshi, blending social commentary with comedy and emotion. His first film with Aamir Khan, 3 Idiots (2009), loosely adapted from Chetan Bhagat's Five Point Someone, cast Aamir as Rancho, a brilliant student who defies an education system built on rote learning. It became the highest-grossing Indian film at the time, won six Filmfare awards including Best Director for Hirani, and influenced debates about education in India, China and South Korea. They reunited on PK (2014), a satire in which Aamir plays an alien questioning religious intermediaries; it drew protests from Hindu nationalist groups but became the first Indian film to gross more than ₹700 crore worldwide. Hirani later made Sanju and Dunki, and his partnership with Chopra ended after Sanju. His biography reports that a biopic of cricketer Lala Amarnath with Aamir Khan considered for the lead was in development as of 2025.</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-105; SOURCE-043</t>
+          <t>SOURCE-109; SOURCE-047; SOURCE-053; SOURCE-073</t>
         </is>
       </c>
       <c r="U32" s="5" t="inlineStr">
@@ -24084,27 +24076,29 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="139" customHeight="1">
+    <row r="33" ht="184" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>PERSON-032</t>
+          <t>PERSON-052</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Yash Raj Films</t>
+          <t>Rajkumar Santoshi</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Production banner</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="n"/>
+          <t>Director; screenwriter</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>1956</v>
+      </c>
       <c r="E33" s="18" t="n"/>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Founded 1970</t>
+          <t>1982–present</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -24114,61 +24108,65 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Founded by director Yash Chopra; led by Aditya Chopra, vice-chairman from 2010 and chairman after Yash Chopra's death in October 2012.</t>
+          <t>Son of filmmaker P. L. Santoshi; assistant director to Govind Nihalani on Vijeta (1982) and Ardh Satya (1983).</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Founded 1970.</t>
+          <t>Ghayal (1990), a blockbuster and critical success.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Dilwale Dulhania Le Jayenge (1995); Fanaa (2006); Ek Tha Tiger (2012); Dhoom 3 (2013); Thugs of Hindostan (2018)</t>
+          <t>Ghayal (1990); Damini (1993); Andaz Apna Apna (1994); Barsaat (1995); Ghatak (1996); Pukar (2000); The Legend of Bhagat Singh (2002); Khakee (2004); Ajab Prem Ki Ghazab Kahani (2009)</t>
         </is>
       </c>
       <c r="K33" s="19" t="inlineStr">
         <is>
-          <t>Romance, spectacle and action franchises</t>
-        </is>
-      </c>
-      <c r="L33" s="19" t="n"/>
+          <t>Women's rights (Damini, Lajja), national integration (Pukar), activism (Halla Bol); also broad comedy</t>
+        </is>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>Socially conscious action and courtroom drama, with a single foray into absurdist comedy that became a cult classic.</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Ranked by Filmfare in 2006 as one of India's most powerful production companies</t>
+          <t>Three National Film Awards; six Filmfare Awards for direction, screenplay, dialogue and story</t>
         </is>
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>One of Hindi cinema's dominant studios, known for landmark romances and, later, the Dhoom and spy franchises; also distributes other producers' films.</t>
+          <t>Credited with early mainstream feminist films addressing rape as a social issue.</t>
         </is>
       </c>
       <c r="O33" s="19" t="inlineStr">
         <is>
-          <t>Produced three Aamir Khan films; Yash Chopra had earlier directed him in Parampara (1993), a non-YRF production.</t>
+          <t>Directed Aamir Khan in the cult comedy Andaz Apna Apna, gave him a cameo in Damini, and directed Aamir Khan Productions' Lahore 1947, in which Aamir did not act.</t>
         </is>
       </c>
       <c r="P33" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>FILM-037; FILM-046; FILM-051</t>
+          <t>FILM-017; FILM-021</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>Dhoom 3 (2013)</t>
+          <t>Andaz Apna Apna (1994)</t>
         </is>
       </c>
       <c r="S33" s="5" t="inlineStr">
         <is>
-          <t>Yash Raj Films was founded in 1970 by director Yash Chopra and is led by his son Aditya Chopra, vice-chairman from 2010 and chairman after Yash Chopra's death in October 2012. The studio is known for landmark romances such as Dilwale Dulhania Le Jayenge and for action franchises including Dhoom and the spy universe begun with Ek Tha Tiger. Aamir Khan's association began before he worked for the banner: Yash Chopra directed him in Parampara (1993), produced by Firoz Nadiadwala. For YRF itself, Aditya and Yash Chopra produced Fanaa (2006), the first film shot at YRF Studios and a major success. Aditya Chopra then cast Aamir as the twin circus-performer thieves of Dhoom 3 (2013), which became the first Indian film to gross ₹500 crore worldwide, and as the con man Firangi in the period epic Thugs of Hindostan (2018), which set a record opening before collapsing commercially.</t>
+          <t>Rajkumar Santoshi, born in 1956, is the son of filmmaker P. L. Santoshi and trained as an assistant to Govind Nihalani on Vijeta and Ardh Satya. His debut, Ghayal (1990), was a blockbuster and critical success, and Damini (1993), a legal drama regarded as a cult feminist film, is widely considered his best. Aamir Khan appears as himself in a song in Damini, promoting their next project. That project, Andaz Apna Apna (1994), paired Aamir with Salman Khan as rival fortune-hunters in an absurdist comedy of mistaken identities. It flopped on release and was nominated for four Filmfare awards, then became a cult classic, voted the second-best Bollywood comedy in an Indian Express poll and re-released in a 4K restoration in 2025. Santoshi went on to Barsaat, Ghatak, Pukar, The Legend of Bhagat Singh, Khakee and Ajab Prem Ki Ghazab Kahani, and has won three National Film Awards and six Filmfare awards. His films are known for socially conscious narratives about women's rights, national integration and activism. He later directed Lahore 1947, produced by Aamir Khan Productions and starring Sunny Deol; it was released in August 2026 as Batwara 1947, with Aamir credited as producer rather than performer.</t>
         </is>
       </c>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-106; SOURCE-024; SOURCE-043; SOURCE-052; SOURCE-057</t>
+          <t>SOURCE-089; SOURCE-023; SOURCE-027; SOURCE-064</t>
         </is>
       </c>
       <c r="U33" s="5" t="inlineStr">
@@ -24177,97 +24175,91 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="154" customHeight="1">
+    <row r="34" ht="169" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>PERSON-033</t>
+          <t>PERSON-053</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>A. R. Murugadoss</t>
+          <t>Reema Kagti</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Director; writer</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="n">
-        <v>1974</v>
-      </c>
+          <t>Director; screenwriter</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="n"/>
       <c r="E34" s="18" t="n"/>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1997–present</t>
+          <t>2007–present</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Tamil; Telugu; Hindi</t>
+          <t>Hindi; streaming series</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Born in Kallakurichi, Tamil Nadu; studied at Bishop Heber College; assistant director on Ratchagan (1997) and Kushi (2000).</t>
+          <t>Assistant director on Lagaan, Dil Chahta Hai and Lakshya; associated with Excel Entertainment since its inception.</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Dheena (2001).</t>
+          <t>Honeymoon Travels Pvt. Ltd. (2007).</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Dheena (2001); Ramanaa (2002); Ghajini (Tamil, 2005); Stalin (2006); Ghajini (Hindi, 2008); 7 Aum Arivu (2011); Thuppakki (2012); Holiday (2014); Kaththi (2014); Sarkar (2018); Sikandar (2025); Madharaasi (2025)</t>
+          <t>Honeymoon Travels Pvt. Ltd. (2007); Zindagi Na Milegi Dobara (2011, co-writer); Talaash (2012); Dil Dhadakne Do (2015, co-writer); Gold (2018); Gully Boy (2019, co-writer); Made in Heaven (2019–); Dahaad (2023)</t>
         </is>
       </c>
       <c r="K34" s="19" t="inlineStr">
         <is>
-          <t>Action films built around social issues and vigilante justice</t>
-        </is>
-      </c>
-      <c r="L34" s="19" t="inlineStr">
-        <is>
-          <t>High-concept mass action with melodrama; remakes his Tamil hits in Hindi.</t>
-        </is>
-      </c>
+          <t>Genre films with character depth; female-led crime and social drama in series</t>
+        </is>
+      </c>
+      <c r="L34" s="19" t="n"/>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Award for Best Director – Tamil (Kaththi); Producers Guild Best Director (Ghajini)</t>
+          <t>Filmfare, IIFA and Zee Cine screenwriting awards</t>
         </is>
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>His Hindi Ghajini was the first Bollywood film to cross ₹100 crore nett in India, creating the '100 crore club'.</t>
+          <t>A leading woman director and writer; co-founded Tiger Baby Films with Zoya Akhtar in 2015.</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
         <is>
-          <t>Directed and co-wrote the Hindi Ghajini with Aamir Khan.</t>
+          <t>Assistant director on two of his 2001 films; later directed and co-wrote Talaash and co-wrote Dil Dhadakne Do.</t>
         </is>
       </c>
       <c r="P34" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>FILM-039</t>
+          <t>FILM-044; FILM-048</t>
         </is>
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>Ghajini (2008)</t>
+          <t>Talaash (2012)</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>A. R. Murugadoss was born in 1974 in Kallakurichi, Tamil Nadu, and trained as an assistant director on Ratchagan and on S. J. Surya's Kushi before his debut with Dheena (2001). Ramanaa (2002) and the Tamil Ghajini (2005), a revenge thriller about an amnesiac inspired by Memento, established him as a major action director. He remade Ghajini in Hindi in 2008, his Hindi debut, with Aamir Khan as the telecom tycoon who loses his short-term memory after witnessing his fiancée's murder. Aamir co-wrote the screenplay with Murugadoss. The film opened with record collections and became the first Hindi film to cross ₹100 crore nett in India, creating the industry's '100 crore club', though reviews were mixed about its length and violence. Murugadoss won the Producers Guild Best Director award. He returned to Tamil cinema with 7 Aum Arivu, Thuppakki, Kaththi, for which he won the Filmfare Best Director award (Tamil), and Sarkar, and made further Hindi films, Holiday (2014) and Sikandar (2025) with Salman Khan. His films typically wrap social issues into mass-market action.</t>
+          <t>Reema Kagti learned filmmaking as an assistant director on three of the key films of 2001–2004: Ashutosh Gowariker's Lagaan and Farhan Akhtar's Dil Chahta Hai, both starring Aamir Khan, and Lakshya. She has been associated with Excel Entertainment since its founding and made her directorial debut with Honeymoon Travels Pvt. Ltd. (2007). With Zoya Akhtar she became one of Hindi cinema's most successful screenwriting partnerships, co-writing Zindagi Na Milegi Dobara, Dil Dhadakne Do, in which Aamir voices the narrating dog, and Gully Boy. Her second feature, Talaash (2012), co-written with Akhtar and co-produced by Excel and Aamir Khan Productions, cast Aamir as a Mumbai police inspector grieving his drowned son while investigating a star's death that leads to a ghost story. It was critically acclaimed and a hit, though some critics found the twist derivative. Kagti went on to direct Gold (2018), co-found Tiger Baby Films with Zoya Akhtar in 2015 and create the series Made in Heaven and Dahaad. Her work with Aamir Khan runs from the sets of his 2001 films to one of his most interior later performances.</t>
         </is>
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-107; SOURCE-045</t>
+          <t>SOURCE-115; SOURCE-050; SOURCE-054</t>
         </is>
       </c>
       <c r="U34" s="5" t="inlineStr">
@@ -24276,97 +24268,93 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="184" customHeight="1">
+    <row r="35" ht="124" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>PERSON-034</t>
+          <t>PERSON-054</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Zoya Akhtar</t>
+          <t>Ronnie Screwvala</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Director; writer</t>
+          <t>Producer; production banner</t>
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>1972</v>
+        <v>1956</v>
       </c>
       <c r="E35" s="18" t="n"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2009–present</t>
+          <t>1981–present</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Hindi; streaming series</t>
+          <t>Hindi; media</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Daughter of Javed Akhtar and Honey Irani; trained at NYU's Tisch School of the Arts and assisted Mira Nair, Tony Gerber and Dev Benegal.</t>
+          <t>Ronnie Screwvala pioneered cable television in India in 1981 and founded UTV Software Communications, whose film arm was UTV Motion Pictures.</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Luck by Chance (2009), which won the Filmfare Best Debut Director award.</t>
+          <t>UTV Motion Pictures productions from the early 2000s.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Luck by Chance (2009); Zindagi Na Milegi Dobara (2011); Talaash (2012, co-writer); Bombay Talkies (2013, segment); Dil Dhadakne Do (2015); Gully Boy (2019); Made in Heaven (2019–2023); The Archies (2023)</t>
+          <t>Lakshya (2004); Swades (2004); Rang De Basanti (2006); Jodhaa Akbar (2008); Delhi Belly (2011); Barfi! (2012); later, as RSVP Movies, Kedarnath (2018) and Uri: The Surgical Strike (2019)</t>
         </is>
       </c>
       <c r="K35" s="19" t="inlineStr">
         <is>
-          <t>Privileged families and friendships under strain; the film industry; class and aspiration</t>
-        </is>
-      </c>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>Observational ensemble drama with wry humour, often co-written with Reema Kagti.</t>
-        </is>
-      </c>
+          <t>Ambitious mainstream and crossover films</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="n"/>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Four Filmfare Awards including Best Debut Director (Luck by Chance) and Best Director (Zindagi Na Milegi Dobara; Gully Boy); member of the Academy of Motion Picture Arts and Sciences</t>
+          <t>National Film Award for Best Popular Film (Rang De Basanti); Filmfare Best Film (Rang De Basanti; Jodhaa Akbar; Barfi!)</t>
         </is>
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>One of the most influential contemporary Hindi filmmakers; Gully Boy was India's Academy Award entry.</t>
+          <t>Built one of India's first corporate studios, sold to Disney in 2012 at an enterprise value of US$1.4 billion.</t>
         </is>
       </c>
       <c r="O35" s="19" t="inlineStr">
         <is>
-          <t>Four credits with Aamir Khan: his cameo in her debut, their co-written Talaash, the anthology whose song features him, and his narration in Dil Dhadakne Do.</t>
+          <t>Co-produced Rang De Basanti and Delhi Belly; UTV also distributed Dangal.</t>
         </is>
       </c>
       <c r="P35" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>FILM-040; FILM-044; FILM-045; FILM-048</t>
+          <t>FILM-036; FILM-043</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Talaash (2012)</t>
+          <t>Rang De Basanti (2006)</t>
         </is>
       </c>
       <c r="S35" s="5" t="inlineStr">
         <is>
-          <t>Zoya Akhtar was born in Mumbai in 1972 to Javed Akhtar and Honey Irani and is the sister of Farhan Akhtar. After a filmmaking diploma from NYU's Tisch School of the Arts she assisted Mira Nair, Tony Gerber and Dev Benegal. Her debut, Luck by Chance (2009), a critically acclaimed look at newcomers in Bollywood, features Aamir Khan among the industry figures playing themselves and won her the Filmfare Best Debut Director award. Zindagi Na Milegi Dobara (2011) brought her the Filmfare Best Director award. With her regular writing partner Reema Kagti she co-wrote the story and screenplay of Talaash (2012), a neo-noir ghost story with Aamir Khan as a grieving police inspector. She directed the 'Sheila Ki Jawaani' segment of the centenary anthology Bombay Talkies (2013), whose song 'Apna Bombay Talkies' features Aamir among many stars, and directed Dil Dhadakne Do (2015), in which Aamir voices Pluto, the dog who narrates the Mehra family's cruise. Gully Boy (2019) won her a second Filmfare Best Director award and was India's Academy Award entry. With Kagti she founded Tiger Baby Films in 2015 and created the series Made in Heaven, and she later directed The Archies. She is a member of the Academy.</t>
+          <t>Ronnie Screwvala, born in 1956, pioneered cable television in India in 1981 and built UTV Software Communications into a media group with partners including News Corp, Fox, Disney and Bloomberg. Its film arm, UTV Motion Pictures, produced prestige and commercial hits including Lakshya, Swades, Jodhaa Akbar and Barfi!. With Aamir Khan it co-produced Rang De Basanti (2006) with director Rakeysh Omprakash Mehra; Screwvala shared its Filmfare Best Film award, National Film Award for Best Popular Film and BAFTA nomination. UTV also co-produced Delhi Belly (2011) with Aamir Khan Productions, and UTV Motion Pictures distributed Dangal in 2016. Screwvala sold UTV to Disney in 2012 and later founded RSVP Movies, which made Kedarnath and Uri: The Surgical Strike.</t>
         </is>
       </c>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-108; SOURCE-046; SOURCE-050; SOURCE-051; SOURCE-054</t>
+          <t>SOURCE-104; SOURCE-042; SOURCE-049; SOURCE-055</t>
         </is>
       </c>
       <c r="U35" s="5" t="inlineStr">
@@ -24375,74 +24363,74 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="184" customHeight="1">
+    <row r="36" ht="169" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>PERSON-035</t>
+          <t>PERSON-057</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Hirani</t>
+          <t>Shantanu Moitra</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Director; writer; editor</t>
+          <t>Music director (songs and background score)</t>
         </is>
       </c>
       <c r="D36" s="17" t="n">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="E36" s="18" t="n"/>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>1991–present</t>
+          <t>1995–present</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Hindi; Bengali</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Studied film editing at FTII on a scholarship; directed and produced advertising films; edited Mission Kashmir (2000) and promos for Vidhu Vinod Chopra.</t>
+          <t>Composed advertising jingles, including the Uncle Chipps campaign, and Indipop albums with Shubha Mudgal; moved to Mumbai in 2002 for Hazaaron Khwaishein Aisi.</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Munna Bhai M.B.B.S. (2003), which won the National Film Award for Best Popular Film.</t>
+          <t>Breakthrough with Parineeta (2005), which won the Filmfare R. D. Burman Award.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Munna Bhai M.B.B.S. (2003); Lage Raho Munna Bhai (2006); 3 Idiots (2009); PK (2014); Sanju (2018); Dunki (2023)</t>
+          <t>Hazaaron Khwaishein Aisi (2005); Parineeta (2005); Lage Raho Munna Bhai (2006); 3 Idiots (2009); Madras Cafe (2013); PK (2014); Pink (2016); October (2018)</t>
         </is>
       </c>
       <c r="K36" s="19" t="inlineStr">
         <is>
-          <t>Social critique through comedy: medicine, Gandhian values, education, religious exploitation, immigration</t>
+          <t>Emotionally resonant, character-driven scores</t>
         </is>
       </c>
       <c r="L36" s="19" t="inlineStr">
         <is>
-          <t>Warm, humane comedy with emotional climaxes; edits his own films; long partnership with writer Abhijat Joshi.</t>
+          <t>A pianist's melodic sensibility, moving easily between songs and understated background scores.</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Four National Film Awards for Best Popular Film; 11 Filmfare Awards including Best Film and Best Director (3 Idiots)</t>
+          <t>National Film Award for Best Music Direction (Background Score) (Na Bangaaru Talli, 2013); Filmfare Best Background Score (Sardar Udham, 2022); IIFA Best Background Score (3 Idiots)</t>
         </is>
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>One of Hindi cinema's most successful directors; 3 Idiots and PK each became the highest-grossing Indian film on release.</t>
+          <t>Hirani's regular composer and a key figure in elevating the background score in contemporary Hindi cinema.</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in two record-breaking films; a Lala Amarnath biopic was reported as a possible third collaboration.</t>
+          <t>Composed the music for both Hirani films starring Aamir Khan.</t>
         </is>
       </c>
       <c r="P36" s="17" t="n">
@@ -24460,12 +24448,12 @@
       </c>
       <c r="S36" s="5" t="inlineStr">
         <is>
-          <t>Rajkumar Hirani, born in 1962, studied film editing at FTII and built a career in advertising before editing Vidhu Vinod Chopra's Mission Kashmir (2000). Chopra produced his directorial debut, Munna Bhai M.B.B.S. (2003), which won the National Film Award for Best Popular Film, and its sequel Lage Raho Munna Bhai (2006). Hirani edits all his own films and writes with Abhijat Joshi, blending social commentary with comedy and emotion. His first film with Aamir Khan, 3 Idiots (2009), loosely adapted from Chetan Bhagat's Five Point Someone, cast Aamir as Rancho, a brilliant student who defies an education system built on rote learning. It became the highest-grossing Indian film at the time, won six Filmfare awards including Best Director for Hirani, and influenced debates about education in India, China and South Korea. They reunited on PK (2014), a satire in which Aamir plays an alien questioning religious intermediaries; it drew protests from Hindu nationalist groups but became the first Indian film to gross more than ₹700 crore worldwide. Hirani later made Sanju and Dunki, and his partnership with Chopra ended after Sanju. His biography reports that a biopic of cricketer Lala Amarnath with Aamir Khan considered for the lead was in development as of 2025.</t>
+          <t>Shantanu Moitra, born in 1968, began in advertising, writing jingles such as the Uncle Chipps campaign, and composed Indipop albums including Ab Ke Saawan with singer Shubha Mudgal. He moved to Mumbai in 2002 to score Hazaaron Khwaishein Aisi, and his songs for Parineeta (2005) won the Filmfare R. D. Burman Award for New Music Talent. His association with Rajkumar Hirani began with Lage Raho Munna Bhai (2006) and continued with 3 Idiots (2009), for which he composed the songs and co-composed the background score. With Swanand Kirkire's lyrics, songs such as 'Zoobi Doobi' and 'All Izz Well' became hugely popular, and the score won the IIFA award. He was one of three song composers on PK (2014), whose background score was by Sanjay Wandrekar and Atul Raninga. Beyond these films, Moitra scored Madras Cafe, Pink and October, won the National Film Award for the background score of the Telugu Na Bangaaru Talli and the Filmfare Best Background Score award for Sardar Udham. His restrained, melody-driven work kept the emotional register of Aamir Khan's two biggest comedies warm rather than broad.</t>
         </is>
       </c>
       <c r="T36" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-109; SOURCE-047; SOURCE-053; SOURCE-073</t>
+          <t>SOURCE-111; SOURCE-047; SOURCE-053</t>
         </is>
       </c>
       <c r="U36" s="5" t="inlineStr">
@@ -24477,12 +24465,12 @@
     <row r="37" ht="109" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>PERSON-036</t>
+          <t>PERSON-062</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Vidhu Vinod Chopra (Vinod Chopra Films)</t>
+          <t>Vidhu Vinod Chopra</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -24572,71 +24560,65 @@
     <row r="38" ht="169" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>PERSON-037</t>
+          <t>PERSON-063</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Shantanu Moitra</t>
+          <t>Vijay Krishna Acharya</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Music director (songs and background score)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="n">
-        <v>1968</v>
-      </c>
+          <t>Director; writer</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="n"/>
       <c r="E38" s="18" t="n"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>1995–present</t>
+          <t>2004–present</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Hindi; Bengali</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>Composed advertising jingles, including the Uncle Chipps campaign, and Indipop albums with Shubha Mudgal; moved to Mumbai in 2002 for Hazaaron Khwaishein Aisi.</t>
+          <t>Born in Kanpur; educated at Kirori Mal College; married to Anusheh Khan, sister of director Kabir Khan.</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Breakthrough with Parineeta (2005), which won the Filmfare R. D. Burman Award.</t>
+          <t>Wrote the screenplays and dialogue of Dhoom (2004) and Dhoom 2 (2006); directorial debut Tashan (2008), which opened to negative reviews.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Hazaaron Khwaishein Aisi (2005); Parineeta (2005); Lage Raho Munna Bhai (2006); 3 Idiots (2009); Madras Cafe (2013); PK (2014); Pink (2016); October (2018)</t>
+          <t>Dhoom (2004, writer); Dhoom 2 (2006, writer); Tashan (2008); Dhoom 3 (2013); Thugs of Hindostan (2018)</t>
         </is>
       </c>
       <c r="K38" s="19" t="inlineStr">
         <is>
-          <t>Emotionally resonant, character-driven scores</t>
-        </is>
-      </c>
-      <c r="L38" s="19" t="inlineStr">
-        <is>
-          <t>A pianist's melodic sensibility, moving easily between songs and understated background scores.</t>
-        </is>
-      </c>
+          <t>Large-scale action spectacle and heist</t>
+        </is>
+      </c>
+      <c r="L38" s="19" t="n"/>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Best Music Direction (Background Score) (Na Bangaaru Talli, 2013); Filmfare Best Background Score (Sardar Udham, 2022); IIFA Best Background Score (3 Idiots)</t>
+          <t>Telstra People's Choice Award, Indian Film Festival of Melbourne 2014 (Dhoom 3)</t>
         </is>
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Hirani's regular composer and a key figure in elevating the background score in contemporary Hindi cinema.</t>
+          <t>Dhoom 3 set international box-office records for Hindi cinema on release.</t>
         </is>
       </c>
       <c r="O38" s="19" t="inlineStr">
         <is>
-          <t>Composed the music for both Hirani films starring Aamir Khan.</t>
+          <t>Directed Aamir Khan in two Yash Raj spectacles, one record-breaking and one a costly failure.</t>
         </is>
       </c>
       <c r="P38" s="17" t="n">
@@ -24644,22 +24626,22 @@
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>FILM-041; FILM-047</t>
+          <t>FILM-046; FILM-051</t>
         </is>
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>3 Idiots (2009)</t>
+          <t>Dhoom 3 (2013)</t>
         </is>
       </c>
       <c r="S38" s="5" t="inlineStr">
         <is>
-          <t>Shantanu Moitra, born in 1968, began in advertising, writing jingles such as the Uncle Chipps campaign, and composed Indipop albums including Ab Ke Saawan with singer Shubha Mudgal. He moved to Mumbai in 2002 to score Hazaaron Khwaishein Aisi, and his songs for Parineeta (2005) won the Filmfare R. D. Burman Award for New Music Talent. His association with Rajkumar Hirani began with Lage Raho Munna Bhai (2006) and continued with 3 Idiots (2009), for which he composed the songs and co-composed the background score. With Swanand Kirkire's lyrics, songs such as 'Zoobi Doobi' and 'All Izz Well' became hugely popular, and the score won the IIFA award. He was one of three song composers on PK (2014), whose background score was by Sanjay Wandrekar and Atul Raninga. Beyond these films, Moitra scored Madras Cafe, Pink and October, won the National Film Award for the background score of the Telugu Na Bangaaru Talli and the Filmfare Best Background Score award for Sardar Udham. His restrained, melody-driven work kept the emotional register of Aamir Khan's two biggest comedies warm rather than broad.</t>
+          <t>Vijay Krishna Acharya, from Kanpur, studied at Kirori Mal College and entered films as the screenwriter and dialogue writer of Yash Raj Films' Dhoom (2004) and Dhoom 2 (2006). His directorial debut, Tashan (2008), opened to negative reviews. Aditya Chopra nevertheless gave him Dhoom 3 (2013), which Acharya wrote and directed, with Aamir Khan in a double role as twin circus performers robbing the Chicago bank that ruined their father. The film grossed about ₹400 crore worldwide in ten days, became the first Indian film to pass ₹500 crore and won the inaugural Telstra People's Choice Award at the Indian Film Festival of Melbourne, though Indian reviews were mixed. Acharya and Aamir reunited on Thugs of Hindostan (2018), which Acharya wrote and directed, with Aamir as the double-crossing con man Firangi Mallah opposite Amitabh Bachchan. It had the biggest opening day for a Hindi film to that point but was widely panned in India, criticised for its direction, writing and length, and became an expensive disappointment. The contrasting fortunes of these two films bracket the most commercially extreme stretch of Aamir Khan's later career.</t>
         </is>
       </c>
       <c r="T38" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-111; SOURCE-047; SOURCE-053</t>
+          <t>SOURCE-117; SOURCE-052; SOURCE-057</t>
         </is>
       </c>
       <c r="U38" s="5" t="inlineStr">
@@ -24668,93 +24650,97 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="124" customHeight="1">
+    <row r="39" ht="154" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>PERSON-038</t>
+          <t>PERSON-067</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Abhijat Joshi</t>
+          <t>A. R. Murugadoss</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Screenwriter</t>
+          <t>Director; writer</t>
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>1969</v>
+        <v>1974</v>
       </c>
       <c r="E39" s="18" t="n"/>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>1998–2023</t>
+          <t>1997–present</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil; Telugu; Hindi</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Playwright and professor of English at Otterbein University, Ohio, since 2003.</t>
+          <t>Born in Kallakurichi, Tamil Nadu; studied at Bishop Heber College; assistant director on Ratchagan (1997) and Kushi (2000).</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Kareeb (1998) and Mission Kashmir (2000) for Vidhu Vinod Chopra.</t>
+          <t>Dheena (2001).</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Mission Kashmir (2000); Lage Raho Munna Bhai (2006); 3 Idiots (2009); PK (2014); Sanju (2018); Shikara (2020); Dunki (2023)</t>
+          <t>Dheena (2001); Ramanaa (2002); Ghajini (Tamil, 2005); Stalin (2006); Ghajini (Hindi, 2008); 7 Aum Arivu (2011); Thuppakki (2012); Holiday (2014); Kaththi (2014); Sarkar (2018); Sikandar (2025); Madharaasi (2025)</t>
         </is>
       </c>
       <c r="K39" s="19" t="inlineStr">
         <is>
-          <t>Moral questions dramatised through comedy and emotion</t>
-        </is>
-      </c>
-      <c r="L39" s="19" t="n"/>
+          <t>Action films built around social issues and vigilante justice</t>
+        </is>
+      </c>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>High-concept mass action with melodrama; remakes his Tamil hits in Hindi.</t>
+        </is>
+      </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Best Screenplay (Lage Raho Munna Bhai); Filmfare story, screenplay and dialogue awards (2007, 2010, 2015)</t>
+          <t>Filmfare Award for Best Director – Tamil (Kaththi); Producers Guild Best Director (Ghajini)</t>
         </is>
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Rajkumar Hirani's principal co-writer; their partnership holds records for IIFA Best Dialogue.</t>
+          <t>His Hindi Ghajini was the first Bollywood film to cross ₹100 crore nett in India, creating the '100 crore club'.</t>
         </is>
       </c>
       <c r="O39" s="19" t="inlineStr">
         <is>
-          <t>Co-wrote both Hirani films starring Aamir Khan, winning Filmfare writing awards for each.</t>
+          <t>Directed and co-wrote the Hindi Ghajini with Aamir Khan.</t>
         </is>
       </c>
       <c r="P39" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>FILM-041; FILM-047</t>
+          <t>FILM-039</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>3 Idiots (2009)</t>
+          <t>Ghajini (2008)</t>
         </is>
       </c>
       <c r="S39" s="5" t="inlineStr">
         <is>
-          <t>Abhijat Joshi, born in 1969, is a playwright and has taught English at Otterbein University in Ohio since 2003, writing Hindi films alongside his academic career. His screen credits began with Kareeb (1998) and Mission Kashmir (2000) for Vidhu Vinod Chopra, and include Eklavya: The Royal Guard, Broken Horses, Wazir and Shikara. He is best known as Rajkumar Hirani's co-writer: Lage Raho Munna Bhai won him the National Film Award for Best Screenplay, and their dialogue collaborations hold records at the IIFA Awards. With Hirani he co-wrote 3 Idiots (2009), sharing the Filmfare awards for Best Story, Screenplay and Dialogue, and PK (2014), sharing the Best Screenplay award; he is also credited on Nanban (2012), the Tamil remake of 3 Idiots. The partnership continued with Sanju (2018) and Dunki (2023).</t>
+          <t>A. R. Murugadoss was born in 1974 in Kallakurichi, Tamil Nadu, and trained as an assistant director on Ratchagan and on S. J. Surya's Kushi before his debut with Dheena (2001). Ramanaa (2002) and the Tamil Ghajini (2005), a revenge thriller about an amnesiac inspired by Memento, established him as a major action director. He remade Ghajini in Hindi in 2008, his Hindi debut, with Aamir Khan as the telecom tycoon who loses his short-term memory after witnessing his fiancée's murder. Aamir co-wrote the screenplay with Murugadoss. The film opened with record collections and became the first Hindi film to cross ₹100 crore nett in India, creating the industry's '100 crore club', though reviews were mixed about its length and violence. Murugadoss won the Producers Guild Best Director award. He returned to Tamil cinema with 7 Aum Arivu, Thuppakki, Kaththi, for which he won the Filmfare Best Director award (Tamil), and Sarkar, and made further Hindi films, Holiday (2014) and Sikandar (2025) with Salman Khan. His films typically wrap social issues into mass-market action.</t>
         </is>
       </c>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-112; SOURCE-047; SOURCE-053; SOURCE-073; SOURCE-109</t>
+          <t>SOURCE-107; SOURCE-045</t>
         </is>
       </c>
       <c r="U39" s="5" t="inlineStr">
@@ -24766,12 +24752,12 @@
     <row r="40" ht="169" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>PERSON-039</t>
+          <t>PERSON-071</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Kiran Rao</t>
+          <t>Aditya Bhattacharya</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -24780,12 +24766,12 @@
         </is>
       </c>
       <c r="D40" s="17" t="n">
-        <v>1973</v>
+        <v>1965</v>
       </c>
       <c r="E40" s="18" t="n"/>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2001–present</t>
+          <t>1983–present</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -24795,65 +24781,65 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Born in Bangalore and raised in Calcutta; studied economics at Sophia College and mass communication at Jamia Millia Islamia; assistant director on Lagaan, Monsoon Wedding and Swades.</t>
+          <t>Son of filmmaker Basu Bhattacharya and Rinki Bhattacharya, and grandson of Bimal Roy; began as an actor.</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Directorial debut Dhobi Ghat (2011); earlier associate producer of Jaane Tu... Ya Jaane Na (2008).</t>
+          <t>Raakh (1989), which won three National Film Awards and the BFJA Best Directorial Debut award but underperformed commercially.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Jaane Tu... Ya Jaane Na (2008, associate producer); Peepli Live (2010); Dhobi Ghat (2011); Delhi Belly (2011); Talaash (2012); Dangal (2016); Secret Superstar (2017); Laal Singh Chaddha (2022); Laapataa Ladies (2024)</t>
+          <t>Raakh (1989); Dubai Return (2005); Bombay's Most Wanted (2012)</t>
         </is>
       </c>
       <c r="K40" s="19" t="inlineStr">
         <is>
-          <t>Loneliness and class in the city; women's lives and small-town India</t>
+          <t>Urban crime, violence and moral corrosion</t>
         </is>
       </c>
       <c r="L40" s="19" t="inlineStr">
         <is>
-          <t>Intimate, observational filmmaking as director; producer of mainstream and independent films at Aamir Khan Productions.</t>
+          <t>Stylised, low-budget urban noir; Raakh gave cinematographer Santosh Sivan and editor A. Sreekar Prasad their Bollywood debuts.</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Laapataa Ladies selected as India's entry for the 97th Academy Awards; Dhobi Ghat longlisted for a BAFTA</t>
+          <t>Three National Film Awards for Raakh (to its cast and crew); Bengal Film Journalists' Association Best Directorial Debut</t>
         </is>
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Chairperson of the Mumbai Film Festival (MAMI) from 2015 and co-founder of the Paani Foundation.</t>
+          <t>Raakh has a cult following as an early, dark counterpoint to the romantic films that made Aamir Khan a star.</t>
         </is>
       </c>
       <c r="O40" s="19" t="inlineStr">
         <is>
-          <t>Former wife (married December 2005, divorced July 2021); directed him in Dhobi Ghat and co-produced five more of his films.</t>
+          <t>Directed Aamir Khan in the anti-hero role he filmed before Qayamat Se Qayamat Tak.</t>
         </is>
       </c>
       <c r="P40" s="17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>FILM-042; FILM-043; FILM-044; FILM-049; FILM-050; FILM-053</t>
+          <t>FILM-005</t>
         </is>
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>Dhobi Ghat (2011)</t>
+          <t>Raakh (1989)</t>
         </is>
       </c>
       <c r="S40" s="5" t="inlineStr">
         <is>
-          <t>Kiran Rao was born in Bangalore in 1973 and grew up in Calcutta. She studied economics at Sophia College and mass communication at Jamia Millia Islamia's AJK Mass Communication Research Centre before working as an assistant director on Lagaan, where she met Aamir Khan, and on Mira Nair's Monsoon Wedding and Ashutosh Gowariker's Swades. She also appears briefly in Dil Chahta Hai. She married Aamir Khan in December 2005; their son Azad was born in 2011, and they divorced in July 2021 while continuing to work together. At Aamir Khan Productions she was associate producer on Jaane Tu... Ya Jaane Na and producer of Peepli Live, Delhi Belly, Talaash, Dangal, Secret Superstar and Laal Singh Chaddha. Her directorial debut, Dhobi Ghat (2011), which she wrote, follows four Mumbai lives, with Aamir as Arun, a reclusive painter haunted by a former tenant's video diaries. It premiered at the Toronto festival, drew strong reviews and was longlisted for a BAFTA. Her second feature, Laapataa Ladies (2024), was India's entry for the 97th Academy Awards. She has chaired the Mumbai Film Festival since 2015 and co-founded the non-profit Paani Foundation in 2016.</t>
+          <t>Aditya Bhattacharya, born in 1965, comes from one of Hindi cinema's best-known film families: he is the son of director Basu Bhattacharya and writer Rinki Bhattacharya, and the grandson of Bimal Roy. He started out as an actor before turning to direction. His debut, Raakh (1989), co-written with Nuzhat Khan, is a stylish crime drama in which Aamir Khan plays a young man who turns vigilante after his girlfriend is raped by a crime boss, guided by a disillusioned policeman played by Pankaj Kapur. Shot before Qayamat Se Qayamat Tak but released after it, the film underperformed commercially but won three National Film Awards: Best Supporting Actor for Pankaj Kapur, Best Editing for A. Sreekar Prasad, and a Special Mention for Aamir Khan covering both his 1988–89 performances. Bhattacharya won the Bengal Film Journalists' Association award for Best Directorial Debut, and the film's photography marked Santosh Sivan's Bollywood debut. Raakh has since built a cult following. Bhattacharya's later films include Dubai Return (2005), with Irrfan Khan and Divya Dutta, which premiered at IFFI Goa, and Bombay's Most Wanted (2012). He divides his time between Barcelona and Mumbai.</t>
         </is>
       </c>
       <c r="T40" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-113; SOURCE-048; SOURCE-049; SOURCE-050; SOURCE-055; SOURCE-056; SOURCE-059</t>
+          <t>SOURCE-081; SOURCE-008; SOURCE-067</t>
         </is>
       </c>
       <c r="U40" s="5" t="inlineStr">
@@ -24862,97 +24848,97 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="154" customHeight="1">
+    <row r="41" ht="184" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>PERSON-040</t>
+          <t>PERSON-104</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Ram Sampath</t>
+          <t>Deepa Mehta</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Music director (songs and background score)</t>
+          <t>Director; writer; producer</t>
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>1977</v>
+        <v>1950</v>
       </c>
       <c r="E41" s="18" t="n"/>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>1997–2017; 2023–present</t>
+          <t>1976–present</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Canadian; Hindi; English</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Composed advertising jingles in Mumbai before moving into pop albums and film music.</t>
+          <t>Born in Amritsar; studied philosophy at Lady Shri Ram College; emigrated to Canada in 1973 and co-founded Sunrise Films.</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Film work includes Khakee (2004); breakthrough with Delhi Belly (2011).</t>
+          <t>Feature debut Sam &amp; Me (1991), followed by Camilla (1994).</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Khakee (2004); Delhi Belly (2011); Talaash (2012); Satyamev Jayate (2012, television); Raees (2017); Laapataa Ladies (2024); Sitaare Zameen Par (2025, background score)</t>
+          <t>Fire (1996); Earth (1998); Bollywood/Hollywood (2002); Water (2005); Heaven on Earth (2008); Midnight's Children (2012); Funny Boy (2020)</t>
         </is>
       </c>
       <c r="K41" s="19" t="inlineStr">
         <is>
-          <t>Contemporary rock-inflected soundtracks and socially themed music</t>
+          <t>Partition, sectarian violence, gender, sexuality and the lives of marginalised women; Indian-Canadian identity</t>
         </is>
       </c>
       <c r="L41" s="19" t="inlineStr">
         <is>
-          <t>Versatile composer moving between advertising, pop and film with contemporary rock elements.</t>
+          <t>Transnational art cinema examining how politics and patriarchy shape ordinary lives.</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Filmfare Best Music Director and Best Background Score (Laapataa Ladies, 2025)</t>
+          <t>Academy Award nomination (Water); Genie Award for Best Original Screenplay; Governor General's Performing Arts Award (2012); Officer of the Order of Canada (2013); Canadian Screen Award for Best Director (2021)</t>
         </is>
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Won a landmark 2008 plagiarism case over Krazzy 4, an important precedent for composers' rights in India.</t>
+          <t>A pioneering Canadian woman filmmaker whose Elements trilogy provoked protests in India and international acclaim.</t>
         </is>
       </c>
       <c r="O41" s="19" t="inlineStr">
         <is>
-          <t>Aamir Khan Productions' regular composer: Delhi Belly, Talaash, the Satyamev Jayate television show and the Sitaare Zameen Par score.</t>
+          <t>Directed Aamir Khan in Earth, one of his darkest and most praised roles.</t>
         </is>
       </c>
       <c r="P41" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>FILM-043; FILM-044; FILM-055</t>
+          <t>FILM-031</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>Talaash (2012)</t>
+          <t>Earth (1998)</t>
         </is>
       </c>
       <c r="S41" s="5" t="inlineStr">
         <is>
-          <t>Ram Sampath, born in 1977, began in Mumbai's advertising industry and moved into pop albums and films, including Khakee (2004). In 2008 he won a plagiarism case against the makers of Krazzy 4, a significant precedent for composers in India. His breakthrough came with Delhi Belly (2011), produced by Aamir Khan Productions, whose 'Bhaag D.K. Bose' became an internet sensation and controversy; Aamir appears in the film's closing-credits song. He scored Talaash (2012), the Aamir Khan Productions and Excel thriller starring Aamir, with lyrics by Javed Akhtar, and composed the music of Aamir's television series Satyamev Jayate, including its title track. After a break he returned with Laapataa Ladies, directed by Kiran Rao, which won him the Filmfare awards for Best Music Director and Best Background Score, and composed the background score for Sitaare Zameen Par (2025), whose songs are by Shankar–Ehsaan–Loy. His career is closely tied to Aamir Khan's production company in the 2010s and 2020s.</t>
+          <t>Deepa Mehta was born in Amritsar in 1950, grew up aware of the scars of Partition, and studied philosophy at Lady Shri Ram College before moving to Canada in 1973. There she co-founded Sunrise Films, directed television, and made her feature debut with Sam &amp; Me (1991). Her Elements trilogy made her internationally known: Fire (1996), about two sisters-in-law in love, drew protests from Hindu fundamentalist groups; Water (2005), about child widows, had to be shot in Sri Lanka and was nominated for the Academy Award. Between them came Earth (1998), adapted from Bapsi Sidhwa's novel Ice Candy Man and seen through a young girl's eyes in 1947 Lahore. Aamir Khan plays Dil Navaz, the ice-candy seller whose rejected love for the nanny Shanta and the horror of Partition massacres turn him into her betrayer. Rediff called it probably the best performance of his life, and the film was India's submission for the Academy Award. Mehta's later work includes Bollywood/Hollywood, Heaven on Earth, Midnight's Children with Salman Rushdie and Funny Boy, which won the Canadian Screen Award for Best Director. She is an Officer of the Order of Canada. Earth is the only film in which Aamir Khan's romantic persona turns fully destructive.</t>
         </is>
       </c>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-114; SOURCE-049; SOURCE-050; SOURCE-061</t>
+          <t>SOURCE-098; SOURCE-035</t>
         </is>
       </c>
       <c r="U41" s="5" t="inlineStr">
@@ -24961,91 +24947,95 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="169" customHeight="1">
+    <row r="42" ht="184" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>PERSON-041</t>
+          <t>PERSON-128</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Reema Kagti</t>
+          <t>John Matthew Matthan</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Director; screenwriter</t>
+          <t>Director; producer; writer (Cinematt Pictures)</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
       <c r="E42" s="18" t="n"/>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2007–present</t>
+          <t>1999–2013</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Hindi; streaming series</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Assistant director on Lagaan, Dil Chahta Hai and Lakshya; associated with Excel Entertainment since its inception.</t>
+          <t>Assistant director on Richard Attenborough's Gandhi (1982) and to Govind Nihalani; later an advertising director who set up Cinematt Pictures in the early 1990s.</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Honeymoon Travels Pvt. Ltd. (2007).</t>
+          <t>Sarfarosh (1999), developed from 1992 over seven years of research and production.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Honeymoon Travels Pvt. Ltd. (2007); Zindagi Na Milegi Dobara (2011, co-writer); Talaash (2012); Dil Dhadakne Do (2015, co-writer); Gold (2018); Gully Boy (2019, co-writer); Made in Heaven (2019–); Dahaad (2023)</t>
+          <t>Sarfarosh (1999); Shikhar (2005); A New Love Ishtory (2013)</t>
         </is>
       </c>
       <c r="K42" s="19" t="inlineStr">
         <is>
-          <t>Genre films with character depth; female-led crime and social drama in series</t>
-        </is>
-      </c>
-      <c r="L42" s="19" t="n"/>
+          <t>Terrorism, policing and national security; social themes such as brain drain</t>
+        </is>
+      </c>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>Meticulously researched realism within a commercial thriller format; praised for characterisation.</t>
+        </is>
+      </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Filmfare, IIFA and Zee Cine screenwriting awards</t>
+          <t>National Film Award for Best Popular Film; Filmfare Best Film (Critics) and Best Screenplay; Screen Most Promising Debut Director (all for Sarfarosh); jury chair at IFFI 2021</t>
         </is>
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>A leading woman director and writer; co-founded Tiger Baby Films with Zoya Akhtar in 2015.</t>
+          <t>Sarfarosh is regarded as a landmark 1990s thriller that married serious themes to commercial filmmaking.</t>
         </is>
       </c>
       <c r="O42" s="19" t="inlineStr">
         <is>
-          <t>Assistant director on two of his 2001 films; later directed and co-wrote Talaash and co-wrote Dil Dhadakne Do.</t>
+          <t>Directed Sarfarosh, one of Aamir Khan's most acclaimed performances of the 1990s.</t>
         </is>
       </c>
       <c r="P42" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>FILM-044; FILM-048</t>
+          <t>FILM-029</t>
         </is>
       </c>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>Talaash (2012)</t>
+          <t>Sarfarosh (1999)</t>
         </is>
       </c>
       <c r="S42" s="5" t="inlineStr">
         <is>
-          <t>Reema Kagti learned filmmaking as an assistant director on three of the key films of 2001–2004: Ashutosh Gowariker's Lagaan and Farhan Akhtar's Dil Chahta Hai, both starring Aamir Khan, and Lakshya. She has been associated with Excel Entertainment since its founding and made her directorial debut with Honeymoon Travels Pvt. Ltd. (2007). With Zoya Akhtar she became one of Hindi cinema's most successful screenwriting partnerships, co-writing Zindagi Na Milegi Dobara, Dil Dhadakne Do, in which Aamir voices the narrating dog, and Gully Boy. Her second feature, Talaash (2012), co-written with Akhtar and co-produced by Excel and Aamir Khan Productions, cast Aamir as a Mumbai police inspector grieving his drowned son while investigating a star's death that leads to a ghost story. It was critically acclaimed and a hit, though some critics found the twist derivative. Kagti went on to direct Gold (2018), co-found Tiger Baby Films with Zoya Akhtar in 2015 and create the series Made in Heaven and Dahaad. Her work with Aamir Khan runs from the sets of his 2001 films to one of his most interior later performances.</t>
+          <t>John Matthew Matthan began his career as an assistant director on Richard Attenborough's Gandhi (1982) and with Govind Nihalani before becoming an advertising director and founding Cinematt Pictures in Mumbai in the early 1990s. He started developing Sarfarosh in 1992 and spent seven years on research, pre-production and production. Released in 1999, the thriller cast Aamir Khan as ACP Ajay Singh Rathod, a policeman whose family was shattered by terrorism, investigating an arms network run by his admired friend, Gulfam Hassan, played by Naseeruddin Shah. Filmfare's reviewer credited Matthan with drawing perfectly crafted performances from the whole cast, and Rediff praised the film for marrying serious and commercial cinema. Sarfarosh won the National Film Award for Best Popular Film, Filmfare's Critics' Award for Best Film and Best Screenplay for Matthan, and the Screen Award for Most Promising Debut Director. It also brought Aamir a Zee Cine Best Actor award. Matthan's later projects were slower: Shikhar (2005) was reworked after 9/11 made its brain-drain theme less relevant, and A New Love Ishtory, completed in 2009, was delayed until 2013. He chaired the feature-film jury at IFFI in 2021.</t>
         </is>
       </c>
       <c r="T42" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-115; SOURCE-050; SOURCE-054</t>
+          <t>SOURCE-097; SOURCE-036; SOURCE-069</t>
         </is>
       </c>
       <c r="U42" s="5" t="inlineStr">
@@ -25054,29 +25044,29 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="169" customHeight="1">
+    <row r="43" ht="154" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>PERSON-042</t>
+          <t>PERSON-142</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Amit Trivedi</t>
+          <t>Kunal Kohli</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Music director (song composer)</t>
+          <t>Director; dialogue writer</t>
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="E43" s="18" t="n"/>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2001–present</t>
+          <t>Late 1990s–present</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -25086,65 +25076,65 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Born in Mumbai; formed Om the Fusion Band in college and composed for theatre, television, Marathi films and advertising.</t>
+          <t>Film critic in the late 1990s; hosted Chalo Cinema on EL TV and directed about 24 music videos.</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Aamir (2008); breakthrough with Dev.D (2009).</t>
+          <t>Mujhse Dosti Karoge! (2002), a commercial failure; breakthrough with Hum Tum (2004).</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Dev.D (2009); Wake Up Sid (2009); Udaan (2010); Lootera (2013); Bombay Talkies (2013); Queen (2014); Udta Punjab (2016); Secret Superstar (2017); Andhadhun (2018)</t>
+          <t>Mujhse Dosti Karoge! (2002); Hum Tum (2004); Fanaa (2006); Thoda Pyaar Thoda Magic (2008); Break Ke Baad (2010, producer); Teri Meri Kahaani (2012)</t>
         </is>
       </c>
       <c r="K43" s="19" t="inlineStr">
         <is>
-          <t>Indie-pop soundtracks for new-wave Hindi films</t>
+          <t>Romantic comedy and romantic thriller</t>
         </is>
       </c>
       <c r="L43" s="19" t="inlineStr">
         <is>
-          <t>Inventive indie-pop blending electronic and traditional sounds.</t>
+          <t>Glossy romantic films with prominent music, made largely with Yash Raj Films.</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>National Film Award for Best Music Direction (Dev.D); Filmfare R. D. Burman Award (2010)</t>
+          <t>Filmfare Best Director (Hum Tum)</t>
         </is>
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>A defining composer of the independent-minded Hindi cinema of the 2010s.</t>
+          <t>A leading director of mainstream romantic films in the mid-2000s.</t>
         </is>
       </c>
       <c r="O43" s="19" t="inlineStr">
         <is>
-          <t>Composed Bombay Talkies, including the song in which Aamir Khan appears, and Secret Superstar.</t>
+          <t>Directed and wrote the dialogue for Fanaa, pairing Aamir Khan with Kajol.</t>
         </is>
       </c>
       <c r="P43" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>FILM-045; FILM-050</t>
+          <t>FILM-037</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>Secret Superstar (2017)</t>
+          <t>Fanaa (2006)</t>
         </is>
       </c>
       <c r="S43" s="5" t="inlineStr">
         <is>
-          <t>Amit Trivedi, born in Mumbai in 1979, formed Om the Fusion Band in college and composed for Hindi and Gujarati theatre, television, Marathi films and advertising jingles for brands such as McDonald's and Airtel before his film debut with Aamir (2008). Dev.D (2009) was his breakthrough, winning the National Film Award for Best Music Direction, and he received Filmfare's R. D. Burman Award for New Music Talent in 2010. He composed and scored Wake Up Sid, wrote all the songs and the background score of Udaan, and became a leading composer of the 2010s Hindi new wave with Lootera, Queen and Andhadhun, for which he wrote nine songs. His indie-pop sound combines electronic textures with traditional elements. He composed the anthology Bombay Talkies (2013), whose song 'Apna Bombay Talkies' brings together many stars including Aamir Khan, and Advait Chandan's Secret Superstar (2017), produced by Aamir Khan Productions. Written for a teenage singer, its songs made Meghna Mishra a Filmfare winner and brought Trivedi the second of three consecutive Filmfare nominations, for Udta Punjab, Secret Superstar and Manmarziyaan.</t>
+          <t>Kunal Kohli, born in 1969, was a film critic and television host on Chalo Cinema before directing music videos and moving to features. His debut, Mujhse Dosti Karoge! (2002), failed despite an A-list cast, but Hum Tum (2004) was a hit and won him the Filmfare Best Director award. His next film, Fanaa (2006), produced by Aditya and Yash Chopra, was a romantic thriller in which Aamir Khan plays Rehan, a charming Delhi tour guide who is secretly a Kashmiri separatist, and Kajol plays the blind woman he seduces. Kohli also wrote the dialogue. Released during a ban in Gujarat prompted by Aamir's remarks on the Narmada dam, it grossed ₹105.48 crore worldwide and marked Kajol's return after five years. It won Filmfare awards for Kajol, for lyricist Prasoon Joshi and for the singers of 'Chand Sifarish', though some critics found it melodramatic. Kohli's later films, Thoda Pyaar Thoda Magic and Teri Meri Kahaani, did not match its success, and he produced Break Ke Baad and made his acting debut in Phir Se....</t>
         </is>
       </c>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-116; SOURCE-051; SOURCE-056</t>
+          <t>SOURCE-105; SOURCE-043</t>
         </is>
       </c>
       <c r="U43" s="5" t="inlineStr">
@@ -25153,15 +25143,15 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="169" customHeight="1">
+    <row r="44" ht="184" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>PERSON-043</t>
+          <t>PERSON-157</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Vijay Krishna Acharya</t>
+          <t>Nitesh Tiwari</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -25169,11 +25159,13 @@
           <t>Director; writer</t>
         </is>
       </c>
-      <c r="D44" s="18" t="n"/>
+      <c r="D44" s="17" t="n">
+        <v>1973</v>
+      </c>
       <c r="E44" s="18" t="n"/>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2004–present</t>
+          <t>2011–present</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -25183,61 +25175,65 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Born in Kanpur; educated at Kirori Mal College; married to Anusheh Khan, sister of director Kabir Khan.</t>
+          <t>Graduated from IIT Bombay (1996) in metallurgy; creative director at Leo Burnett.</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Wrote the screenplays and dialogue of Dhoom (2004) and Dhoom 2 (2006); directorial debut Tashan (2008), which opened to negative reviews.</t>
+          <t>Co-directed and co-wrote Chillar Party (2011), which won National Film Awards for Best Children's Film and Best Screenplay.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Dhoom (2004, writer); Dhoom 2 (2006, writer); Tashan (2008); Dhoom 3 (2013); Thugs of Hindostan (2018)</t>
+          <t>Chillar Party (2011); Bhoothnath Returns (2014); Dangal (2016); Chhichhore (2019); Bawaal (2023); Ramayana: Part 1 (2026)</t>
         </is>
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>Large-scale action spectacle and heist</t>
-        </is>
-      </c>
-      <c r="L44" s="19" t="n"/>
+          <t>Emotionally direct stories of family, underdogs and female empowerment</t>
+        </is>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>Grounded, character-driven storytelling that balances commercial appeal with social themes.</t>
+        </is>
+      </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Telstra People's Choice Award, Indian Film Festival of Melbourne 2014 (Dhoom 3)</t>
+          <t>Three National Film Awards (including Best Feature Film in Hindi for Chhichhore); Filmfare Best Director (Dangal)</t>
         </is>
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Dhoom 3 set international box-office records for Hindi cinema on release.</t>
+          <t>Directed Dangal, the highest-grossing Indian film, with unprecedented success in China.</t>
         </is>
       </c>
       <c r="O44" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in two Yash Raj spectacles, one record-breaking and one a costly failure.</t>
+          <t>Directed Aamir Khan in Dangal; the actor reportedly agreed to the film after the first narration.</t>
         </is>
       </c>
       <c r="P44" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>FILM-046; FILM-051</t>
+          <t>FILM-049</t>
         </is>
       </c>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>Dhoom 3 (2013)</t>
+          <t>Dangal (2016)</t>
         </is>
       </c>
       <c r="S44" s="5" t="inlineStr">
         <is>
-          <t>Vijay Krishna Acharya, from Kanpur, studied at Kirori Mal College and entered films as the screenwriter and dialogue writer of Yash Raj Films' Dhoom (2004) and Dhoom 2 (2006). His directorial debut, Tashan (2008), opened to negative reviews. Aditya Chopra nevertheless gave him Dhoom 3 (2013), which Acharya wrote and directed, with Aamir Khan in a double role as twin circus performers robbing the Chicago bank that ruined their father. The film grossed about ₹400 crore worldwide in ten days, became the first Indian film to pass ₹500 crore and won the inaugural Telstra People's Choice Award at the Indian Film Festival of Melbourne, though Indian reviews were mixed. Acharya and Aamir reunited on Thugs of Hindostan (2018), which Acharya wrote and directed, with Aamir as the double-crossing con man Firangi Mallah opposite Amitabh Bachchan. It had the biggest opening day for a Hindi film to that point but was widely panned in India, criticised for its direction, writing and length, and became an expensive disappointment. The contrasting fortunes of these two films bracket the most commercially extreme stretch of Aamir Khan's later career.</t>
+          <t>Nitesh Tiwari, born in 1973, graduated in metallurgical engineering from IIT Bombay in 1996 and worked as a creative director at the advertising agency Leo Burnett. He co-directed and co-wrote the children's film Chillar Party (2011), which won National Film Awards for Best Children's Film and Best Screenplay, and directed Bhoothnath Returns (2014). His biography reports that Aamir Khan agreed to Dangal after its first narration, which it presents as a first in Aamir's career. Released in 2016 and written by Tiwari with Piyush Gupta, Shreyas Jain and Nikhil Mehrotra, the film tells the true story of wrestler Mahavir Singh Phogat, who trains his daughters Geeta and Babita into international champions. It won Filmfare Best Film, Best Director for Tiwari and Best Actor for Aamir, and became the highest-grossing Indian film, with extraordinary success in China. Critics praised its honesty while debating whether it truly centres the daughters or the father. Tiwari followed it with Chhichhore (2019), drawn from his IIT years, which won the National Film Award for Best Feature Film in Hindi, and Bawaal (2023), and directed the two-part epic Ramayana. He is married to director Ashwiny Iyer Tiwari.</t>
         </is>
       </c>
       <c r="T44" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-117; SOURCE-052; SOURCE-057</t>
+          <t>SOURCE-119; SOURCE-055</t>
         </is>
       </c>
       <c r="U44" s="5" t="inlineStr">
@@ -25246,97 +25242,91 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="169" customHeight="1">
+    <row r="45" ht="154" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>PERSON-044</t>
+          <t>PERSON-167</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Pritam</t>
+          <t>R. S. Prasanna</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Music director (song composer)</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="n">
-        <v>1971</v>
-      </c>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="n"/>
       <c r="E45" s="18" t="n"/>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2001–present</t>
+          <t>2013–present</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil; Hindi</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Pritam Chakraborty studied sound recording at FTII and composed advertising jingles and television title tracks.</t>
+          <t>Gold medal winner at the L. V. Prasad Film Institute.</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Co-composed Tere Liye (2001) with Jeet Gannguli; solo debut Stumped (2003); breakthrough with Dhoom (2004).</t>
+          <t>Kalyana Samayal Saadham (2013), a Tamil romantic comedy.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Dhoom (2004); Gangster (2006); Jab We Met (2007); Life in a... Metro (2007); Barfi! (2012); Dhoom 3 (2013); Ae Dil Hai Mushkil (2016); Dangal (2016); Laal Singh Chaddha (2022); Brahmastra: Part One – Shiva (2022); Animal (2023)</t>
+          <t>Kalyana Samayal Saadham (2013); Shubh Mangal Saavdhan (2017); Sitaare Zameen Par (2025)</t>
         </is>
       </c>
       <c r="K45" s="19" t="inlineStr">
         <is>
-          <t>Chart-topping romantic and anthem songs for big-budget films</t>
+          <t>Sensitive subjects handled through comedy</t>
         </is>
       </c>
       <c r="L45" s="19" t="inlineStr">
         <is>
-          <t>Fusion of Indian classical influences with rock, Sufi and contemporary pop; has acknowledged early plagiarism mistakes.</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>National Film Award for Best Music Direction (70th National Film Awards); six Filmfare Best Music Director awards</t>
-        </is>
-      </c>
+          <t>Mature, humane comedy about taboo or overlooked issues.</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="n"/>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>One of contemporary Bollywood's most prolific and commercially successful composers, with more than 125 film scores.</t>
+          <t>Known for mainstream comedies that address subjects such as erectile dysfunction and intellectual disability.</t>
         </is>
       </c>
       <c r="O45" s="19" t="inlineStr">
         <is>
-          <t>Composed the songs for three of Aamir Khan's biggest productions of the 2010s–2020s.</t>
+          <t>Directed Aamir Khan in Sitaare Zameen Par, produced by Aamir Khan Productions.</t>
         </is>
       </c>
       <c r="P45" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>FILM-046; FILM-049; FILM-053</t>
+          <t>FILM-055</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>Dangal (2016)</t>
+          <t>Sitaare Zameen Par (2025)</t>
         </is>
       </c>
       <c r="S45" s="5" t="inlineStr">
         <is>
-          <t>Pritam Chakraborty, born in 1971, studied sound recording at FTII and wrote jingles for brands such as Santro and McDonald's and television title tracks before co-composing Tere Liye (2001) with Jeet Gannguli. His breakthrough was Yash Raj's Dhoom (2004), whose title track became popular internationally, followed by Gangster, Jab We Met and Barfi!. His style fuses Indian classical colours with rock, Sufi and contemporary pop, and he has acknowledged that he made plagiarism mistakes early in his career. With Aamir Khan he composed the songs for Dhoom 3 (2013), extending the franchise's sound, and for Dangal (2016), whose earthy, lyric-driven songs by Amitabh Bhattacharya, such as 'Haanikaarak Bapu' and 'Dhaakad', won Screen and Mirchi awards. He then composed Laal Singh Chaddha (2022); its songs, including 'Tere Hawaale', earned several Filmfare nominations although the film failed. Pritam has won six Filmfare Best Music Director awards and a National Film Award at the 70th National Film Awards. Across three films he became the principal song composer of Aamir Khan's large-scale later productions.</t>
+          <t>R. S. Prasanna trained at the L. V. Prasad Film Institute, where he won a gold medal, and made his debut with the Tamil romantic comedy Kalyana Samayal Saadham (2013), which treated erectile dysfunction as a modern urban problem with maturity and humour. He remade it in Hindi as Shubh Mangal Saavdhan (2017). His fetched biography does not yet cover his third feature, Sitaare Zameen Par (2025), details of which come from the film's article. An official remake of the Spanish film Campeones, produced by Aamir Khan and Aparna Purohit, it cast Aamir as Gulshan Arora, an arrogant assistant basketball coach sentenced to train a team of intellectually disabled players. The film opened to positive reviews for Aamir's committed performance and its warmth, though some critics found it preachy. It was a hit, and after its theatrical run it was released on YouTube as a pay-per-view film, along with extensive accessibility features. The collaboration continues Prasanna's interest in turning sensitive subjects into accessible mainstream comedy.</t>
         </is>
       </c>
       <c r="T45" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-118; SOURCE-052; SOURCE-055; SOURCE-059</t>
+          <t>SOURCE-121; SOURCE-061</t>
         </is>
       </c>
       <c r="U45" s="5" t="inlineStr">
@@ -25345,29 +25335,29 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="184" customHeight="1">
+    <row r="46" ht="199" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>PERSON-045</t>
+          <t>PERSON-172</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Nitesh Tiwari</t>
+          <t>Rakeysh Omprakash Mehra</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Director; writer</t>
+          <t>Director; producer; writer</t>
         </is>
       </c>
       <c r="D46" s="17" t="n">
-        <v>1973</v>
+        <v>1963</v>
       </c>
       <c r="E46" s="18" t="n"/>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2011–present</t>
+          <t>2001–present</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -25377,42 +25367,42 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Graduated from IIT Bombay (1996) in metallurgy; creative director at Leo Burnett.</t>
+          <t>Born in Delhi; studied at Shri Ram College of Commerce; sold vacuum cleaners for Eureka Forbes, then founded Flicks Motion Picture Company in 1986 to make commercials.</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Co-directed and co-wrote Chillar Party (2011), which won National Film Awards for Best Children's Film and Best Screenplay.</t>
+          <t>Aks (2001), a commercial failure; breakthrough with Rang De Basanti (2006).</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Chillar Party (2011); Bhoothnath Returns (2014); Dangal (2016); Chhichhore (2019); Bawaal (2023); Ramayana: Part 1 (2026)</t>
+          <t>Aks (2001); Rang De Basanti (2006); Delhi-6 (2009); Bhaag Milkha Bhaag (2013); Mirzya (2016); Mere Pyare Prime Minister (2019); Toofaan (2021)</t>
         </is>
       </c>
       <c r="K46" s="19" t="inlineStr">
         <is>
-          <t>Emotionally direct stories of family, underdogs and female empowerment</t>
+          <t>Youth activism, national identity, marks-driven education and vote-bank politics</t>
         </is>
       </c>
       <c r="L46" s="19" t="inlineStr">
         <is>
-          <t>Grounded, character-driven storytelling that balances commercial appeal with social themes.</t>
+          <t>Ensemble socio-political drama with music by A. R. Rahman and editing by P. S. Bharathi, his wife.</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Three National Film Awards (including Best Feature Film in Hindi for Chhichhore); Filmfare Best Director (Dangal)</t>
+          <t>Two Filmfare Best Director awards (Rang De Basanti; Bhaag Milkha Bhaag); two National Film Awards for Best Popular Film; BAFTA nomination; Nargis Dutt Award</t>
         </is>
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Directed Dangal, the highest-grossing Indian film, with unprecedented success in China.</t>
+          <t>Rang De Basanti's influence on youth protest was dubbed the 'RDB effect'.</t>
         </is>
       </c>
       <c r="O46" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in Dangal; the actor reportedly agreed to the film after the first narration.</t>
+          <t>Directed Aamir Khan in Rang De Basanti, which won him the Filmfare Best Actor (Critics) award.</t>
         </is>
       </c>
       <c r="P46" s="17" t="n">
@@ -25420,22 +25410,22 @@
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>FILM-049</t>
+          <t>FILM-036</t>
         </is>
       </c>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>Dangal (2016)</t>
+          <t>Rang De Basanti (2006)</t>
         </is>
       </c>
       <c r="S46" s="5" t="inlineStr">
         <is>
-          <t>Nitesh Tiwari, born in 1973, graduated in metallurgical engineering from IIT Bombay in 1996 and worked as a creative director at the advertising agency Leo Burnett. He co-directed and co-wrote the children's film Chillar Party (2011), which won National Film Awards for Best Children's Film and Best Screenplay, and directed Bhoothnath Returns (2014). His biography reports that Aamir Khan agreed to Dangal after its first narration, which it presents as a first in Aamir's career. Released in 2016 and written by Tiwari with Piyush Gupta, Shreyas Jain and Nikhil Mehrotra, the film tells the true story of wrestler Mahavir Singh Phogat, who trains his daughters Geeta and Babita into international champions. It won Filmfare Best Film, Best Director for Tiwari and Best Actor for Aamir, and became the highest-grossing Indian film, with extraordinary success in China. Critics praised its honesty while debating whether it truly centres the daughters or the father. Tiwari followed it with Chhichhore (2019), drawn from his IIT years, which won the National Film Award for Best Feature Film in Hindi, and Bawaal (2023), and directed the two-part epic Ramayana. He is married to director Ashwiny Iyer Tiwari.</t>
+          <t>Rakeysh Omprakash Mehra was born in Delhi in 1963 and studied commerce before working in sales for Eureka Forbes. In 1986 he founded Flicks Motion Picture Company and directed commercials for brands such as Coca-Cola and Pepsi. His first feature, the supernatural thriller Aks (2001) with Amitabh Bachchan, failed commercially. His second, Rang De Basanti (2006), was inspired partly by the Mandal Commission protests and follows a group of Delhi students cast in a British filmmaker's documentary about revolutionaries. Aamir Khan plays DJ, their charismatic, cynical leader, who is also cast as Chandrashekhar Azad. The film broke opening records, won the Filmfare awards for Best Film and Best Director, the National Film Award for Best Popular Film and a BAFTA nomination, and was India's Academy Award submission. Aamir won the Filmfare Best Actor (Critics) award. Its candlelight protests were copied in real life after the Jessica Lall verdict, and the media coined the term 'RDB effect' for such activism. Mehra later made Delhi-6, the Milkha Singh biopic Bhaag Milkha Bhaag (his second Filmfare Best Director award), Mirzya and Toofaan. He is married to P. S. Bharathi, who won the National and Filmfare editing awards for Rang De Basanti. In 2025 he chaired the international jury at IFFI.</t>
         </is>
       </c>
       <c r="T46" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-119; SOURCE-055</t>
+          <t>SOURCE-103; SOURCE-042</t>
         </is>
       </c>
       <c r="U46" s="5" t="inlineStr">
@@ -25447,88 +25437,94 @@
     <row r="47" ht="169" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>PERSON-046</t>
+          <t>PERSON-174</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Advait Chandan</t>
+          <t>Ram Gopal Varma</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Director; writer</t>
-        </is>
-      </c>
-      <c r="D47" s="18" t="n"/>
+          <t>Director; producer; writer</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>1962</v>
+      </c>
       <c r="E47" s="18" t="n"/>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2017–present</t>
+          <t>1989–present</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu; Hindi</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Began in 2007 as third assistant director and assistant production manager on Taare Zameen Par; assistant, casting director and post-production supervisor on Dhobi Ghat.</t>
+          <t>Born in Hyderabad; studied civil engineering and ran a video rental store, then assisted on Telugu films.</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Secret Superstar (2017), which he wrote and directed.</t>
+          <t>Siva (1989), a Telugu crime thriller that introduced the Steadicam to Indian cinema; Hindi breakthrough with Rangeela (1995).</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Secret Superstar (2017); Laal Singh Chaddha (2022); Loveyapa (2025)</t>
+          <t>Siva (1989); Kshana Kshanam (1991); Rangeela (1995); Satya (1998); Company (2002); Bhoot (2003); Sarkar (2005); Rakta Charitra (2010)</t>
         </is>
       </c>
       <c r="K47" s="19" t="inlineStr">
         <is>
-          <t>Ordinary people achieving the extraordinary; family and devotion</t>
-        </is>
-      </c>
-      <c r="L47" s="19" t="n"/>
+          <t>Gangster noir, horror and political crime; one major musical romance</t>
+        </is>
+      </c>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <t>Pioneer of 'Mumbai noir'; gritty realism and technical innovation.</t>
+        </is>
+      </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Zee Cine Most Promising Director (Secret Superstar); Filmfare Best Director and Best Screenplay nominations</t>
+          <t>National Film Award for Shool (1999, as producer); Nandi Awards for Siva; Filmfare Best Story (Rangeela)</t>
         </is>
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>His debut became one of the most profitable Indian films, driven by its success in China.</t>
+          <t>Regarded as a pioneer of new-age Indian cinema; launched directors including Anurag Kashyap and Madhur Bhandarkar.</t>
         </is>
       </c>
       <c r="O47" s="19" t="inlineStr">
         <is>
-          <t>Trained on Aamir Khan's productions and directed him in two films, one a major success and one a major failure.</t>
+          <t>Directed Rangeela, a turning point that recast Aamir Khan as a streetwise Mumbai lover.</t>
         </is>
       </c>
       <c r="P47" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>FILM-050; FILM-053</t>
+          <t>FILM-024</t>
         </is>
       </c>
       <c r="R47" s="5" t="inlineStr">
         <is>
-          <t>Secret Superstar (2017)</t>
+          <t>Rangeela (1995)</t>
         </is>
       </c>
       <c r="S47" s="5" t="inlineStr">
         <is>
-          <t>Advait Chandan came up inside Aamir Khan's production world. In 2007 he was third assistant director and assistant production manager on Taare Zameen Par, and on Kiran Rao's Dhobi Ghat he worked as an assistant, casting director and post-production supervisor. His biography's career section is flagged as needing more citations. Aamir Khan Productions and Zee Studios backed his writing-directing debut, Secret Superstar (2017), about a teenage girl who sings anonymously on YouTube to escape an abusive father; Aamir played Shakti Kumar, a vain music director who becomes her mentor, earning a Filmfare supporting nomination. The film became the highest-grossing Hindi film of 2017 and one of the most profitable Indian films, largely through its release in China. It won Chandan the Zee Cine Most Promising Director award and Filmfare nominations for direction and screenplay. He then directed Laal Singh Chaddha (2022), Atul Kulkarni's Indian adaptation of Forrest Gump with Aamir in the title role. Hit by a boycott campaign and mixed reviews, it lost heavily at the box office. Chandan's next film was Loveyapa (2025).</t>
+          <t>Ram Gopal Varma was born in Hyderabad in 1962, studied civil engineering and briefly worked as a site engineer before running a video rental store, where he studied which films audiences chose. After assisting on Telugu films he directed Siva (1989), a crime thriller that won Nandi Awards and introduced the Steadicam to Indian cinema. His Hindi breakthrough came with Rangeela (1995), a musical romance with Aamir Khan as Munna, a black-market ticket seller in love with his childhood friend Mili, played by Urmila Matondkar, who is being groomed for stardom. With A. R. Rahman's music and Manish Malhotra's costumes, the film was hailed for bringing a modern sensibility to mid-1990s Hindi cinema; it won Filmfare awards including Best Music Director and Best Story for Varma, and marked a turning point for both leads. Varma then redefined Hindi crime cinema with Satya (1998), Company (2002) and Sarkar (2005), pioneering a 'Mumbai noir' style, and scored a horror hit with Bhoot. His production 'factory' launched directors such as Anurag Kashyap and Madhur Bhandarkar. Rangeela remains his only film with Aamir Khan.</t>
         </is>
       </c>
       <c r="T47" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-120; SOURCE-044; SOURCE-048; SOURCE-056; SOURCE-059</t>
+          <t>SOURCE-093; SOURCE-030</t>
         </is>
       </c>
       <c r="U47" s="5" t="inlineStr">
@@ -25540,12 +25536,12 @@
     <row r="48" ht="154" customHeight="1">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>PERSON-047</t>
+          <t>PERSON-225</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>R. S. Prasanna</t>
+          <t>Vikram Bhatt</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -25557,48 +25553,52 @@
       <c r="E48" s="18" t="n"/>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2013–present</t>
+          <t>1982–present</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Tamil; Hindi</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>Gold medal winner at the L. V. Prasad Film Institute.</t>
+          <t>Grandson of pioneer filmmaker Vijay Bhatt and son of cinematographer Pravin Bhatt; began at 14 assisting Mukul Anand on Kanoon Kya Karega (1982).</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Kalyana Samayal Saadham (2013), a Tamil romantic comedy.</t>
+          <t>Breakthrough with Ghulam (1998).</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Kalyana Samayal Saadham (2013); Shubh Mangal Saavdhan (2017); Sitaare Zameen Par (2025)</t>
+          <t>Ghulam (1998); Kasoor (2001); Raaz (2002); 1920 (2008); Shaapit (2010); Haunted – 3D (2011); Raaz 3D (2012)</t>
         </is>
       </c>
       <c r="K48" s="19" t="inlineStr">
         <is>
-          <t>Sensitive subjects handled through comedy</t>
+          <t>Horror and thriller; the Raaz franchise</t>
         </is>
       </c>
       <c r="L48" s="19" t="inlineStr">
         <is>
-          <t>Mature, humane comedy about taboo or overlooked issues.</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="n"/>
+          <t>Genre filmmaking; introduced stereoscopic 3D horror to Indian cinema with Haunted – 3D.</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Filmfare Best Director nominations for Ghulam (1999) and Raaz (2003)</t>
+        </is>
+      </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Known for mainstream comedies that address subjects such as erectile dysfunction and intellectual disability.</t>
+          <t>A leading figure in Hindi horror cinema; founded Loneranger Productions.</t>
         </is>
       </c>
       <c r="O48" s="19" t="inlineStr">
         <is>
-          <t>Directed Aamir Khan in Sitaare Zameen Par, produced by Aamir Khan Productions.</t>
+          <t>Directed Aamir Khan in Ghulam, his most successful film.</t>
         </is>
       </c>
       <c r="P48" s="17" t="n">
@@ -25606,22 +25606,22 @@
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>FILM-055</t>
+          <t>FILM-028</t>
         </is>
       </c>
       <c r="R48" s="5" t="inlineStr">
         <is>
-          <t>Sitaare Zameen Par (2025)</t>
+          <t>Ghulam (1998)</t>
         </is>
       </c>
       <c r="S48" s="5" t="inlineStr">
         <is>
-          <t>R. S. Prasanna trained at the L. V. Prasad Film Institute, where he won a gold medal, and made his debut with the Tamil romantic comedy Kalyana Samayal Saadham (2013), which treated erectile dysfunction as a modern urban problem with maturity and humour. He remade it in Hindi as Shubh Mangal Saavdhan (2017). His fetched biography does not yet cover his third feature, Sitaare Zameen Par (2025), details of which come from the film's article. An official remake of the Spanish film Campeones, produced by Aamir Khan and Aparna Purohit, it cast Aamir as Gulshan Arora, an arrogant assistant basketball coach sentenced to train a team of intellectually disabled players. The film opened to positive reviews for Aamir's committed performance and its warmth, though some critics found it preachy. It was a hit, and after its theatrical run it was released on YouTube as a pay-per-view film, along with extensive accessibility features. The collaboration continues Prasanna's interest in turning sensitive subjects into accessible mainstream comedy.</t>
+          <t>Vikram Bhatt is the grandson of Vijay Bhatt, a pioneer of Indian cinema, and the son of cinematographer Pravin Bhatt. He entered films at 14, working with Mukul Anand on Kanoon Kya Karega (1982). His breakthrough came with Ghulam (1998), produced by Mukesh Bhatt and written by Anjum Rajabali from On the Waterfront. Aamir Khan plays Siddhu, an aimless Mumbai boxer drawn into a gangster's orbit through his brother, who finds the courage to testify and fight back. The film was a hit and earned Bhatt a Filmfare Best Director nomination. Its train-race dare won Filmfare's Best Scene award, and Aamir's own recording of 'Aati Kya Khandala' earned him a playback nomination. Bhatt then moved toward thrillers and horror with Kasoor and Raaz (2002), which earned a second Best Director nomination and began a franchise. Later films include 1920, Shaapit and Haunted – 3D (2011), which introduced stereoscopic 3D horror to India and became the highest-grossing Hindi horror film at the time. Ghulam remains his only film with Aamir Khan.</t>
         </is>
       </c>
       <c r="T48" s="5" t="inlineStr">
         <is>
-          <t>SOURCE-121; SOURCE-061</t>
+          <t>SOURCE-096; SOURCE-034</t>
         </is>
       </c>
       <c r="U48" s="5" t="inlineStr">
